--- a/GourmetProject/GameConfig/Datas/event.xlsx
+++ b/GourmetProject/GameConfig/Datas/event.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,70 +456,74 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>事件ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>事件名称</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>事件描述</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>消耗时间</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>效果类型</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>效果数值</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>float</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr"/>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ev_market</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>集市采购</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>花一点时间逛集市，获得金币。</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>GainGold</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>30</t>
         </is>
       </c>
     </row>
@@ -527,17 +531,17 @@
       <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ev_tasting</t>
+          <t>ev_market</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>试菜会</t>
+          <t>集市采购</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>举办试菜会，向菜谱加入一道新菜。</t>
+          <t>花一点时间逛集市，获得金币。</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -547,12 +551,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AddDish</t>
+          <t>GainGold</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -560,17 +564,17 @@
       <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ev_rest</t>
+          <t>ev_tasting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>歇业一天</t>
+          <t>试菜会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短暂休息，降低下一关要求分。</t>
+          <t>举办试菜会，向菜谱加入一道新菜。</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -580,12 +584,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LowerReq</t>
+          <t>AddDish</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -593,32 +597,32 @@
       <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ev_recruit</t>
+          <t>ev_rest</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>招募帮厨</t>
+          <t>歇业一天</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>招募帮厨，获得一件被动道具。</t>
+          <t>短暂休息，降低下一关要求分。</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GainItem</t>
+          <t>LowerReq</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0.1</t>
         </is>
       </c>
     </row>
@@ -626,32 +630,32 @@
       <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ev_gamble</t>
+          <t>ev_recruit</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>豪赌一桌</t>
+          <t>招募帮厨</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>高风险高回报：可能大赚也可能亏本。</t>
+          <t>招募帮厨，获得一件被动道具。</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>GainItem</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Gamble</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>50</t>
         </is>
       </c>
     </row>
@@ -659,30 +663,63 @@
       <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
+          <t>ev_gamble</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>豪赌一桌</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>高风险高回报：可能大赚也可能亏本。</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gamble</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
           <t>ev_upgrade</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>钻研食谱</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>钻研食谱，提升一道菜的美味度。</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="E9" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>UpgradeDish</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>5</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/event.xlsx
+++ b/GourmetProject/GameConfig/Datas/event.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event_option" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -413,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,277 +453,488 @@
           <t>effectValue</t>
         </is>
       </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>category</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>repeatable</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>preconditions</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>##comment</t>
+          <t>##type</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>事件ID</t>
+          <t>string</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>事件名称</t>
+          <t>string</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>事件描述</t>
+          <t>string</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>消耗时间</t>
+          <t>int</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>效果类型</t>
+          <t>string</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>效果数值</t>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>string</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ev_market</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>集市采购</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>花一点时间逛集市，获得金币。</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>GainGold</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
+        <v>30</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>reward</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ev_tasting</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>试菜会</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>举办试菜会，向菜谱加入一道新菜。</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>AddDish</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ev_rest</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>歇业一天</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>短暂休息，降低下一关要求分。</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>LowerReq</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>reward</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ev_recruit</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>招募帮厨</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>招募帮厨，获得一件被动道具。</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>2</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>GainItem</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>reward</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ev_gamble</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>豪赌一桌</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>高风险高回报：可能大赚也可能亏本。</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>1</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Gamble</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>50</v>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ev_upgrade</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>钻研食谱</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>钻研食谱，提升一道菜的美味度。</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>UpgradeDish</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>5</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>food</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eventId</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>resultType</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>resultValue</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>resultParam</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
         <is>
           <t>##type</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>opt_market_cheap</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>ev_market</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>省着点逛（+20 金币）</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>int</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
+          <t>GainGold</t>
+        </is>
+      </c>
+      <c r="F3" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
+          <t>opt_market_spree</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>ev_market</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>集市采购</t>
-        </is>
-      </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>花一点时间逛集市，获得金币。</t>
+          <t>大手笔扫货（+55 金币）</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
           <t>GainGold</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
+      <c r="F4" t="n">
+        <v>55</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ev_tasting</t>
+          <t>opt_gamble_small</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>试菜会</t>
+          <t>ev_gamble</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>举办试菜会，向菜谱加入一道新菜。</t>
+          <t>小赌怡情</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>AddDish</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+          <t>Gamble</t>
+        </is>
+      </c>
+      <c r="F5" t="n">
+        <v>30</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ev_rest</t>
+          <t>opt_gamble_big</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>歇业一天</t>
+          <t>ev_gamble</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>短暂休息，降低下一关要求分。</t>
+          <t>豪赌一把</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>LowerReq</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0.1</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr"/>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>ev_recruit</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>招募帮厨</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>招募帮厨，获得一件被动道具。</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>GainItem</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>ev_gamble</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>豪赌一桌</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>高风险高回报：可能大赚也可能亏本。</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
           <t>Gamble</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr"/>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>ev_upgrade</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>钻研食谱</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>钻研食谱，提升一道菜的美味度。</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>UpgradeDish</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
+      <c r="F6" t="n">
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/event.xlsx
+++ b/GourmetProject/GameConfig/Datas/event.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J8"/>
+  <dimension ref="A1:J9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -472,107 +472,121 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>事件ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>事件名称</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>事件描述</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>消耗天数</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>效果类型</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>效果数值</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>事件分类</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>是否可重复</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>前置条件</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
         <is>
           <t>int</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
         <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ev_market</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>集市采购</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>花一点时间逛集市，获得金币。</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>1</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>GainGold</t>
-        </is>
-      </c>
-      <c r="G3" t="n">
-        <v>30</v>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>reward</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>true</t>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>string</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="B4" t="inlineStr">
         <is>
-          <t>ev_tasting</t>
+          <t>ev_market</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>试菜会</t>
+          <t>集市采购</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>举办试菜会，向菜谱加入一道新菜。</t>
+          <t>花一点时间逛集市，获得金币。</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -580,15 +594,15 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>AddDish</t>
+          <t>GainGold</t>
         </is>
       </c>
       <c r="G4" t="n">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>food</t>
+          <t>reward</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -600,17 +614,17 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>ev_rest</t>
+          <t>ev_tasting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>歇业一天</t>
+          <t>试菜会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>短暂休息，降低下一关要求分。</t>
+          <t>举办试菜会，向菜谱加入一道新菜。</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -618,15 +632,15 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>LowerReq</t>
+          <t>AddDish</t>
         </is>
       </c>
       <c r="G5" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>reward</t>
+          <t>food</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -638,29 +652,29 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>ev_recruit</t>
+          <t>ev_rest</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>招募帮厨</t>
+          <t>歇业一天</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>招募帮厨，获得一件被动道具。</t>
+          <t>短暂休息，降低下一关要求分。</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>GainItem</t>
+          <t>LowerReq</t>
         </is>
       </c>
       <c r="G6" t="n">
-        <v>1</v>
+        <v>0.1</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -669,81 +683,119 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>false</t>
+          <t>true</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>ev_gamble</t>
+          <t>ev_recruit</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>豪赌一桌</t>
+          <t>招募帮厨</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>高风险高回报：可能大赚也可能亏本。</t>
+          <t>招募帮厨，获得一件被动道具。</t>
         </is>
       </c>
       <c r="E7" t="n">
+        <v>2</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>GainItem</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>1</v>
       </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Gamble</t>
-        </is>
-      </c>
-      <c r="G7" t="n">
-        <v>50</v>
-      </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>negative</t>
+          <t>reward</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
+          <t>ev_gamble</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>豪赌一桌</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>高风险高回报：可能大赚也可能亏本。</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>1</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Gamble</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>50</v>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>negative</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
           <t>ev_upgrade</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>钻研食谱</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
+      <c r="D9" t="inlineStr">
         <is>
           <t>钻研食谱，提升一道菜的美味度。</t>
         </is>
       </c>
-      <c r="E8" t="n">
+      <c r="E9" t="n">
         <v>2</v>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>UpgradeDish</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="G9" t="n">
         <v>5</v>
       </c>
-      <c r="H8" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>food</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I9" t="inlineStr">
         <is>
           <t>true</t>
         </is>

--- a/GourmetProject/GameConfig/Datas/event.xlsx
+++ b/GourmetProject/GameConfig/Datas/event.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -460,10 +460,15 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>repeatable</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>preconditions</t>
         </is>
@@ -477,47 +482,52 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>事件ID</t>
+          <t>事件ID。</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>事件名称</t>
+          <t>事件名称。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>事件描述</t>
+          <t>事件描述。</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>消耗天数</t>
+          <t>事件默认耗时；事件行动仍以行动costDays推进。</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>效果类型</t>
+          <t>无选项事件的直接效果类型。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>效果数值</t>
+          <t>无选项事件的直接效果数值。</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>事件分类</t>
+          <t>事件分类，用于后续事件池扩展。</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>是否可重复</t>
+          <t>事件节点随机权重；&lt;=0时运行时按1处理。</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>前置条件</t>
+          <t>是否可重复触发；false命中后写入UsedEventIds。</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>前置条件表达式，空=无条件。</t>
         </is>
       </c>
     </row>
@@ -564,16 +574,22 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
           <t>bool</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="K3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
     <row r="4">
+      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>ev_market</t>
@@ -605,13 +621,18 @@
           <t>reward</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="I4" t="n">
+        <v>80</v>
+      </c>
+      <c r="J4" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
+      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
+      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>ev_tasting</t>
@@ -643,13 +664,18 @@
           <t>food</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="I5" t="n">
+        <v>60</v>
+      </c>
+      <c r="J5" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
+      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
+      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>ev_rest</t>
@@ -681,13 +707,18 @@
           <t>reward</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="I6" t="n">
+        <v>45</v>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
+      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
+      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>ev_recruit</t>
@@ -719,13 +750,18 @@
           <t>reward</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
+      <c r="I7" t="n">
+        <v>35</v>
+      </c>
+      <c r="J7" t="inlineStr">
         <is>
           <t>false</t>
         </is>
       </c>
+      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
+      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>ev_gamble</t>
@@ -757,13 +793,18 @@
           <t>negative</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="I8" t="n">
+        <v>30</v>
+      </c>
+      <c r="J8" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
+      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
+      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>ev_upgrade</t>
@@ -795,11 +836,15 @@
           <t>food</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
+      <c r="I9" t="n">
+        <v>50</v>
+      </c>
+      <c r="J9" t="inlineStr">
         <is>
           <t>true</t>
         </is>
       </c>
+      <c r="K9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -812,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -855,139 +900,184 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>事件选项ID。</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>所属事件ID。</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>选项显示文本。</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>选项结果类型。</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>选项结果数值。</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>选项结果参数。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
           <t>##type</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>float</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>string</t>
         </is>
       </c>
     </row>
-    <row r="3">
-      <c r="B3" t="inlineStr">
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
         <is>
           <t>opt_market_cheap</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>ev_market</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>省着点逛（+20 金币）</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>GainGold</t>
         </is>
       </c>
-      <c r="F3" t="n">
+      <c r="F4" t="n">
         <v>20</v>
       </c>
-    </row>
-    <row r="4">
-      <c r="B4" t="inlineStr">
+      <c r="G4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
         <is>
           <t>opt_market_spree</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>ev_market</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>大手笔扫货（+55 金币）</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>GainGold</t>
         </is>
       </c>
-      <c r="F4" t="n">
+      <c r="F5" t="n">
         <v>55</v>
       </c>
-    </row>
-    <row r="5">
-      <c r="B5" t="inlineStr">
+      <c r="G5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
         <is>
           <t>opt_gamble_small</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>ev_gamble</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>小赌怡情</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>Gamble</t>
         </is>
       </c>
-      <c r="F5" t="n">
+      <c r="F6" t="n">
         <v>30</v>
       </c>
-    </row>
-    <row r="6">
-      <c r="B6" t="inlineStr">
+      <c r="G6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
         <is>
           <t>opt_gamble_big</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>ev_gamble</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>豪赌一把</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>Gamble</t>
         </is>
       </c>
-      <c r="F6" t="n">
+      <c r="F7" t="n">
         <v>90</v>
       </c>
+      <c r="G7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/GourmetProject/GameConfig/Datas/event.xlsx
+++ b/GourmetProject/GameConfig/Datas/event.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,7 +589,6 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>ev_market</t>
@@ -629,10 +628,8 @@
           <t>true</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>ev_tasting</t>
@@ -672,10 +669,8 @@
           <t>true</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>ev_rest</t>
@@ -715,10 +710,8 @@
           <t>true</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>ev_recruit</t>
@@ -758,10 +751,8 @@
           <t>false</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
       <c r="B8" t="inlineStr">
         <is>
           <t>ev_gamble</t>
@@ -801,10 +792,8 @@
           <t>true</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr"/>
       <c r="B9" t="inlineStr">
         <is>
           <t>ev_upgrade</t>
@@ -844,7 +833,50 @@
           <t>true</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ev_debug_shop</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>神秘商贩</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>你听说附近有一间临时食材店。</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>debug</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="b">
+        <v>1</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>minWeek:999</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -972,7 +1004,6 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr"/>
       <c r="B4" t="inlineStr">
         <is>
           <t>opt_market_cheap</t>
@@ -996,10 +1027,8 @@
       <c r="F4" t="n">
         <v>20</v>
       </c>
-      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr"/>
       <c r="B5" t="inlineStr">
         <is>
           <t>opt_market_spree</t>
@@ -1023,10 +1052,8 @@
       <c r="F5" t="n">
         <v>55</v>
       </c>
-      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr"/>
       <c r="B6" t="inlineStr">
         <is>
           <t>opt_gamble_small</t>
@@ -1050,10 +1077,8 @@
       <c r="F6" t="n">
         <v>30</v>
       </c>
-      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr"/>
       <c r="B7" t="inlineStr">
         <is>
           <t>opt_gamble_big</t>
@@ -1077,7 +1102,6 @@
       <c r="F7" t="n">
         <v>90</v>
       </c>
-      <c r="G7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/GourmetProject/GameConfig/Datas/event.xlsx
+++ b/GourmetProject/GameConfig/Datas/event.xlsx
@@ -414,7 +414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K10"/>
+  <dimension ref="A1:H14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,37 +440,22 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>timeCost</t>
+          <t>eventType</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>effectType</t>
+          <t>preconditions</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>effectValue</t>
+          <t>weight</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>category</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>weight</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
           <t>repeatable</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>preconditions</t>
         </is>
       </c>
     </row>
@@ -482,52 +467,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>事件ID。</t>
+          <t>事件ID</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>事件名称。</t>
+          <t>事件名称</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>事件描述。</t>
+          <t>事件描述</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>事件默认耗时；事件行动仍以行动costDays推进。</t>
+          <t>事件分类(Event/Reward/Negative,决定被哪种行动 roll)</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>无选项事件的直接效果类型。</t>
+          <t>出现前置条件</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>无选项事件的直接效果数值。</t>
+          <t>随机权重</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>事件分类，用于后续事件池扩展。</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>事件节点随机权重；&lt;=0时运行时按1处理。</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>是否可重复触发；false命中后写入UsedEventIds。</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>前置条件表达式，空=无条件。</t>
+          <t>是否可重复(false 命中后本局不再出)</t>
         </is>
       </c>
     </row>
@@ -554,7 +524,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>int</t>
+          <t>ActionBehavior</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -569,22 +539,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>float</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
           <t>bool</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>string</t>
         </is>
       </c>
     </row>
@@ -596,37 +551,24 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>集市采购</t>
+          <t>逛集市</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>花一点时间逛集市，获得金币。</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
+          <t>花点时间逛集市采购。</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>60</v>
+      </c>
+      <c r="H4" t="b">
         <v>1</v>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>GainGold</t>
-        </is>
-      </c>
-      <c r="G4" t="n">
-        <v>30</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>reward</t>
-        </is>
-      </c>
-      <c r="I4" t="n">
-        <v>80</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
       </c>
     </row>
     <row r="5">
@@ -637,37 +579,24 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>试菜会</t>
+          <t>办试菜会</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>举办试菜会，向菜谱加入一道新菜。</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
+          <t>举办试菜会，给菜谱加一道菜。</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>50</v>
+      </c>
+      <c r="H5" t="b">
         <v>1</v>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>AddDish</t>
-        </is>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>food</t>
-        </is>
-      </c>
-      <c r="I5" t="n">
-        <v>60</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
       </c>
     </row>
     <row r="6">
@@ -686,29 +615,16 @@
           <t>短暂休息，降低下一关要求分。</t>
         </is>
       </c>
-      <c r="E6" t="n">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>40</v>
+      </c>
+      <c r="H6" t="b">
         <v>1</v>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>LowerReq</t>
-        </is>
-      </c>
-      <c r="G6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>reward</t>
-        </is>
-      </c>
-      <c r="I6" t="n">
-        <v>45</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
       </c>
     </row>
     <row r="7">
@@ -727,117 +643,78 @@
           <t>招募帮厨，获得一件被动道具。</t>
         </is>
       </c>
-      <c r="E7" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>GainItem</t>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Event</t>
         </is>
       </c>
       <c r="G7" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>reward</t>
-        </is>
-      </c>
-      <c r="I7" t="n">
         <v>35</v>
       </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
+      <c r="H7" t="b">
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" t="inlineStr">
         <is>
-          <t>ev_gamble</t>
+          <t>ev_study</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>豪赌一桌</t>
+          <t>钻研食谱</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>高风险高回报：可能大赚也可能亏本。</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
+          <t>钻研食谱，提升一道菜。</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>30</v>
+      </c>
+      <c r="H8" t="b">
         <v>1</v>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Gamble</t>
-        </is>
-      </c>
-      <c r="G8" t="n">
-        <v>50</v>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>negative</t>
-        </is>
-      </c>
-      <c r="I8" t="n">
-        <v>30</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>ev_upgrade</t>
+          <t>ev_gamble</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>钻研食谱</t>
+          <t>豪赌一桌</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>钻研食谱，提升一道菜的美味度。</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>UpgradeDish</t>
+          <t>高风险高回报，可能大赚也可能亏本。</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Event</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>5</v>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>food</t>
-        </is>
-      </c>
-      <c r="I9" t="n">
-        <v>50</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>true</t>
-        </is>
+        <v>30</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
       <c r="B10" t="inlineStr">
         <is>
-          <t>ev_debug_shop</t>
+          <t>ev_shop</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -847,35 +724,131 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>你听说附近有一间临时食材店。</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>1</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Shop</t>
+          <t>遇到神秘商贩，进入商店。</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Event</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>0</v>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>debug</t>
-        </is>
-      </c>
-      <c r="I10" t="n">
-        <v>0</v>
-      </c>
-      <c r="J10" t="b">
+      <c r="H10" t="b">
         <v>1</v>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>minWeek:999</t>
-        </is>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ev_tip</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>收小费</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>客人很满意，留下一笔小费。</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>25</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ev_gift</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>免费赠礼</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>获得一件被动道具。</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>20</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ev_tax</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>临时摊派</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>被临时摊派了一笔费用。</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G13" t="n">
+        <v>30</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>ev_spoil</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>食材变质</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>部分食材变质，损失金币。</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="G14" t="n">
+        <v>20</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -889,7 +862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -915,17 +888,17 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>resultType</t>
+          <t>effectType</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>resultValue</t>
+          <t>effectValue</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>resultParam</t>
+          <t>effectParam</t>
         </is>
       </c>
     </row>
@@ -937,32 +910,32 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>事件选项ID。</t>
+          <t>选项ID</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>所属事件ID。</t>
+          <t>所属事件ID→event.id</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>选项显示文本。</t>
+          <t>选项文本(单选项=自动结算,无需玩家点选)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>选项结果类型。</t>
+          <t>结果效果类型</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>选项结果数值。</t>
+          <t>结果数值</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>选项结果参数。</t>
+          <t>结果参数</t>
         </is>
       </c>
     </row>
@@ -989,7 +962,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>string</t>
+          <t>EffectType</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -1056,51 +1029,286 @@
     <row r="6">
       <c r="B6" t="inlineStr">
         <is>
-          <t>opt_gamble_small</t>
+          <t>opt_tasting</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>ev_gamble</t>
+          <t>ev_tasting</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>小赌怡情</t>
+          <t>给菜谱加一道菜</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Gamble</t>
+          <t>AddDish</t>
         </is>
       </c>
       <c r="F6" t="n">
-        <v>30</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
+          <t>opt_rest</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ev_rest</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>歇业，降低下一关目标分</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LowerReq</t>
+        </is>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>opt_recruit</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ev_recruit</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>招募帮厨（+被动道具）</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>GainItem</t>
+        </is>
+      </c>
+      <c r="F8" t="n">
+        <v>1</v>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>opt_study</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ev_study</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>钻研，提升一道菜</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>UpgradeDish</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>opt_gamble_small</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ev_gamble</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>小赌怡情</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Gamble</t>
+        </is>
+      </c>
+      <c r="F10" t="n">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
           <t>opt_gamble_big</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C11" t="inlineStr">
         <is>
           <t>ev_gamble</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="D11" t="inlineStr">
         <is>
           <t>豪赌一把</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="E11" t="inlineStr">
         <is>
           <t>Gamble</t>
         </is>
       </c>
-      <c r="F7" t="n">
+      <c r="F11" t="n">
         <v>90</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>opt_shop</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ev_shop</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>进入商店</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Shop</t>
+        </is>
+      </c>
+      <c r="F12" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>opt_tip</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ev_tip</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>收下小费（+25 金币）</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>GainGold</t>
+        </is>
+      </c>
+      <c r="F13" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>opt_gift</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ev_gift</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>收下赠礼（+被动道具）</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>GainItem</t>
+        </is>
+      </c>
+      <c r="F14" t="n">
+        <v>1</v>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Passive</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>opt_tax</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ev_tax</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>接受摊派（-20 金币）</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>GainGold</t>
+        </is>
+      </c>
+      <c r="F15" t="n">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>opt_spoil</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>ev_spoil</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>认栽（-15 金币）</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>GainGold</t>
+        </is>
+      </c>
+      <c r="F16" t="n">
+        <v>-15</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/event.xlsx
+++ b/GourmetProject/GameConfig/Datas/event.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16760"/>
+    <workbookView windowHeight="16760" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="event" sheetId="1" r:id="rId1"/>
@@ -28,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
   <si>
     <t>##var</t>
   </si>
@@ -54,6 +54,9 @@
     <t>repeatable</t>
   </si>
   <si>
+    <t>bgSprite</t>
+  </si>
+  <si>
     <t>##comment</t>
   </si>
   <si>
@@ -78,6 +81,9 @@
     <t>是否可重复(false 命中后本局不再出)</t>
   </si>
   <si>
+    <t>事件背景 Sprite(Resources 路径,空=默认占位)</t>
+  </si>
+  <si>
     <t>##type</t>
   </si>
   <si>
@@ -93,120 +99,6 @@
     <t>bool</t>
   </si>
   <si>
-    <t>ev_market</t>
-  </si>
-  <si>
-    <t>逛集市</t>
-  </si>
-  <si>
-    <t>花点时间逛集市采购。</t>
-  </si>
-  <si>
-    <t>Event</t>
-  </si>
-  <si>
-    <t>True</t>
-  </si>
-  <si>
-    <t>ev_tasting</t>
-  </si>
-  <si>
-    <t>办试菜会</t>
-  </si>
-  <si>
-    <t>举办试菜会，给菜谱加一道菜。</t>
-  </si>
-  <si>
-    <t>ev_rest</t>
-  </si>
-  <si>
-    <t>歇业一天</t>
-  </si>
-  <si>
-    <t>短暂休息，降低下一关要求分。</t>
-  </si>
-  <si>
-    <t>ev_recruit</t>
-  </si>
-  <si>
-    <t>招募帮厨</t>
-  </si>
-  <si>
-    <t>招募帮厨，获得一件被动道具。</t>
-  </si>
-  <si>
-    <t>False</t>
-  </si>
-  <si>
-    <t>ev_study</t>
-  </si>
-  <si>
-    <t>钻研食谱</t>
-  </si>
-  <si>
-    <t>钻研食谱，提升一道菜。</t>
-  </si>
-  <si>
-    <t>ev_gamble</t>
-  </si>
-  <si>
-    <t>豪赌一桌</t>
-  </si>
-  <si>
-    <t>赌桌就在眼前，热气腾腾。要不要试试手气？</t>
-  </si>
-  <si>
-    <t>ev_shop</t>
-  </si>
-  <si>
-    <t>神秘商贩</t>
-  </si>
-  <si>
-    <t>遇到神秘商贩，进入商店。</t>
-  </si>
-  <si>
-    <t>ev_tip</t>
-  </si>
-  <si>
-    <t>收小费</t>
-  </si>
-  <si>
-    <t>客人很满意，留下一笔小费。</t>
-  </si>
-  <si>
-    <t>Reward</t>
-  </si>
-  <si>
-    <t>ev_gift</t>
-  </si>
-  <si>
-    <t>免费赠礼</t>
-  </si>
-  <si>
-    <t>获得一件被动道具。</t>
-  </si>
-  <si>
-    <t>ev_tax</t>
-  </si>
-  <si>
-    <t>临时摊派</t>
-  </si>
-  <si>
-    <t>被临时摊派了一笔费用。</t>
-  </si>
-  <si>
-    <t>Negative</t>
-  </si>
-  <si>
-    <t>ev_spoil</t>
-  </si>
-  <si>
-    <t>食材变质</t>
-  </si>
-  <si>
-    <t>部分食材变质，损失金币。</t>
-  </si>
-  <si>
     <t>eventId</t>
   </si>
   <si>
@@ -231,6 +123,9 @@
     <t>*effectParams</t>
   </si>
   <si>
+    <t>repeatSelf</t>
+  </si>
+  <si>
     <t>选项ID</t>
   </si>
   <si>
@@ -258,6 +153,9 @@
     <t>效果参数列表(与类型逐行对齐,可空)</t>
   </si>
   <si>
+    <t>是否可在结果页重复选择本选项(false=否)</t>
+  </si>
+  <si>
     <t>list,EffectType</t>
   </si>
   <si>
@@ -265,168 +163,6 @@
   </si>
   <si>
     <t>list,string</t>
-  </si>
-  <si>
-    <t>opt_market_cheap</t>
-  </si>
-  <si>
-    <t>省着点逛（+20 金币）</t>
-  </si>
-  <si>
-    <t>GainGold</t>
-  </si>
-  <si>
-    <t>20</t>
-  </si>
-  <si>
-    <t>opt_market_spree</t>
-  </si>
-  <si>
-    <t>大手笔扫货（+55 金币）</t>
-  </si>
-  <si>
-    <t>55</t>
-  </si>
-  <si>
-    <t>opt_tasting</t>
-  </si>
-  <si>
-    <t>给菜谱加一道菜</t>
-  </si>
-  <si>
-    <t>AddDish</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>opt_rest</t>
-  </si>
-  <si>
-    <t>歇业，降低下一关目标分</t>
-  </si>
-  <si>
-    <t>LowerReq</t>
-  </si>
-  <si>
-    <t>0.1</t>
-  </si>
-  <si>
-    <t>opt_recruit</t>
-  </si>
-  <si>
-    <t>招募帮厨（+被动道具）</t>
-  </si>
-  <si>
-    <t>GainItem</t>
-  </si>
-  <si>
-    <t>Passive</t>
-  </si>
-  <si>
-    <t>opt_study</t>
-  </si>
-  <si>
-    <t>钻研，提升一道菜</t>
-  </si>
-  <si>
-    <t>UpgradeDish</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>opt_gamble_small</t>
-  </si>
-  <si>
-    <t>稳妥点，小赌一把</t>
-  </si>
-  <si>
-    <t>Gamble</t>
-  </si>
-  <si>
-    <t>30</t>
-  </si>
-  <si>
-    <t>opt_gamble_big</t>
-  </si>
-  <si>
-    <t>上大注，豪赌一场</t>
-  </si>
-  <si>
-    <t>90</t>
-  </si>
-  <si>
-    <t>opt_gamble_think</t>
-  </si>
-  <si>
-    <t>先观察一会儿…</t>
-  </si>
-  <si>
-    <t>邻座的老赌客压低声音，朝你使了个眼色。</t>
-  </si>
-  <si>
-    <t>opt_gamble_follow</t>
-  </si>
-  <si>
-    <t>听老赌客的，押他说的号</t>
-  </si>
-  <si>
-    <t>60</t>
-  </si>
-  <si>
-    <t>opt_gamble_leave</t>
-  </si>
-  <si>
-    <t>不信这套，转身离开</t>
-  </si>
-  <si>
-    <t>你摆摆手离开了赌桌，什么也没发生。</t>
-  </si>
-  <si>
-    <t>opt_shop</t>
-  </si>
-  <si>
-    <t>进入商店</t>
-  </si>
-  <si>
-    <t>Shop</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>opt_tip</t>
-  </si>
-  <si>
-    <t>收下小费（+25 金币）</t>
-  </si>
-  <si>
-    <t>25</t>
-  </si>
-  <si>
-    <t>opt_gift</t>
-  </si>
-  <si>
-    <t>收下赠礼（+被动道具）</t>
-  </si>
-  <si>
-    <t>opt_tax</t>
-  </si>
-  <si>
-    <t>接受摊派（-20 金币）</t>
-  </si>
-  <si>
-    <t>-20</t>
-  </si>
-  <si>
-    <t>opt_spoil</t>
-  </si>
-  <si>
-    <t>认栽（-15 金币）</t>
-  </si>
-  <si>
-    <t>-15</t>
   </si>
 </sst>
 </file>
@@ -1388,8 +1124,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H14"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelCol="7"/>
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
     <col min="2" max="2" width="11.2307692307692" customWidth="1"/>
@@ -1401,7 +1137,7 @@
     <col min="8" max="8" width="38.6923076923077" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:9">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1426,277 +1162,66 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="2" spans="1:8">
+    <row r="2" spans="1:9">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C2" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="E2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H2" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:8">
+    <row r="3" spans="1:9">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
+        <v>21</v>
+      </c>
+      <c r="H3" t="s">
+        <v>22</v>
+      </c>
+      <c r="I3" t="s">
         <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="2:8">
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" t="s">
-        <v>22</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>24</v>
-      </c>
-      <c r="G4">
-        <v>60</v>
-      </c>
-      <c r="H4" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="5" spans="2:8">
-      <c r="B5" t="s">
-        <v>26</v>
-      </c>
-      <c r="C5" t="s">
-        <v>27</v>
-      </c>
-      <c r="D5" t="s">
-        <v>28</v>
-      </c>
-      <c r="E5" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5">
-        <v>50</v>
-      </c>
-      <c r="H5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="6" spans="2:8">
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="D6" t="s">
-        <v>31</v>
-      </c>
-      <c r="E6" t="s">
-        <v>24</v>
-      </c>
-      <c r="G6">
-        <v>40</v>
-      </c>
-      <c r="H6" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="7" spans="2:8">
-      <c r="B7" t="s">
-        <v>32</v>
-      </c>
-      <c r="C7" t="s">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7" t="s">
-        <v>24</v>
-      </c>
-      <c r="G7">
-        <v>35</v>
-      </c>
-      <c r="H7" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="8" spans="2:8">
-      <c r="B8" t="s">
-        <v>36</v>
-      </c>
-      <c r="C8" t="s">
-        <v>37</v>
-      </c>
-      <c r="D8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8" t="s">
-        <v>24</v>
-      </c>
-      <c r="G8">
-        <v>30</v>
-      </c>
-      <c r="H8" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="2:8">
-      <c r="B9" t="s">
-        <v>39</v>
-      </c>
-      <c r="C9" t="s">
-        <v>40</v>
-      </c>
-      <c r="D9" t="s">
-        <v>41</v>
-      </c>
-      <c r="E9" t="s">
-        <v>24</v>
-      </c>
-      <c r="G9">
-        <v>30</v>
-      </c>
-      <c r="H9" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="10" spans="2:8">
-      <c r="B10" t="s">
-        <v>42</v>
-      </c>
-      <c r="C10" t="s">
-        <v>43</v>
-      </c>
-      <c r="D10" t="s">
-        <v>44</v>
-      </c>
-      <c r="E10" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10">
-        <v>0</v>
-      </c>
-      <c r="H10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="11" spans="2:8">
-      <c r="B11" t="s">
-        <v>45</v>
-      </c>
-      <c r="C11" t="s">
-        <v>46</v>
-      </c>
-      <c r="D11" t="s">
-        <v>47</v>
-      </c>
-      <c r="E11" t="s">
-        <v>48</v>
-      </c>
-      <c r="G11">
-        <v>25</v>
-      </c>
-      <c r="H11" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="2:8">
-      <c r="B12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C12" t="s">
-        <v>50</v>
-      </c>
-      <c r="D12" t="s">
-        <v>51</v>
-      </c>
-      <c r="E12" t="s">
-        <v>48</v>
-      </c>
-      <c r="G12">
-        <v>20</v>
-      </c>
-      <c r="H12" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="13" spans="2:8">
-      <c r="B13" t="s">
-        <v>52</v>
-      </c>
-      <c r="C13" t="s">
-        <v>53</v>
-      </c>
-      <c r="D13" t="s">
-        <v>54</v>
-      </c>
-      <c r="E13" t="s">
-        <v>55</v>
-      </c>
-      <c r="G13">
-        <v>30</v>
-      </c>
-      <c r="H13" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="14" spans="2:8">
-      <c r="B14" t="s">
-        <v>56</v>
-      </c>
-      <c r="C14" t="s">
-        <v>57</v>
-      </c>
-      <c r="D14" t="s">
-        <v>58</v>
-      </c>
-      <c r="E14" t="s">
-        <v>55</v>
-      </c>
-      <c r="G14">
-        <v>20</v>
-      </c>
-      <c r="H14" t="s">
-        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -1708,8 +1233,8 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
+  <dimension ref="A1:K3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="2"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
     <col min="2" max="2" width="19.8461538461538" customWidth="1"/>
@@ -1723,7 +1248,7 @@
     <col min="10" max="10" width="38.8461538461538" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:11">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1731,370 +1256,101 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>59</v>
+        <v>23</v>
       </c>
       <c r="D1" t="s">
-        <v>60</v>
+        <v>24</v>
       </c>
       <c r="E1" t="s">
-        <v>61</v>
+        <v>25</v>
       </c>
       <c r="F1" t="s">
-        <v>62</v>
+        <v>26</v>
       </c>
       <c r="G1" t="s">
-        <v>63</v>
+        <v>27</v>
       </c>
       <c r="H1" t="s">
-        <v>64</v>
+        <v>28</v>
       </c>
       <c r="I1" t="s">
-        <v>65</v>
+        <v>29</v>
       </c>
       <c r="J1" t="s">
-        <v>66</v>
+        <v>30</v>
+      </c>
+      <c r="K1" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="2" spans="1:10">
+    <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B2" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="C2" t="s">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="D2" t="s">
-        <v>69</v>
+        <v>34</v>
       </c>
       <c r="E2" t="s">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="F2" t="s">
-        <v>71</v>
+        <v>36</v>
       </c>
       <c r="G2" t="s">
-        <v>72</v>
+        <v>37</v>
       </c>
       <c r="H2" t="s">
-        <v>73</v>
+        <v>38</v>
       </c>
       <c r="I2" t="s">
-        <v>74</v>
+        <v>39</v>
       </c>
       <c r="J2" t="s">
-        <v>75</v>
+        <v>40</v>
+      </c>
+      <c r="K2" t="s">
+        <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:10">
+    <row r="3" spans="1:11">
       <c r="A3" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="B3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H3" t="s">
-        <v>76</v>
+        <v>42</v>
       </c>
       <c r="I3" t="s">
-        <v>77</v>
+        <v>43</v>
       </c>
       <c r="J3" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="4" spans="2:9">
-      <c r="B4" t="s">
-        <v>79</v>
-      </c>
-      <c r="C4" t="s">
-        <v>21</v>
-      </c>
-      <c r="E4" t="s">
-        <v>80</v>
-      </c>
-      <c r="H4" t="s">
-        <v>81</v>
-      </c>
-      <c r="I4" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="5" spans="2:9">
-      <c r="B5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C5" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" t="s">
-        <v>84</v>
-      </c>
-      <c r="H5" t="s">
-        <v>81</v>
-      </c>
-      <c r="I5" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="6" spans="2:9">
-      <c r="B6" t="s">
-        <v>86</v>
-      </c>
-      <c r="C6" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" t="s">
-        <v>87</v>
-      </c>
-      <c r="H6" t="s">
-        <v>88</v>
-      </c>
-      <c r="I6" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="7" spans="2:9">
-      <c r="B7" t="s">
-        <v>90</v>
-      </c>
-      <c r="C7" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" t="s">
-        <v>91</v>
-      </c>
-      <c r="H7" t="s">
-        <v>92</v>
-      </c>
-      <c r="I7" t="s">
-        <v>93</v>
-      </c>
-    </row>
-    <row r="8" spans="2:10">
-      <c r="B8" t="s">
-        <v>94</v>
-      </c>
-      <c r="C8" t="s">
-        <v>32</v>
-      </c>
-      <c r="E8" t="s">
-        <v>95</v>
-      </c>
-      <c r="H8" t="s">
-        <v>96</v>
-      </c>
-      <c r="I8" t="s">
-        <v>89</v>
-      </c>
-      <c r="J8" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="9" spans="2:9">
-      <c r="B9" t="s">
-        <v>98</v>
-      </c>
-      <c r="C9" t="s">
-        <v>36</v>
-      </c>
-      <c r="E9" t="s">
-        <v>99</v>
-      </c>
-      <c r="H9" t="s">
-        <v>100</v>
-      </c>
-      <c r="I9" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="10" spans="2:9">
-      <c r="B10" t="s">
-        <v>102</v>
-      </c>
-      <c r="C10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E10" t="s">
-        <v>103</v>
-      </c>
-      <c r="H10" t="s">
-        <v>104</v>
-      </c>
-      <c r="I10" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="11" spans="2:9">
-      <c r="B11" t="s">
-        <v>106</v>
-      </c>
-      <c r="C11" t="s">
-        <v>39</v>
-      </c>
-      <c r="E11" t="s">
-        <v>107</v>
-      </c>
-      <c r="H11" t="s">
-        <v>104</v>
-      </c>
-      <c r="I11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="12" spans="2:6">
-      <c r="B12" t="s">
-        <v>109</v>
-      </c>
-      <c r="C12" t="s">
-        <v>39</v>
-      </c>
-      <c r="E12" t="s">
-        <v>110</v>
-      </c>
-      <c r="F12" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="13" spans="2:9">
-      <c r="B13" t="s">
-        <v>112</v>
-      </c>
-      <c r="C13" t="s">
-        <v>39</v>
-      </c>
-      <c r="D13" t="s">
-        <v>109</v>
-      </c>
-      <c r="E13" t="s">
-        <v>113</v>
-      </c>
-      <c r="H13" t="s">
-        <v>104</v>
-      </c>
-      <c r="I13" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="14" spans="2:6">
-      <c r="B14" t="s">
-        <v>115</v>
-      </c>
-      <c r="C14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D14" t="s">
-        <v>109</v>
-      </c>
-      <c r="E14" t="s">
-        <v>116</v>
-      </c>
-      <c r="F14" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="15" spans="2:9">
-      <c r="B15" t="s">
-        <v>118</v>
-      </c>
-      <c r="C15" t="s">
-        <v>42</v>
-      </c>
-      <c r="E15" t="s">
-        <v>119</v>
-      </c>
-      <c r="H15" t="s">
-        <v>120</v>
-      </c>
-      <c r="I15" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="16" spans="2:9">
-      <c r="B16" t="s">
-        <v>122</v>
-      </c>
-      <c r="C16" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" t="s">
-        <v>123</v>
-      </c>
-      <c r="H16" t="s">
-        <v>81</v>
-      </c>
-      <c r="I16" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="17" spans="2:10">
-      <c r="B17" t="s">
-        <v>125</v>
-      </c>
-      <c r="C17" t="s">
-        <v>49</v>
-      </c>
-      <c r="E17" t="s">
-        <v>126</v>
-      </c>
-      <c r="H17" t="s">
-        <v>96</v>
-      </c>
-      <c r="I17" t="s">
-        <v>89</v>
-      </c>
-      <c r="J17" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="18" spans="2:9">
-      <c r="B18" t="s">
-        <v>127</v>
-      </c>
-      <c r="C18" t="s">
-        <v>52</v>
-      </c>
-      <c r="E18" t="s">
-        <v>128</v>
-      </c>
-      <c r="H18" t="s">
-        <v>81</v>
-      </c>
-      <c r="I18" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="19" spans="2:9">
-      <c r="B19" t="s">
-        <v>130</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" t="s">
-        <v>131</v>
-      </c>
-      <c r="H19" t="s">
-        <v>81</v>
-      </c>
-      <c r="I19" t="s">
-        <v>132</v>
+        <v>44</v>
+      </c>
+      <c r="K3" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/event.xlsx
+++ b/GourmetProject/GameConfig/Datas/event.xlsx
@@ -1,336 +1,178 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="16760" activeTab="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowHeight="16760" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="event" sheetId="1" r:id="rId1"/>
-    <sheet name="event_option" sheetId="2" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event_option" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <definedNames/>
+  <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="45">
-  <si>
-    <t>##var</t>
-  </si>
-  <si>
-    <t>id</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>desc</t>
-  </si>
-  <si>
-    <t>eventType</t>
-  </si>
-  <si>
-    <t>preconditions</t>
-  </si>
-  <si>
-    <t>weight</t>
-  </si>
-  <si>
-    <t>repeatable</t>
-  </si>
-  <si>
-    <t>bgSprite</t>
-  </si>
-  <si>
-    <t>##comment</t>
-  </si>
-  <si>
-    <t>事件ID</t>
-  </si>
-  <si>
-    <t>事件名称</t>
-  </si>
-  <si>
-    <t>事件描述(初始/根页正文)</t>
-  </si>
-  <si>
-    <t>事件分类(Event/Reward/Negative,决定被哪种行动 roll)</t>
-  </si>
-  <si>
-    <t>出现前置条件</t>
-  </si>
-  <si>
-    <t>随机权重</t>
-  </si>
-  <si>
-    <t>是否可重复(false 命中后本局不再出)</t>
-  </si>
-  <si>
-    <t>事件背景 Sprite(Resources 路径,空=默认占位)</t>
-  </si>
-  <si>
-    <t>##type</t>
-  </si>
-  <si>
-    <t>string</t>
-  </si>
-  <si>
-    <t>ActionBehavior</t>
-  </si>
-  <si>
-    <t>float</t>
-  </si>
-  <si>
-    <t>bool</t>
-  </si>
-  <si>
-    <t>eventId</t>
-  </si>
-  <si>
-    <t>parentId</t>
-  </si>
-  <si>
-    <t>text</t>
-  </si>
-  <si>
-    <t>resultText</t>
-  </si>
-  <si>
-    <t>condition</t>
-  </si>
-  <si>
-    <t>*effectTypes</t>
-  </si>
-  <si>
-    <t>*effectValues</t>
-  </si>
-  <si>
-    <t>*effectParams</t>
-  </si>
-  <si>
-    <t>repeatSelf</t>
-  </si>
-  <si>
-    <t>选项ID</t>
-  </si>
-  <si>
-    <t>所属事件ID→event.id</t>
-  </si>
-  <si>
-    <t>父选项ID→event_option.id(空=根页选项)</t>
-  </si>
-  <si>
-    <t>选项文本(按钮)</t>
-  </si>
-  <si>
-    <t>选中后的结果/子页正文(有子选项时作子页正文;空则回退效果反馈)</t>
-  </si>
-  <si>
-    <t>选项前置条件(空=恒可见,复用行动前置语法)</t>
-  </si>
-  <si>
-    <t>效果类型列表(多效果多行,续行前导列留空)</t>
-  </si>
-  <si>
-    <t>效果数值列表(与类型逐行对齐)</t>
-  </si>
-  <si>
-    <t>效果参数列表(与类型逐行对齐,可空)</t>
-  </si>
-  <si>
-    <t>是否可在结果页重复选择本选项(false=否)</t>
-  </si>
-  <si>
-    <t>list,EffectType</t>
-  </si>
-  <si>
-    <t>list,float</t>
-  </si>
-  <si>
-    <t>list,string</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
   <fonts count="20">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u val="single"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="33">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -631,153 +473,153 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="32" borderId="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="7" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="8" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="9" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="13" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="32" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -831,11 +673,74 @@
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -1122,239 +1027,1921 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:I3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
-    <col min="2" max="2" width="11.2307692307692" customWidth="1"/>
-    <col min="3" max="3" width="10.3076923076923" customWidth="1"/>
-    <col min="4" max="4" width="49.0769230769231" customWidth="1"/>
-    <col min="5" max="5" width="57.9230769230769" customWidth="1"/>
-    <col min="6" max="6" width="15.1538461538462" customWidth="1"/>
-    <col min="7" max="7" width="10.3076923076923" customWidth="1"/>
-    <col min="8" max="8" width="38.6923076923077" customWidth="1"/>
+    <col width="13.0769230769231" customWidth="1" min="1" max="1"/>
+    <col width="11.2307692307692" customWidth="1" min="2" max="2"/>
+    <col width="10.3076923076923" customWidth="1" min="3" max="3"/>
+    <col width="49.0769230769231" customWidth="1" min="4" max="4"/>
+    <col width="57.9230769230769" customWidth="1" min="5" max="5"/>
+    <col width="15.1538461538462" customWidth="1" min="6" max="6"/>
+    <col width="10.3076923076923" customWidth="1" min="7" max="7"/>
+    <col width="38.6923076923077" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>name</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>desc</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>eventType</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>preconditions</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>weight</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>repeatable</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>bgSprite</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>事件ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>事件名称</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>事件描述(初始/根页正文)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>事件分类(Event/Reward/Negative,决定被哪种行动 roll)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>出现前置条件</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>随机权重</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>是否可重复(false 命中后本局不再出)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>事件背景 Sprite(Resources 路径,空=默认占位)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ActionBehavior</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>float</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ev_midnight_tasting</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>深夜试吃摊</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>行动轴进入夜间事件节点时，一个试菜摊主拿出刚调好的风味样品，邀请你把它放进本周菜谱。</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>10</v>
-      </c>
-      <c r="C2" t="s">
-        <v>11</v>
-      </c>
-      <c r="D2" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" t="s">
-        <v>13</v>
-      </c>
-      <c r="F2" t="s">
-        <v>14</v>
-      </c>
-      <c r="G2" t="s">
-        <v>15</v>
-      </c>
-      <c r="H2" t="s">
-        <v>16</v>
-      </c>
-      <c r="I2" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>20</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>21</v>
-      </c>
-      <c r="H3" t="s">
-        <v>22</v>
-      </c>
-      <c r="I3" t="s">
-        <v>19</v>
+      <c r="H4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>ev_ancestral_recipe_page</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>祖传菜谱残页</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>你得到一页油渍斑驳的菜谱残页，上面记录的不是固定菜品，而是一组菜品线索。</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ev_table_carpenter</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>拼桌木匠</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>一个木匠正在修补餐桌碎片，愿意把边角料拼进你的餐桌。</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>ev_kitchen_god_statue</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>食神像</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>旧街尽头有一座食神像，贡品被摆在不同材质的餐桌碎片上。</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>ev_crossroad_sign</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>岔路招牌</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>行动轴前方出现会旋转的招牌，可以把本周剩余节奏导向不同收益类型。</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>ev_delivery_order</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>限时外卖单</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>外卖箱上的计时器开始倒数，下一场美食挑战具有更高的目标分。</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ev_black_market_advance</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>黑市预支券</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>黑市商人递来预支券，允许你提前拿走未来几次奖励的一部分。</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>ev_wishing_casserole_i</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>许愿砂锅I</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>砂锅中有着粘稠的白色汤汁，旁边写着“投入珍贵之物可以获得奖励”</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>ev_wishing_casserole_ii</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>许愿砂锅II</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>砂锅中有着粘稠的黑色汤汁，旁边写着“投入珍贵之物可以获得奖励”</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Event</t>
+        </is>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
-  <dimension ref="A1:K3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="2"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:K46"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="9" defaultRowHeight="16.8" outlineLevelRow="2"/>
   <cols>
-    <col min="1" max="1" width="13.0769230769231" customWidth="1"/>
-    <col min="2" max="2" width="19.8461538461538" customWidth="1"/>
-    <col min="3" max="3" width="23.2307692307692" customWidth="1"/>
-    <col min="4" max="4" width="43.6153846153846" customWidth="1"/>
-    <col min="5" max="5" width="27.3076923076923" customWidth="1"/>
-    <col min="6" max="6" width="71.6153846153846" customWidth="1"/>
-    <col min="7" max="7" width="47.7692307692308" customWidth="1"/>
-    <col min="8" max="8" width="46.1538461538462" customWidth="1"/>
-    <col min="9" max="9" width="33.5384615384615" customWidth="1"/>
-    <col min="10" max="10" width="38.8461538461538" customWidth="1"/>
+    <col width="13.0769230769231" customWidth="1" min="1" max="1"/>
+    <col width="19.8461538461538" customWidth="1" min="2" max="2"/>
+    <col width="23.2307692307692" customWidth="1" min="3" max="3"/>
+    <col width="43.6153846153846" customWidth="1" min="4" max="4"/>
+    <col width="27.3076923076923" customWidth="1" min="5" max="5"/>
+    <col width="71.6153846153846" customWidth="1" min="6" max="6"/>
+    <col width="47.7692307692308" customWidth="1" min="7" max="7"/>
+    <col width="46.1538461538462" customWidth="1" min="8" max="8"/>
+    <col width="33.5384615384615" customWidth="1" min="9" max="9"/>
+    <col width="38.8461538461538" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
-      <c r="A1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s">
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>##var</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>id</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>eventId</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>parentId</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>resultText</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>condition</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>*effectTypes</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>*effectValues</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>*effectParams</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>repeatSelf</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>##comment</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>选项ID</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>所属事件ID→event.id</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>父选项ID→event_option.id(空=根页选项)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>选项文本(按钮)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>选中后的结果/子页正文(有子选项时作子页正文;空则回退效果反馈)</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>选项前置条件(空=恒可见,复用行动前置语法)</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>效果类型列表(多效果多行,续行前导列留空)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>效果数值列表(与类型逐行对齐)</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>效果参数列表(与类型逐行对齐,可空)</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>是否可在结果页重复选择本选项(false=否)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>##type</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>string</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>list,EffectType</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>list,float</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>list,string</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>opt_midnight_sample</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ev_midnight_tasting</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>试吃样品</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>摊主把新调的风味塞进你的菜谱。</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>minGold:20</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>GainGold</t>
+        </is>
+      </c>
+      <c r="I4" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>AddRandomRecipeFlavor</t>
+        </is>
+      </c>
+      <c r="I5" t="n">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
-        <v>23</v>
-      </c>
-      <c r="D1" t="s">
-        <v>24</v>
-      </c>
-      <c r="E1" t="s">
-        <v>25</v>
-      </c>
-      <c r="F1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G1" t="s">
-        <v>27</v>
-      </c>
-      <c r="H1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I1" t="s">
-        <v>29</v>
-      </c>
-      <c r="J1" t="s">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>opt_midnight_menu</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ev_midnight_tasting</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>帮摊主整理菜单</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>这需要打开菜谱选择目标，后续接入 UI 后再实际删除。</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>minGold:20</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>GainGold</t>
+        </is>
+      </c>
+      <c r="I6" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>UiTodo</t>
+        </is>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>TODO: 打开菜谱选择并删除 1 道菜。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>opt_midnight_leave</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ev_midnight_tasting</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>赶路离开</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>你没有停留，继续赶路。</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>opt_recipe_page_cover</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ev_ancestral_recipe_page</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>抄写扉页部分</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>你记下了菜品线索，后续菜品奖励更容易变好。</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>AddHiddenScoreOffset</t>
+        </is>
+      </c>
+      <c r="I9" t="n">
+        <v>5</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Dish</t>
+        </is>
+      </c>
+      <c r="K9" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>opt_recipe_page_body</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>ev_ancestral_recipe_page</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>抄写正文部分</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>你获得了一组新的菜品线索。</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>EnqueueDishChoice</t>
+        </is>
+      </c>
+      <c r="I10" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>dish_choice_3|祖传菜谱残页</t>
+        </is>
+      </c>
+      <c r="K10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>opt_recipe_page_sell</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>ev_ancestral_recipe_page</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>卖给商店老板</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>商店老板收下残页，付给你一袋金币。</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>GainGold</t>
+        </is>
+      </c>
+      <c r="I11" t="n">
+        <v>40</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>opt_carpenter_wood</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>ev_table_carpenter</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>选择木料</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>木匠递给你一张木料采购单。</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>GainSpecificItem</t>
+        </is>
+      </c>
+      <c r="I12" t="n">
+        <v>1</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>lay_wood</t>
+        </is>
+      </c>
+      <c r="K12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>opt_carpenter_stone</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>ev_table_carpenter</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>选择石料</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>木匠递给你一张石料采购单。</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>GainSpecificItem</t>
+        </is>
+      </c>
+      <c r="I13" t="n">
+        <v>1</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>lay_stone</t>
+        </is>
+      </c>
+      <c r="K13" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>opt_carpenter_metal</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>ev_table_carpenter</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>选择金属料</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>木匠递给你一张金属采购单。</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>GainSpecificItem</t>
+        </is>
+      </c>
+      <c r="I14" t="n">
+        <v>1</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>lay_metal</t>
+        </is>
+      </c>
+      <c r="K14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>opt_statue_gold</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>ev_kitchen_god_statue</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>供奉金币</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>神像前的贡盘轻轻一震。</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>minGold:30</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>GainGold</t>
+        </is>
+      </c>
+      <c r="I15" t="n">
+        <v>-30</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>GainItem</t>
+        </is>
+      </c>
+      <c r="I16" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>passive_choice_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>opt_statue_dish</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>ev_kitchen_god_statue</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>供奉一道菜</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>供奉目标需要菜谱选择 UI，后续接入后再实际移除菜品。</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>UiTodo</t>
+        </is>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>TODO: 打开菜谱选择并移除 1 道菜。</t>
+        </is>
+      </c>
+      <c r="K17" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>GainItem</t>
+        </is>
+      </c>
+      <c r="I18" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>passive_choice_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>opt_statue_steal</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ev_kitchen_god_statue</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>偷走贡品</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>你抱走贡品，附近商店很快听说了这件事。</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>GainGold</t>
+        </is>
+      </c>
+      <c r="I19" t="n">
+        <v>100</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>GainItem</t>
+        </is>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>active_grant_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>AddShopPricePct</t>
+        </is>
+      </c>
+      <c r="I21" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>opt_sign_food_street</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>ev_crossroad_sign</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>指向美食街</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>招牌指向灯火通明的美食街，后续食物奖励更容易变好。</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>AddHiddenScoreOffset</t>
+        </is>
+      </c>
+      <c r="I22" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>Dish</t>
+        </is>
+      </c>
+      <c r="K22" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>opt_sign_secondhand</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>ev_crossroad_sign</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>指向旧货巷</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>招牌指向堆满旧货的小巷，后续道具奖励更容易变好。</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>AddHiddenScoreOffset</t>
+        </is>
+      </c>
+      <c r="I23" t="n">
+        <v>5</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>PassiveItem</t>
+        </is>
+      </c>
+      <c r="K23" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>opt_sign_mall</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>ev_crossroad_sign</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>指向商场</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>招牌指向商场，后续金币收益提高。</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>AddHiddenScoreOffset</t>
+        </is>
+      </c>
+      <c r="I24" t="n">
+        <v>5</v>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>Gold</t>
+        </is>
+      </c>
+      <c r="K24" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>opt_delivery_normal</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>ev_delivery_order</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>接普通单</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>你接下普通外卖单，下一场美食挑战目标略有提高。</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>AddNextFoodTargetOffset</t>
+        </is>
+      </c>
+      <c r="I25" t="n">
+        <v>5</v>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>AddNextMealGold</t>
+        </is>
+      </c>
+      <c r="I26" t="n">
         <v>30</v>
       </c>
-      <c r="K1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
-      <c r="A2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B2" t="s">
-        <v>32</v>
-      </c>
-      <c r="C2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E2" t="s">
-        <v>35</v>
-      </c>
-      <c r="F2" t="s">
-        <v>36</v>
-      </c>
-      <c r="G2" t="s">
-        <v>37</v>
-      </c>
-      <c r="H2" t="s">
-        <v>38</v>
-      </c>
-      <c r="I2" t="s">
-        <v>39</v>
-      </c>
-      <c r="J2" t="s">
-        <v>40</v>
-      </c>
-      <c r="K2" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
-      <c r="A3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B3" t="s">
-        <v>19</v>
-      </c>
-      <c r="C3" t="s">
-        <v>19</v>
-      </c>
-      <c r="D3" t="s">
-        <v>19</v>
-      </c>
-      <c r="E3" t="s">
-        <v>19</v>
-      </c>
-      <c r="F3" t="s">
-        <v>19</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
-      </c>
-      <c r="H3" t="s">
-        <v>42</v>
-      </c>
-      <c r="I3" t="s">
-        <v>43</v>
-      </c>
-      <c r="J3" t="s">
-        <v>44</v>
-      </c>
-      <c r="K3" t="s">
-        <v>22</v>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>opt_delivery_luxury</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>ev_delivery_order</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>接豪华单</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>你接下豪华外卖单，下一场美食挑战目标明显提高。</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>AddNextFoodTargetOffset</t>
+        </is>
+      </c>
+      <c r="I27" t="n">
+        <v>10</v>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>AddNextMealGold</t>
+        </is>
+      </c>
+      <c r="I28" t="n">
+        <v>80</v>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>opt_delivery_reject</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>ev_delivery_order</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>拒接</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>你合上外卖箱，没有接单。</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>opt_advance_passive</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>ev_black_market_advance</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>预支被动道具</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>你提前拿走一个被动道具，未来奖励质量被压低。</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>GainItem</t>
+        </is>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>passive_choice_1</t>
+        </is>
+      </c>
+      <c r="K30" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>AddHiddenScoreOffset</t>
+        </is>
+      </c>
+      <c r="I31" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>opt_advance_fragment</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>ev_black_market_advance</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>预支餐桌碎片</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>你提前拿走一包餐桌碎片，未来奖励质量被压低。</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>GrantFragmentPack</t>
+        </is>
+      </c>
+      <c r="I32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>fragment_choice_3</t>
+        </is>
+      </c>
+      <c r="K32" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>AddHiddenScoreOffset</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>-10</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Reward</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>opt_advance_active</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>ev_black_market_advance</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>预支主动道具</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>你提前拿走一个主动道具，后续两次奖励选择少 1 个选项。</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>GainItem</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>active_grant_1</t>
+        </is>
+      </c>
+      <c r="K34" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>AddChoiceCountPenalty</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>2</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>-1</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>opt_casserole_i_food</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>ev_wishing_casserole_i</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>献上一个美食</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>砂锅吞下随机贡品后吐出几枚金币。</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>hasRecipeDish</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>RemoveRandomRecipeDish</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>1</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>GainGold</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>20</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>opt_casserole_i_flavored</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>ev_wishing_casserole_i</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>献上一个独具风味的美食</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>砂锅吞下一道带风味的美食，只是汤汁颜色变深了一点。</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>hasFlavoredRecipeDish</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>RemoveRandomRecipeDish</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>1</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>flavored</t>
+        </is>
+      </c>
+      <c r="K38" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>IncrementEventCounter</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>3</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>wishing_casserole|ev_wishing_casserole_ii</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>opt_casserole_i_gold</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>ev_wishing_casserole_i</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>献上少量金币</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>砂锅吐出一个普通的被动道具。</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>minGold:20</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>GainGold</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>-20</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>GainItem</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>passive_choice_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>opt_casserole_ii_flavored</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>ev_wishing_casserole_ii</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>献上一个独具风味的美食</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>黑汤翻涌，吐出三份带有风味的美食。</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>hasFlavoredRecipeDish</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>RemoveRandomRecipeDish</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>1</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>flavored</t>
+        </is>
+      </c>
+      <c r="K42" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>GainRandomFlavoredDishes</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>3</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>flavored_dish_3</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>opt_casserole_ii_gold</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>ev_wishing_casserole_ii</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>献上一切金币</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>所有金币沉入锅底，砂锅吐出一件传说级贡品。</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>minGold:1</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>LoseAllGold</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>GainLegendaryItem</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>1</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>legendary_choice_1</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>opt_casserole_ii_actives</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>ev_wishing_casserole_ii</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>献上主动道具</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>主动道具被黑汤吞没，金币从锅沿滚落。</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>RemoveActiveItemsForGold</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>100</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/GourmetProject/GameConfig/Datas/event.xlsx
+++ b/GourmetProject/GameConfig/Datas/event.xlsx
@@ -1711,12 +1711,12 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>这需要打开菜谱选择目标，后续接入 UI 后再实际删除。</t>
+          <t>选择一道菜品后，摊主会帮你把它从菜谱中删去。</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>minGold:20</t>
+          <t>minGold:20|hasRecipeDish</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -1739,15 +1739,15 @@
     <row r="7">
       <c r="H7" t="inlineStr">
         <is>
-          <t>UiTodo</t>
+          <t>SelectRemoveRecipeDish</t>
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>TODO: 打开菜谱选择并删除 1 道菜。</t>
+          <t>-</t>
         </is>
       </c>
     </row>
@@ -2093,20 +2093,25 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>供奉目标需要菜谱选择 UI，后续接入后再实际移除菜品。</t>
+          <t>选择一道菜品供奉给食神像。</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>hasRecipeDish</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>UiTodo</t>
+          <t>SelectRemoveRecipeDish</t>
         </is>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>TODO: 打开菜谱选择并移除 1 道菜。</t>
+          <t>-</t>
         </is>
       </c>
       <c r="K17" t="b">

--- a/GourmetProject/GameConfig/Datas/event.xlsx
+++ b/GourmetProject/GameConfig/Datas/event.xlsx
@@ -4,18 +4,31 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15160" activeTab="1"/>
+    <workbookView windowHeight="16760" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="event" sheetId="1" r:id="rId1"/>
     <sheet name="event_option" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="194">
   <si>
     <t>##var</t>
   </si>
@@ -200,9 +213,6 @@
     <t>*effectParams</t>
   </si>
   <si>
-    <t>repeatSelf</t>
-  </si>
-  <si>
     <t>选项ID</t>
   </si>
   <si>
@@ -228,9 +238,6 @@
   </si>
   <si>
     <t>效果参数列表</t>
-  </si>
-  <si>
-    <t>是否可在结果页重复选择本选项(false=否)</t>
   </si>
   <si>
     <t>list,EffectType</t>
@@ -608,7 +615,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -1859,7 +1866,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:K44"/>
+  <dimension ref="A1:J44"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.8"/>
   <cols>
     <col min="1" max="1" width="13.0769230769231" style="1" customWidth="1"/>
@@ -1872,10 +1879,11 @@
     <col min="8" max="8" width="29.5384615384615" style="1" customWidth="1"/>
     <col min="9" max="9" width="15.1538461538462" style="1" customWidth="1"/>
     <col min="10" max="10" width="38.8461538461538" style="1" customWidth="1"/>
-    <col min="11" max="16384" width="9" style="1" customWidth="1"/>
+    <col min="11" max="16383" width="9" style="1" customWidth="1"/>
+    <col min="16384" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11">
+    <row r="1" spans="1:10">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1906,46 +1914,40 @@
       <c r="J1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="K1" s="1" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:11">
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>61</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>67</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="J2" s="1" t="s">
         <v>69</v>
       </c>
-      <c r="J2" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="K2" s="1" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11">
+    </row>
+    <row r="3" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>18</v>
       </c>
@@ -1968,896 +1970,812 @@
         <v>19</v>
       </c>
       <c r="H3" s="1" t="s">
+        <v>70</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="J3" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="I3" s="1" t="s">
+    </row>
+    <row r="4" spans="2:10">
+      <c r="B4" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="K3" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="2:11">
-      <c r="B4" s="1" t="s">
-        <v>75</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="H4" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="H4" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="I4" s="1">
         <v>1</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K4" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="5" spans="2:10">
       <c r="B5" s="1" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E5" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>82</v>
-      </c>
-      <c r="G5" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="I5" s="1">
         <v>1</v>
       </c>
       <c r="J5" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K5" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="6" spans="2:10">
       <c r="B6" s="1" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>23</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="H6" s="1" t="s">
         <v>86</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="H6" s="1" t="s">
-        <v>88</v>
       </c>
       <c r="I6" s="1">
         <v>0</v>
       </c>
       <c r="J6" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K6" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="7" spans="2:10">
       <c r="B7" s="1" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E7" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="H7" s="1" t="s">
         <v>90</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>91</v>
-      </c>
-      <c r="H7" s="1" t="s">
-        <v>92</v>
       </c>
       <c r="I7" s="1">
         <v>5</v>
       </c>
       <c r="J7" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="K7" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="2:11">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="8" spans="2:10">
       <c r="B8" s="1" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E8" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>94</v>
+      </c>
+      <c r="H8" s="1" t="s">
         <v>95</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="H8" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="I8" s="1">
         <v>3</v>
       </c>
       <c r="J8" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="K8" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:11">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="9" spans="2:10">
       <c r="B9" s="1" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="H9" s="1" t="s">
         <v>100</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="H9" s="1" t="s">
-        <v>102</v>
       </c>
       <c r="I9" s="1">
         <v>40</v>
       </c>
       <c r="J9" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K9" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="2:11">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="10" spans="2:10">
       <c r="B10" s="1" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E10" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>103</v>
+      </c>
+      <c r="H10" s="1" t="s">
         <v>104</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="H10" s="1" t="s">
-        <v>106</v>
       </c>
       <c r="I10" s="1">
         <v>1</v>
       </c>
       <c r="J10" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="K10" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="2:11">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="11" spans="2:10">
       <c r="B11" s="1" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I11" s="1">
         <v>1</v>
       </c>
       <c r="J11" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="K11" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="2:11">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="12" spans="2:10">
       <c r="B12" s="1" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>31</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="I12" s="1">
         <v>1</v>
       </c>
       <c r="J12" s="1" t="s">
-        <v>115</v>
-      </c>
-      <c r="K12" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="2:11">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="13" spans="2:10">
       <c r="B13" s="1" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E13" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="G13" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="F13" s="1" t="s">
-        <v>118</v>
-      </c>
-      <c r="G13" s="1" t="s">
-        <v>119</v>
-      </c>
       <c r="H13" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I13" s="1">
         <v>-30</v>
       </c>
       <c r="J13" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K13" s="1" t="b">
-        <v>0</v>
+        <v>77</v>
       </c>
     </row>
     <row r="14" spans="8:10">
       <c r="H14" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I14" s="1">
         <v>0</v>
       </c>
       <c r="J14" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="15" spans="2:11">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="15" spans="2:10">
       <c r="B15" s="1" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="H15" s="1" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="I15" s="1">
         <v>1</v>
       </c>
       <c r="J15" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K15" s="1" t="b">
-        <v>0</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" spans="8:10">
       <c r="H16" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I16" s="1">
         <v>0</v>
       </c>
       <c r="J16" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="17" spans="2:10">
       <c r="B17" s="1" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>34</v>
       </c>
       <c r="E17" s="1" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="H17" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I17" s="1">
         <v>100</v>
       </c>
       <c r="J17" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K17" s="1" t="b">
-        <v>0</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" spans="8:10">
       <c r="H18" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I18" s="1">
         <v>0</v>
       </c>
       <c r="J18" s="1" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="8:10">
       <c r="H19" s="1" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="I19" s="1">
         <v>0.25</v>
       </c>
       <c r="J19" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="20" spans="2:11">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" spans="2:10">
       <c r="B20" s="1" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="H20" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I20" s="1">
         <v>3</v>
       </c>
       <c r="J20" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="K20" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="21" spans="2:10">
       <c r="B21" s="1" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E21" s="1" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H21" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I21" s="1">
         <v>3</v>
       </c>
       <c r="J21" s="1" t="s">
-        <v>136</v>
-      </c>
-      <c r="K21" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="22" spans="2:10">
       <c r="B22" s="1" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="H22" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I22" s="1">
         <v>5</v>
       </c>
       <c r="J22" s="1" t="s">
-        <v>140</v>
-      </c>
-      <c r="K22" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:11">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="23" spans="2:10">
       <c r="B23" s="1" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>40</v>
       </c>
       <c r="E23" s="1" t="s">
+        <v>140</v>
+      </c>
+      <c r="F23" s="1" t="s">
+        <v>141</v>
+      </c>
+      <c r="H23" s="1" t="s">
         <v>142</v>
-      </c>
-      <c r="F23" s="1" t="s">
-        <v>143</v>
-      </c>
-      <c r="H23" s="1" t="s">
-        <v>144</v>
       </c>
       <c r="I23" s="1">
         <v>5</v>
       </c>
       <c r="J23" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K23" s="1" t="b">
-        <v>0</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" spans="8:10">
       <c r="H24" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I24" s="1">
         <v>30</v>
       </c>
       <c r="J24" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="25" spans="2:11">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="25" spans="2:10">
       <c r="B25" s="1" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>40</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="H25" s="1" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="I25" s="1">
         <v>10</v>
       </c>
       <c r="J25" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K25" s="1" t="b">
-        <v>0</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="8:10">
       <c r="H26" s="1" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I26" s="1">
         <v>80</v>
       </c>
       <c r="J26" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="27" spans="2:11">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="27" spans="2:10">
       <c r="B27" s="1" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>40</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H27" s="1" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I27" s="1">
         <v>0</v>
       </c>
       <c r="J27" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K27" s="1" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:11">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="28" spans="2:10">
       <c r="B28" s="1" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="H28" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I28" s="1">
         <v>0</v>
       </c>
       <c r="J28" s="1" t="s">
-        <v>121</v>
-      </c>
-      <c r="K28" s="1" t="b">
-        <v>0</v>
+        <v>119</v>
       </c>
     </row>
     <row r="29" spans="8:10">
       <c r="H29" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I29" s="1">
         <v>-5</v>
       </c>
       <c r="J29" s="1" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="30" spans="2:11">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="30" spans="2:10">
       <c r="B30" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E30" s="1" t="s">
+        <v>154</v>
+      </c>
+      <c r="F30" s="1" t="s">
+        <v>155</v>
+      </c>
+      <c r="H30" s="1" t="s">
         <v>156</v>
-      </c>
-      <c r="F30" s="1" t="s">
-        <v>157</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>158</v>
       </c>
       <c r="I30" s="1">
         <v>3</v>
       </c>
       <c r="J30" s="1" t="s">
-        <v>159</v>
-      </c>
-      <c r="K30" s="1" t="b">
-        <v>0</v>
+        <v>157</v>
       </c>
     </row>
     <row r="31" spans="8:10">
       <c r="H31" s="1" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="I31" s="1">
         <v>-5</v>
       </c>
       <c r="J31" s="1" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="32" spans="2:11">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="32" spans="2:10">
       <c r="B32" s="1" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>43</v>
       </c>
       <c r="E32" s="1" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="H32" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I32" s="1">
         <v>0</v>
       </c>
       <c r="J32" s="1" t="s">
-        <v>128</v>
-      </c>
-      <c r="K32" s="1" t="b">
-        <v>0</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="8:10">
       <c r="H33" s="1" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="I33" s="1">
         <v>2</v>
       </c>
       <c r="J33" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="34" spans="2:11">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="34" spans="2:10">
       <c r="B34" s="1" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E34" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="F34" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="G34" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="H34" s="1" t="s">
         <v>167</v>
-      </c>
-      <c r="F34" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="H34" s="1" t="s">
-        <v>169</v>
       </c>
       <c r="I34" s="1">
         <v>1</v>
       </c>
       <c r="J34" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K34" s="1" t="b">
-        <v>0</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" spans="8:10">
       <c r="H35" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I35" s="1">
         <v>20</v>
       </c>
       <c r="J35" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="36" spans="2:11">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="36" spans="2:10">
       <c r="B36" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E36" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F36" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="G36" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F36" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="G36" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="H36" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I36" s="1">
         <v>1</v>
       </c>
       <c r="J36" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="K36" s="1" t="b">
-        <v>0</v>
+        <v>172</v>
       </c>
     </row>
     <row r="37" spans="8:10">
       <c r="H37" s="1" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="I37" s="1">
         <v>3</v>
       </c>
       <c r="J37" s="1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="38" spans="2:11">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="38" spans="2:10">
       <c r="B38" s="1" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E38" s="1" t="s">
+        <v>176</v>
+      </c>
+      <c r="F38" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="G38" s="1" t="s">
         <v>178</v>
       </c>
-      <c r="F38" s="1" t="s">
-        <v>179</v>
-      </c>
-      <c r="G38" s="1" t="s">
-        <v>180</v>
-      </c>
       <c r="H38" s="1" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="I38" s="1">
         <v>-20</v>
       </c>
       <c r="J38" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K38" s="1" t="b">
-        <v>0</v>
+        <v>77</v>
       </c>
     </row>
     <row r="39" spans="8:10">
       <c r="H39" s="1" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="I39" s="1">
         <v>0</v>
       </c>
       <c r="J39" s="1" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="40" spans="2:11">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="40" spans="2:10">
       <c r="B40" s="1" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E40" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F40" s="1" t="s">
+        <v>180</v>
+      </c>
+      <c r="G40" s="1" t="s">
         <v>171</v>
       </c>
-      <c r="F40" s="1" t="s">
-        <v>182</v>
-      </c>
-      <c r="G40" s="1" t="s">
-        <v>173</v>
-      </c>
       <c r="H40" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="I40" s="1">
         <v>1</v>
       </c>
       <c r="J40" s="1" t="s">
-        <v>174</v>
-      </c>
-      <c r="K40" s="1" t="b">
-        <v>0</v>
+        <v>172</v>
       </c>
     </row>
     <row r="41" spans="8:10">
       <c r="H41" s="1" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="I41" s="1">
         <v>3</v>
       </c>
       <c r="J41" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="42" spans="2:11">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="42" spans="2:10">
       <c r="B42" s="1" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E42" s="1" t="s">
+        <v>184</v>
+      </c>
+      <c r="F42" s="1" t="s">
+        <v>185</v>
+      </c>
+      <c r="G42" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="H42" s="1" t="s">
         <v>187</v>
-      </c>
-      <c r="G42" s="1" t="s">
-        <v>188</v>
-      </c>
-      <c r="H42" s="1" t="s">
-        <v>189</v>
       </c>
       <c r="I42" s="1">
         <v>0</v>
       </c>
       <c r="J42" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K42" s="1" t="b">
-        <v>0</v>
+        <v>77</v>
       </c>
     </row>
     <row r="43" spans="8:10">
       <c r="H43" s="1" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="I43" s="1">
         <v>1</v>
       </c>
       <c r="J43" s="1" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="44" spans="2:11">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="44" spans="2:10">
       <c r="B44" s="1" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E44" s="1" t="s">
+        <v>191</v>
+      </c>
+      <c r="F44" s="1" t="s">
+        <v>192</v>
+      </c>
+      <c r="H44" s="1" t="s">
         <v>193</v>
-      </c>
-      <c r="F44" s="1" t="s">
-        <v>194</v>
-      </c>
-      <c r="H44" s="1" t="s">
-        <v>195</v>
       </c>
       <c r="I44" s="1">
         <v>100</v>
       </c>
       <c r="J44" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="K44" s="1" t="b">
-        <v>0</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>

--- a/GourmetProject/GameConfig/Datas/event.xlsx
+++ b/GourmetProject/GameConfig/Datas/event.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowHeight="15340"/>
+    <workbookView windowHeight="15300"/>
   </bookViews>
   <sheets>
     <sheet name="event" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
     <t>desc</t>
   </si>
   <si>
-    <t>eventType</t>
+    <t>eventTypes</t>
   </si>
   <si>
     <t>preconditions</t>
@@ -59,7 +59,7 @@
     <t>事件描述(初始/根页正文)</t>
   </si>
   <si>
-    <t>事件分类(Event/Reward/Negative,决定被哪种行动 roll)</t>
+    <t>事件分类列表（|分隔；首项决定权重/保底，其余项也加入对应行动池）</t>
   </si>
   <si>
     <t>出现前置条件</t>
@@ -83,7 +83,7 @@
     <t>string</t>
   </si>
   <si>
-    <t>ActionBehavior</t>
+    <t>(list#sep=|),ActionBehavior</t>
   </si>
   <si>
     <t>float</t>
@@ -113,7 +113,7 @@
     <t>你得到一页油渍斑驳的菜谱残页，上面记录的不是固定菜品，而是一组菜品线索。</t>
   </si>
   <si>
-    <t>Reward</t>
+    <t>Event|Reward</t>
   </si>
   <si>
     <t>ev_table_carpenter</t>

--- a/GourmetProject/GameConfig/Datas/event.xlsx
+++ b/GourmetProject/GameConfig/Datas/event.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event" sheetId="1" r:id="R262a844f347948a6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event_option" sheetId="2" r:id="Rb307fca2de794621"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event" sheetId="1" r:id="R1cc325f9b60947e8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event_option" sheetId="2" r:id="R38ea2e423d764c4b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -125,21 +125,12 @@
     <x:t xml:space="preserve">深夜试吃摊</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">行动轴进入夜间事件节点时，一个试菜摊主拿出刚调好的风味样品，邀请你把它放进本周菜谱。</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Event</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">ev_ancestral_recipe_page</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">祖传菜谱残页</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">你得到一页油渍斑驳的菜谱残页，上面记录的不是固定菜品，而是一组菜品线索。</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Event|Reward</x:t>
   </x:si>
   <x:si>
@@ -149,36 +140,24 @@
     <x:t xml:space="preserve">拼桌木匠</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">一个木匠正在修补餐桌碎片，愿意把边角料拼进你的餐桌。</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">ev_kitchen_god_statue</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">食神像</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">旧街尽头有一座食神像，贡品被摆在不同材质的餐桌碎片上。</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">ev_crossroad_sign</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">岔路招牌</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">行动轴前方出现会旋转的招牌，可以把本周剩余节奏导向不同收益类型。</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">ev_delivery_order</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">限时外卖单</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">外卖箱上的计时器开始倒数，下一场美食挑战具有更高的目标分。</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">ev_black_market_advance</x:t>
   </x:si>
   <x:si>
@@ -239,9 +218,6 @@
     <x:t xml:space="preserve">抽奖机</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">一个华丽的机器，投入金币有概率获得格子奖励</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">Slot</x:t>
   </x:si>
   <x:si>
@@ -320,9 +296,6 @@
     <x:t xml:space="preserve">试吃样品</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">摊主把新调的风味塞进你的菜谱</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">AddRandomRecipeFlavor</x:t>
   </x:si>
   <x:si>
@@ -332,12 +305,6 @@
     <x:t xml:space="preserve">opt_midnight_menu</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">帮摊主整理菜单</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">选择一道食物后，摊主会帮你把它从菜谱中删去</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">hasRecipeDish</x:t>
   </x:si>
   <x:si>
@@ -377,15 +344,9 @@
     <x:t xml:space="preserve">抄写正文部分</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">你获得了一个食物</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">EnqueueDishChoice</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">dish_choice_3|祖传菜谱残页</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">opt_recipe_page_sell</x:t>
   </x:si>
   <x:si>
@@ -440,9 +401,6 @@
     <x:t xml:space="preserve">opt_statue_gold</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">供奉30金币</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">神像前的贡盘轻轻一震</x:t>
   </x:si>
   <x:si>
@@ -458,12 +416,6 @@
     <x:t xml:space="preserve">opt_statue_dish</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">供奉一道菜</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">选择一道食物供奉给食神像</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">opt_statue_steal</x:t>
   </x:si>
   <x:si>
@@ -518,9 +470,6 @@
     <x:t xml:space="preserve">接普通单</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">你接下普通外卖单，下一场美食挑战目标略有提高</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">AddNextFoodTargetOffset</x:t>
   </x:si>
   <x:si>
@@ -533,9 +482,6 @@
     <x:t xml:space="preserve">接豪华单</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">你接下豪华外卖单，下一场美食挑战目标明显提高</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">opt_delivery_reject</x:t>
   </x:si>
   <x:si>
@@ -548,21 +494,9 @@
     <x:t xml:space="preserve">opt_advance_passive</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">预支被动道具</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">你提前拿走一个被动道具，相关的运气降低了</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">opt_advance_fragment</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">预支餐桌碎片</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">你提前拿走一包餐桌碎片，相关的运气降低了</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">GrantFragmentPack</x:t>
   </x:si>
   <x:si>
@@ -575,12 +509,6 @@
     <x:t xml:space="preserve">opt_advance_active</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">预支主动道具</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">你提前拿走一个主动道具，后续2次奖励选择少 1 个选项</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">AddChoiceCountPenalty</x:t>
   </x:si>
   <x:si>
@@ -590,9 +518,6 @@
     <x:t xml:space="preserve">opt_casserole_i_food</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">献上一个美食</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">砂锅吞下随机贡品后，吐出几枚金币</x:t>
   </x:si>
   <x:si>
@@ -602,12 +527,6 @@
     <x:t xml:space="preserve">opt_casserole_i_flavored</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">献上一个独具风味的美食</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">砂锅吞下1个带风味的美食，只是汤汁颜色变深了一点</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">hasFlavoredRecipeDish</x:t>
   </x:si>
   <x:si>
@@ -626,18 +545,12 @@
     <x:t xml:space="preserve">献上少量金币</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">砂锅吐出1个被动道具</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">minGold:20</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">opt_casserole_ii_flavored</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">黑汤翻涌，吐出3个带有风味的美食</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">GainRandomFlavoredDishes</x:t>
   </x:si>
   <x:si>
@@ -650,9 +563,6 @@
     <x:t xml:space="preserve">献上一切金币</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">所有金币沉入锅底，砂锅吐出1个珍贵道具</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">minGold:1</x:t>
   </x:si>
   <x:si>
@@ -668,19 +578,10 @@
     <x:t xml:space="preserve">opt_casserole_ii_actives</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">献上主动道具</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">主动道具被黑汤吞没，金币从锅沿滚落</x:t>
-  </x:si>
-  <x:si>
     <x:t xml:space="preserve">RemoveActiveItemsForGold</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">opt_roast_meat_pork</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">吃猪肉，-30金币</x:t>
   </x:si>
   <x:si>
     <x:t xml:space="preserve">猪肉好香好美味</x:t>
@@ -1901,11 +1802,11 @@
       <x:c r="C4" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="D4" t="s">
+      <x:c r="D4" t="str">
+        <x:v>时间轴进入夜间事件节点时，一个试菜摊主拿出刚调好的风味样品，邀请你把它放进本周食谱。</x:v>
+      </x:c>
+      <x:c r="E4" t="s">
         <x:v>38</x:v>
-      </x:c>
-      <x:c r="E4" t="s">
-        <x:v>39</x:v>
       </x:c>
       <x:c r="G4">
         <x:v>1</x:v>
@@ -1916,16 +1817,16 @@
     </x:row>
     <x:row r="5">
       <x:c r="B5" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C5" t="str">
+        <x:v>祖传食谱残页</x:v>
+      </x:c>
+      <x:c r="D5" t="str">
+        <x:v>你得到一页油渍斑驳的食谱残页，上面记录的不是固定食物，而是一组食物线索。</x:v>
+      </x:c>
+      <x:c r="E5" t="s">
         <x:v>40</x:v>
-      </x:c>
-      <x:c r="C5" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="D5" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="E5" t="s">
-        <x:v>43</x:v>
       </x:c>
       <x:c r="G5">
         <x:v>1</x:v>
@@ -1936,16 +1837,16 @@
     </x:row>
     <x:row r="6">
       <x:c r="B6" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C6" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="D6" t="s">
-        <x:v>46</x:v>
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D6" t="str">
+        <x:v>一个木匠正在修补餐桌格，愿意把边角料拼进你的餐桌。</x:v>
       </x:c>
       <x:c r="E6" t="s">
-        <x:v>43</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G6">
         <x:v>1</x:v>
@@ -1956,16 +1857,16 @@
     </x:row>
     <x:row r="7">
       <x:c r="B7" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C7" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="D7" t="s">
-        <x:v>49</x:v>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D7" t="str">
+        <x:v>旧街尽头有一座食神像，贡品被摆在不同材质的餐桌格上。</x:v>
       </x:c>
       <x:c r="E7" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G7">
         <x:v>1</x:v>
@@ -1976,16 +1877,16 @@
     </x:row>
     <x:row r="8">
       <x:c r="B8" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C8" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="D8" t="s">
-        <x:v>52</x:v>
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D8" t="str">
+        <x:v>时间轴前方出现会旋转的招牌，可以把本周剩余节奏导向不同收益类型。</x:v>
       </x:c>
       <x:c r="E8" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G8">
         <x:v>1</x:v>
@@ -1996,16 +1897,16 @@
     </x:row>
     <x:row r="9">
       <x:c r="B9" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C9" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="D9" t="s">
-        <x:v>55</x:v>
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D9" t="str">
+        <x:v>外卖箱上的计时器开始倒数，下一场经营挑战具有更高的目标美味值。</x:v>
       </x:c>
       <x:c r="E9" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G9">
         <x:v>1</x:v>
@@ -2016,16 +1917,16 @@
     </x:row>
     <x:row r="10">
       <x:c r="B10" t="s">
-        <x:v>56</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C10" t="s">
-        <x:v>57</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D10" t="s">
-        <x:v>58</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E10" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G10">
         <x:v>1</x:v>
@@ -2036,16 +1937,16 @@
     </x:row>
     <x:row r="11">
       <x:c r="B11" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C11" t="s">
-        <x:v>60</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D11" t="s">
-        <x:v>61</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E11" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G11">
         <x:v>1</x:v>
@@ -2056,19 +1957,19 @@
     </x:row>
     <x:row r="12">
       <x:c r="B12" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C12" t="s">
-        <x:v>63</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D12" t="s">
-        <x:v>64</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E12" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F12" t="s">
-        <x:v>65</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G12">
         <x:v>1</x:v>
@@ -2079,16 +1980,16 @@
     </x:row>
     <x:row r="13">
       <x:c r="B13" t="s">
-        <x:v>66</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C13" t="s">
-        <x:v>67</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D13" t="s">
-        <x:v>68</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E13" t="s">
-        <x:v>39</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="G13">
         <x:v>0</x:v>
@@ -2099,16 +2000,16 @@
     </x:row>
     <x:row r="14">
       <x:c r="B14" t="s">
-        <x:v>69</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C14" t="s">
-        <x:v>70</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D14" t="s">
-        <x:v>71</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E14" t="s">
-        <x:v>72</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G14">
         <x:v>0</x:v>
@@ -2117,21 +2018,21 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J14" t="s">
-        <x:v>73</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="B15" t="s">
-        <x:v>74</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C15" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D15" t="s">
-        <x:v>76</x:v>
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D15" t="str">
+        <x:v>一个华丽的机器，投入金币有概率获得餐桌格奖励</x:v>
       </x:c>
       <x:c r="E15" t="s">
-        <x:v>77</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G15">
         <x:v>0</x:v>
@@ -2140,10 +2041,10 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="J15" t="s">
-        <x:v>78</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="K15" t="s">
-        <x:v>79</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="L15">
         <x:v>40</x:v>
@@ -2189,31 +2090,31 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="C1" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D1" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E1" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="F1" s="1" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="G1" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H1" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="I1" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="J1" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="K1" t="s">
-        <x:v>87</x:v>
+        <x:v>79</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -2221,34 +2122,34 @@
         <x:v>15</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C2" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D2" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="E2" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="I2" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="J2" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C2" s="1" t="s">
+      <x:c r="K2" t="s">
         <x:v>89</x:v>
-      </x:c>
-      <x:c r="D2" s="1" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E2" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="G2" s="1" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="H2" s="1" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="I2" s="1" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="J2" s="1" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="K2" t="s">
-        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -2274,13 +2175,13 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="H3" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="I3" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="J3" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="K3" t="s">
         <x:v>34</x:v>
@@ -2288,25 +2189,25 @@
     </x:row>
     <x:row r="4">
       <x:c r="B4" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C4" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="E4" s="1" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="F4" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="F4" s="1" t="str">
+        <x:v>摊主把新调的风味塞进你的食谱</x:v>
       </x:c>
       <x:c r="H4" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="I4" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J4" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K4" t="b">
         <x:v>0</x:v>
@@ -2314,28 +2215,28 @@
     </x:row>
     <x:row r="5">
       <x:c r="B5" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C5" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="E5" s="1" t="s">
-        <x:v>107</x:v>
-      </x:c>
-      <x:c r="F5" s="1" t="s">
-        <x:v>108</x:v>
+      <x:c r="E5" s="1" t="str">
+        <x:v>帮摊主整理食谱</x:v>
+      </x:c>
+      <x:c r="F5" s="1" t="str">
+        <x:v>选择1 个食物后，摊主会帮你把它从食谱中删去</x:v>
       </x:c>
       <x:c r="G5" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H5" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="I5" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J5" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K5" t="b">
         <x:v>0</x:v>
@@ -2343,25 +2244,25 @@
     </x:row>
     <x:row r="6">
       <x:c r="B6" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C6" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
       <x:c r="E6" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="H6" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J6" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K6" t="b">
         <x:v>0</x:v>
@@ -2369,25 +2270,25 @@
     </x:row>
     <x:row r="7">
       <x:c r="B7" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="H7" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>5</x:v>
       </x:c>
       <x:c r="J7" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="K7" t="b">
         <x:v>0</x:v>
@@ -2395,25 +2296,25 @@
     </x:row>
     <x:row r="8">
       <x:c r="B8" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>121</x:v>
-      </x:c>
-      <x:c r="F8" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="F8" s="1" t="str">
+        <x:v>你获得了1 个食物</x:v>
       </x:c>
       <x:c r="H8" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>3</x:v>
       </x:c>
-      <x:c r="J8" s="1" t="s">
-        <x:v>124</x:v>
+      <x:c r="J8" s="1" t="str">
+        <x:v>dish_choice_3|祖传食谱残页</x:v>
       </x:c>
       <x:c r="K8" t="b">
         <x:v>0</x:v>
@@ -2421,25 +2322,25 @@
     </x:row>
     <x:row r="9">
       <x:c r="B9" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>126</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>127</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>40</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K9" t="b">
         <x:v>0</x:v>
@@ -2447,25 +2348,25 @@
     </x:row>
     <x:row r="10">
       <x:c r="B10" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>131</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="H10" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="K10" t="b">
         <x:v>0</x:v>
@@ -2473,25 +2374,25 @@
     </x:row>
     <x:row r="11">
       <x:c r="B11" s="1" t="s">
-        <x:v>134</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>135</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>136</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H11" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>137</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="K11" t="b">
         <x:v>0</x:v>
@@ -2499,25 +2400,25 @@
     </x:row>
     <x:row r="12">
       <x:c r="B12" s="1" t="s">
-        <x:v>138</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>139</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>140</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="H12" s="1" t="s">
-        <x:v>132</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>141</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="K12" t="b">
         <x:v>0</x:v>
@@ -2525,28 +2426,28 @@
     </x:row>
     <x:row r="13">
       <x:c r="B13" s="1" t="s">
-        <x:v>142</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>143</x:v>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="str">
+        <x:v>供奉30 金币</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>144</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>145</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="H13" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>-30</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K13" t="b">
         <x:v>0</x:v>
@@ -2554,40 +2455,40 @@
     </x:row>
     <x:row r="14">
       <x:c r="H14" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="K14"/>
     </x:row>
     <x:row r="15">
       <x:c r="B15" s="1" t="s">
-        <x:v>148</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>149</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>150</x:v>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="str">
+        <x:v>供奉1 个食物</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="str">
+        <x:v>选择1 个食物供奉给食神像</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H15" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K15" t="b">
         <x:v>0</x:v>
@@ -2595,37 +2496,37 @@
     </x:row>
     <x:row r="16">
       <x:c r="H16" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="K16"/>
     </x:row>
     <x:row r="17">
       <x:c r="B17" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>152</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>153</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="H17" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K17" t="b">
         <x:v>0</x:v>
@@ -2633,49 +2534,49 @@
     </x:row>
     <x:row r="18">
       <x:c r="H18" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="K18"/>
     </x:row>
     <x:row r="19">
       <x:c r="H19" s="1" t="s">
-        <x:v>155</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>0.25</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K19"/>
     </x:row>
     <x:row r="20">
       <x:c r="B20" s="1" t="s">
-        <x:v>156</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>157</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>158</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="H20" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="K20" t="b">
         <x:v>0</x:v>
@@ -2683,25 +2584,25 @@
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="1" t="s">
-        <x:v>159</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>160</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>161</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="H21" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="K21" t="b">
         <x:v>0</x:v>
@@ -2709,25 +2610,25 @@
     </x:row>
     <x:row r="22">
       <x:c r="B22" s="1" t="s">
-        <x:v>163</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
-        <x:v>164</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>165</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="H22" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>5</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>166</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="K22" t="b">
         <x:v>0</x:v>
@@ -2735,25 +2636,25 @@
     </x:row>
     <x:row r="23">
       <x:c r="B23" s="1" t="s">
-        <x:v>167</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>168</x:v>
-      </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>169</x:v>
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="str">
+        <x:v>你接下普通外卖单，下一场经营挑战目标略有提高</x:v>
       </x:c>
       <x:c r="H23" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>5</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K23" t="b">
         <x:v>0</x:v>
@@ -2761,37 +2662,37 @@
     </x:row>
     <x:row r="24">
       <x:c r="H24" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>30</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K24"/>
     </x:row>
     <x:row r="25">
       <x:c r="B25" s="1" t="s">
-        <x:v>172</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
-        <x:v>173</x:v>
-      </x:c>
-      <x:c r="F25" s="1" t="s">
-        <x:v>174</x:v>
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="str">
+        <x:v>你接下豪华外卖单，下一场经营挑战目标明显提高</x:v>
       </x:c>
       <x:c r="H25" s="1" t="s">
-        <x:v>170</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>10</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K25" t="b">
         <x:v>0</x:v>
@@ -2799,37 +2700,37 @@
     </x:row>
     <x:row r="26">
       <x:c r="H26" s="1" t="s">
-        <x:v>171</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>80</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K26"/>
     </x:row>
     <x:row r="27">
       <x:c r="B27" s="1" t="s">
-        <x:v>175</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
-        <x:v>176</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>177</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="H27" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K27" t="b">
         <x:v>0</x:v>
@@ -2837,25 +2738,25 @@
     </x:row>
     <x:row r="28">
       <x:c r="B28" s="1" t="s">
-        <x:v>178</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E28" s="1" t="s">
-        <x:v>179</x:v>
-      </x:c>
-      <x:c r="F28" s="1" t="s">
-        <x:v>180</x:v>
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="str">
+        <x:v>预支装饰品</x:v>
+      </x:c>
+      <x:c r="F28" s="1" t="str">
+        <x:v>你提前拿走一个装饰品，相关的运气降低了</x:v>
       </x:c>
       <x:c r="H28" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="K28" t="b">
         <x:v>0</x:v>
@@ -2863,37 +2764,37 @@
     </x:row>
     <x:row r="29">
       <x:c r="H29" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>-5</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
-        <x:v>162</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="K29"/>
     </x:row>
     <x:row r="30">
       <x:c r="B30" s="1" t="s">
-        <x:v>181</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>182</x:v>
-      </x:c>
-      <x:c r="F30" s="1" t="s">
-        <x:v>183</x:v>
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="str">
+        <x:v>预支餐桌格</x:v>
+      </x:c>
+      <x:c r="F30" s="1" t="str">
+        <x:v>你提前拿走一包餐桌格，相关的运气降低了</x:v>
       </x:c>
       <x:c r="H30" s="1" t="s">
-        <x:v>184</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
-        <x:v>185</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="K30" t="b">
         <x:v>0</x:v>
@@ -2901,37 +2802,37 @@
     </x:row>
     <x:row r="31">
       <x:c r="H31" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>-5</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
-        <x:v>186</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="K31"/>
     </x:row>
     <x:row r="32">
       <x:c r="B32" s="1" t="s">
-        <x:v>187</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E32" s="1" t="s">
-        <x:v>188</x:v>
-      </x:c>
-      <x:c r="F32" s="1" t="s">
-        <x:v>189</x:v>
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="str">
+        <x:v>预支消耗品</x:v>
+      </x:c>
+      <x:c r="F32" s="1" t="str">
+        <x:v>你提前拿走一个消耗品，后续2 次奖励选择少 1 个选项</x:v>
       </x:c>
       <x:c r="H32" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
-        <x:v>154</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="K32" t="b">
         <x:v>0</x:v>
@@ -2939,40 +2840,40 @@
     </x:row>
     <x:row r="33">
       <x:c r="H33" s="1" t="s">
-        <x:v>190</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
-        <x:v>191</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="K33"/>
     </x:row>
     <x:row r="34">
       <x:c r="B34" s="1" t="s">
-        <x:v>192</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E34" s="1" t="s">
-        <x:v>193</x:v>
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E34" s="1" t="str">
+        <x:v>献上1 个食物</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>194</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H34" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J34" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K34" t="b">
         <x:v>0</x:v>
@@ -2980,40 +2881,40 @@
     </x:row>
     <x:row r="35">
       <x:c r="H35" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>20</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K35"/>
     </x:row>
     <x:row r="36">
       <x:c r="B36" s="1" t="s">
-        <x:v>196</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="C36" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E36" s="1" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="F36" s="1" t="s">
-        <x:v>198</x:v>
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="str">
+        <x:v>献上一个独具风味的食物</x:v>
+      </x:c>
+      <x:c r="F36" s="1" t="str">
+        <x:v>砂锅吞下1 个带风味的食物，只是汤汁颜色变深了一点</x:v>
       </x:c>
       <x:c r="G36" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H36" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="I36" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J36" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="K36" t="b">
         <x:v>0</x:v>
@@ -3021,40 +2922,40 @@
     </x:row>
     <x:row r="37">
       <x:c r="H37" s="1" t="s">
-        <x:v>201</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="I37" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J37" s="1" t="s">
-        <x:v>202</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="K37"/>
     </x:row>
     <x:row r="38">
       <x:c r="B38" s="1" t="s">
-        <x:v>203</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="C38" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E38" s="1" t="s">
-        <x:v>204</x:v>
-      </x:c>
-      <x:c r="F38" s="1" t="s">
-        <x:v>205</x:v>
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="F38" s="1" t="str">
+        <x:v>砂锅吐出1 个装饰品</x:v>
       </x:c>
       <x:c r="G38" s="1" t="s">
-        <x:v>206</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="H38" s="1" t="s">
-        <x:v>128</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I38" s="1">
         <x:v>-20</x:v>
       </x:c>
       <x:c r="J38" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K38" t="b">
         <x:v>0</x:v>
@@ -3062,40 +2963,40 @@
     </x:row>
     <x:row r="39">
       <x:c r="H39" s="1" t="s">
-        <x:v>146</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="I39" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J39" s="1" t="s">
-        <x:v>147</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="K39"/>
     </x:row>
     <x:row r="40">
       <x:c r="B40" s="1" t="s">
-        <x:v>207</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C40" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="E40" s="1" t="s">
-        <x:v>197</x:v>
-      </x:c>
-      <x:c r="F40" s="1" t="s">
-        <x:v>208</x:v>
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E40" s="1" t="str">
+        <x:v>献上一个独具风味的食物</x:v>
+      </x:c>
+      <x:c r="F40" s="1" t="str">
+        <x:v>黑汤翻涌，吐出3 个带有风味的食物</x:v>
       </x:c>
       <x:c r="G40" s="1" t="s">
-        <x:v>199</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="H40" s="1" t="s">
-        <x:v>195</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="I40" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J40" s="1" t="s">
-        <x:v>200</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="K40" t="b">
         <x:v>0</x:v>
@@ -3103,40 +3004,40 @@
     </x:row>
     <x:row r="41">
       <x:c r="H41" s="1" t="s">
-        <x:v>209</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="I41" s="1">
         <x:v>3</x:v>
       </x:c>
       <x:c r="J41" s="1" t="s">
-        <x:v>210</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="K41"/>
     </x:row>
     <x:row r="42">
       <x:c r="B42" s="1" t="s">
-        <x:v>211</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C42" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E42" s="1" t="s">
-        <x:v>212</x:v>
-      </x:c>
-      <x:c r="F42" s="1" t="s">
-        <x:v>213</x:v>
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="F42" s="1" t="str">
+        <x:v>所有金币沉入锅底，砂锅吐出1 个珍贵装饰品和消耗品</x:v>
       </x:c>
       <x:c r="G42" s="1" t="s">
-        <x:v>214</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="H42" s="1" t="s">
-        <x:v>215</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="I42" s="1">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J42" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K42" t="b">
         <x:v>0</x:v>
@@ -3144,37 +3045,37 @@
     </x:row>
     <x:row r="43">
       <x:c r="H43" s="1" t="s">
-        <x:v>216</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="I43" s="1">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J43" s="1" t="s">
-        <x:v>217</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="K43"/>
     </x:row>
     <x:row r="44">
       <x:c r="B44" s="1" t="s">
-        <x:v>218</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C44" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="E44" s="1" t="s">
-        <x:v>219</x:v>
-      </x:c>
-      <x:c r="F44" s="1" t="s">
-        <x:v>220</x:v>
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="E44" s="1" t="str">
+        <x:v>献上消耗品</x:v>
+      </x:c>
+      <x:c r="F44" s="1" t="str">
+        <x:v>消耗品被黑汤吞没，金币从锅沿滚落</x:v>
       </x:c>
       <x:c r="H44" s="1" t="s">
-        <x:v>221</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="I44" s="1">
         <x:v>100</x:v>
       </x:c>
       <x:c r="J44" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K44" t="b">
         <x:v>0</x:v>
@@ -3183,27 +3084,27 @@
     <x:row r="45">
       <x:c r="A45"/>
       <x:c r="B45" t="s">
-        <x:v>222</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C45" t="s">
-        <x:v>66</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D45"/>
-      <x:c r="E45" t="s">
-        <x:v>223</x:v>
+      <x:c r="E45" t="str">
+        <x:v>吃猪肉，-30 金币</x:v>
       </x:c>
       <x:c r="F45" t="s">
-        <x:v>224</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="G45"/>
       <x:c r="H45" t="s">
-        <x:v>128</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I45">
         <x:v>-30</x:v>
       </x:c>
       <x:c r="J45" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K45" t="b">
         <x:v>0</x:v>
@@ -3212,27 +3113,27 @@
     <x:row r="46">
       <x:c r="A46"/>
       <x:c r="B46" t="s">
-        <x:v>225</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C46" t="s">
-        <x:v>66</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D46"/>
       <x:c r="E46" t="s">
-        <x:v>226</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="F46" t="s">
-        <x:v>227</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="G46"/>
       <x:c r="H46" t="s">
-        <x:v>228</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="I46">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J46" t="s">
-        <x:v>227</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="K46" t="b">
         <x:v>0</x:v>
@@ -3241,27 +3142,27 @@
     <x:row r="47">
       <x:c r="A47"/>
       <x:c r="B47" t="s">
-        <x:v>229</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C47" t="s">
-        <x:v>66</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D47"/>
       <x:c r="E47" t="s">
-        <x:v>230</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="F47" t="s">
-        <x:v>231</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="G47"/>
       <x:c r="H47" t="s">
-        <x:v>114</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="I47">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J47" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K47" t="b">
         <x:v>0</x:v>
@@ -3270,29 +3171,29 @@
     <x:row r="48">
       <x:c r="A48"/>
       <x:c r="B48" t="s">
-        <x:v>232</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C48" t="s">
-        <x:v>66</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D48" t="s">
-        <x:v>222</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="E48" t="s">
-        <x:v>233</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="F48" t="s">
-        <x:v>234</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G48"/>
       <x:c r="H48" t="s">
-        <x:v>235</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="I48">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J48" t="s">
-        <x:v>236</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="K48" t="b">
         <x:v>0</x:v>
@@ -3301,29 +3202,29 @@
     <x:row r="49">
       <x:c r="A49"/>
       <x:c r="B49" t="s">
-        <x:v>237</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="C49" t="s">
-        <x:v>66</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D49" t="s">
-        <x:v>222</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="E49" t="s">
-        <x:v>238</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="F49" t="s">
-        <x:v>239</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="G49"/>
       <x:c r="H49" t="s">
-        <x:v>114</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="I49">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J49" t="s">
-        <x:v>105</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="K49" t="b">
         <x:v>0</x:v>
@@ -3332,29 +3233,29 @@
     <x:row r="50">
       <x:c r="A50"/>
       <x:c r="B50" t="s">
-        <x:v>240</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C50" t="s">
-        <x:v>66</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D50" t="s">
-        <x:v>237</x:v>
+        <x:v>204</x:v>
       </x:c>
       <x:c r="E50" t="s">
-        <x:v>241</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="F50" t="s">
-        <x:v>234</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="G50"/>
       <x:c r="H50" t="s">
-        <x:v>235</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="I50">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J50" t="s">
-        <x:v>236</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="K50" t="b">
         <x:v>0</x:v>
@@ -3363,29 +3264,29 @@
     <x:row r="51">
       <x:c r="A51"/>
       <x:c r="B51" t="s">
-        <x:v>242</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C51" t="s">
-        <x:v>66</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D51" t="s">
-        <x:v>229</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="E51" t="s">
-        <x:v>233</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="F51" t="s">
-        <x:v>243</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="G51"/>
       <x:c r="H51" t="s">
-        <x:v>235</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="I51">
         <x:v>1</x:v>
       </x:c>
       <x:c r="J51" t="s">
-        <x:v>244</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="K51" t="b">
         <x:v>0</x:v>
@@ -3394,25 +3295,25 @@
     <x:row r="52">
       <x:c r="A52"/>
       <x:c r="B52" t="s">
-        <x:v>245</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C52" t="s">
-        <x:v>69</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D52"/>
       <x:c r="E52" t="s">
-        <x:v>73</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="F52"/>
       <x:c r="G52"/>
       <x:c r="H52" t="s">
-        <x:v>246</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="I52">
         <x:v>0</x:v>
       </x:c>
       <x:c r="J52" t="s">
-        <x:v>69</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="K52" t="b">
         <x:v>1</x:v>

--- a/GourmetProject/GameConfig/Datas/event.xlsx
+++ b/GourmetProject/GameConfig/Datas/event.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event" sheetId="1" r:id="Rdccd1303eef846db"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event_option" sheetId="2" r:id="Re612b83caa4f4021"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event" sheetId="1" r:id="Ra26460acd8d2445a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event_option" sheetId="2" r:id="R212b18f305094f95"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1031,10 +1031,8 @@
           <x:t xml:space="preserve">name</x:t>
         </x:is>
       </x:c>
-      <x:c r="D1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">desc</x:t>
-        </x:is>
+      <x:c r="D1" t="str">
+        <x:v>desc</x:v>
       </x:c>
       <x:c r="E1" t="inlineStr">
         <x:is>
@@ -1061,10 +1059,8 @@
           <x:t xml:space="preserve">bgSprite</x:t>
         </x:is>
       </x:c>
-      <x:c r="J1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">resultText</x:t>
-        </x:is>
+      <x:c r="J1" t="str">
+        <x:v>resultText</x:v>
       </x:c>
       <x:c r="K1" t="inlineStr">
         <x:is>
@@ -1098,10 +1094,8 @@
           <x:t xml:space="preserve">事件名称</x:t>
         </x:is>
       </x:c>
-      <x:c r="D2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">事件描述(初始/根页正文)</x:t>
-        </x:is>
+      <x:c r="D2" t="str">
+        <x:v>事件描述(初始/根页正文)</x:v>
       </x:c>
       <x:c r="E2" t="inlineStr">
         <x:is>
@@ -1128,10 +1122,8 @@
           <x:t xml:space="preserve">事件插画 Sprite（Resources 路径，空=不显示）</x:t>
         </x:is>
       </x:c>
-      <x:c r="J2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">终止型事件结果文本模板</x:t>
-        </x:is>
+      <x:c r="J2" t="str">
+        <x:v>终止型事件结果文本模板</x:v>
       </x:c>
       <x:c r="K2" t="inlineStr">
         <x:is>
@@ -1165,40 +1157,36 @@
           <x:t xml:space="preserve">string</x:t>
         </x:is>
       </x:c>
-      <x:c r="D3" t="inlineStr">
+      <x:c r="D3" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="E3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">(list#sep=|),ActionBehavior</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">string</x:t>
         </x:is>
       </x:c>
-      <x:c r="E3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">(list#sep=|),ActionBehavior</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F3" t="inlineStr">
+      <x:c r="G3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">float</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="H3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">bool</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="I3" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">string</x:t>
         </x:is>
       </x:c>
-      <x:c r="G3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">bool</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">string</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J3" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">string</x:t>
-        </x:is>
+      <x:c r="J3" t="str">
+        <x:v>string</x:v>
       </x:c>
       <x:c r="K3" t="inlineStr">
         <x:is>
@@ -1227,10 +1215,8 @@
           <x:t xml:space="preserve">午夜食堂</x:t>
         </x:is>
       </x:c>
-      <x:c r="D4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">深夜时分，一家食堂悄然开启，厨师端出一道红香肠，说到，“要切成章鱼的样子吗”</x:t>
-        </x:is>
+      <x:c r="D4" t="str">
+        <x:v>深夜时分，一家食堂悄然开启，厨师端出一道红香肠，说到，“要切成章鱼的样子吗”</x:v>
       </x:c>
       <x:c r="E4" t="inlineStr">
         <x:is>
@@ -1248,6 +1234,7 @@
           <x:t xml:space="preserve">Sprites/UI/Events/event_midnight_tasting</x:t>
         </x:is>
       </x:c>
+      <x:c r="J4"/>
       <x:c r="K4" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1263,10 +1250,8 @@
           <x:t xml:space="preserve">决战食神</x:t>
         </x:is>
       </x:c>
-      <x:c r="D5" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">你去对面新开的西餐厅，点了一份沙拉，店员将水浇到沙拉上，说到“没见过吧，这是生长沙拉，里面所有元素都是可食用的”</x:t>
-        </x:is>
+      <x:c r="D5" t="str">
+        <x:v>你去对面新开的西餐厅，点了一份沙拉，店员将水浇到沙拉上，说到“没见过吧，这是生长沙拉，里面所有元素都是可食用的”</x:v>
       </x:c>
       <x:c r="E5" t="inlineStr">
         <x:is>
@@ -1284,6 +1269,7 @@
           <x:t xml:space="preserve">Sprites/UI/Events/event_ancestral_recipe_page</x:t>
         </x:is>
       </x:c>
+      <x:c r="J5"/>
       <x:c r="K5" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1299,10 +1285,8 @@
           <x:t xml:space="preserve">木匠吉佩托</x:t>
         </x:is>
       </x:c>
-      <x:c r="D6" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">一位技艺精湛的木匠造访，询问你是否需要强化一下餐桌</x:t>
-        </x:is>
+      <x:c r="D6" t="str">
+        <x:v>一位技艺精湛的木匠造访，询问你是否需要强化一下餐桌</x:v>
       </x:c>
       <x:c r="E6" t="inlineStr">
         <x:is>
@@ -1320,6 +1304,7 @@
           <x:t xml:space="preserve">Sprites/UI/Events/event_table_carpenter</x:t>
         </x:is>
       </x:c>
+      <x:c r="J6"/>
       <x:c r="K6" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1335,10 +1320,8 @@
           <x:t xml:space="preserve">举报风波</x:t>
         </x:is>
       </x:c>
-      <x:c r="D7" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">隔壁的餐厅，在网上发表污蔑的言论，希望以此获得竞争优势</x:t>
-        </x:is>
+      <x:c r="D7" t="str">
+        <x:v>隔壁的餐厅，在网上发表污蔑的言论，希望以此获得竞争优势</x:v>
       </x:c>
       <x:c r="E7" t="inlineStr">
         <x:is>
@@ -1356,6 +1339,7 @@
           <x:t xml:space="preserve">Sprites/UI/Events/event_kitchen_god_statue</x:t>
         </x:is>
       </x:c>
+      <x:c r="J7"/>
       <x:c r="K7" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1371,10 +1355,8 @@
           <x:t xml:space="preserve">蘑菇挑战赛</x:t>
         </x:is>
       </x:c>
-      <x:c r="D8" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">主厨端出来一份蘑菇煲，其中各种鲜香的鲜艳蘑菇，让你既忍不住吞咽口水，又担心安全。主厨说道，“吃下这些蘑菇，可以获得我的终极大奖”</x:t>
-        </x:is>
+      <x:c r="D8" t="str">
+        <x:v>主厨端出来一份蘑菇煲，其中各种鲜香的鲜艳蘑菇，让你既忍不住吞咽口水，又担心安全。主厨说道，“吃下这些蘑菇，可以获得我的终极大奖”</x:v>
       </x:c>
       <x:c r="E8" t="inlineStr">
         <x:is>
@@ -1397,6 +1379,7 @@
           <x:t xml:space="preserve">Sprites/UI/Events/event_crossroad_sign</x:t>
         </x:is>
       </x:c>
+      <x:c r="J8"/>
       <x:c r="K8" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1412,10 +1395,8 @@
           <x:t xml:space="preserve">收取利息</x:t>
         </x:is>
       </x:c>
-      <x:c r="D9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">每满 {threshold} 金币获得 {goldPer}金币，最高 {maxGain}金币</x:t>
-        </x:is>
+      <x:c r="D9" t="str">
+        <x:v>每满 [gold]{threshold} 金币[/gold]获得 [gold]{goldPer}金币[/gold]，最高 [gold]{maxGain}金币[/gold]</x:v>
       </x:c>
       <x:c r="E9" t="inlineStr">
         <x:is>
@@ -1433,10 +1414,8 @@
           <x:t xml:space="preserve">Sprites/UI/Events/event_interest</x:t>
         </x:is>
       </x:c>
-      <x:c r="J9" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">金币 +{gain}</x:t>
-        </x:is>
+      <x:c r="J9" t="str">
+        <x:v>[gold]金币 +{gain}[/gold]</x:v>
       </x:c>
       <x:c r="K9" t="n">
         <x:v>0</x:v>
@@ -1453,10 +1432,8 @@
           <x:t xml:space="preserve">抽奖机</x:t>
         </x:is>
       </x:c>
-      <x:c r="D10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">一个华丽的机器，投入金币有概率获得任何奖励</x:t>
-        </x:is>
+      <x:c r="D10" t="str">
+        <x:v>一个华丽的机器，投入[gold]金币[/gold]有概率获得任何奖励</x:v>
       </x:c>
       <x:c r="E10" t="inlineStr">
         <x:is>
@@ -1474,10 +1451,8 @@
           <x:t xml:space="preserve">Sprites/UI/Events/event_slot_machine</x:t>
         </x:is>
       </x:c>
-      <x:c r="J10" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">这次什么也没有。</x:t>
-        </x:is>
+      <x:c r="J10" t="str">
+        <x:v>这次什么也没有。</x:v>
       </x:c>
       <x:c r="K10" t="n">
         <x:v>0.4</x:v>
@@ -1504,10 +1479,8 @@
           <x:t xml:space="preserve">会员制餐厅</x:t>
         </x:is>
       </x:c>
-      <x:c r="D11" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">你与另一位朋友德川相约同去一处会员制餐厅就餐。服务员上了三道菜，分别是迎宾酒、蔬菜棒蘸酱、汉堡肉</x:t>
-        </x:is>
+      <x:c r="D11" t="str">
+        <x:v>你与另一位朋友德川相约同去一处会员制餐厅就餐。服务员上了三道菜，分别是迎宾酒、蔬菜棒蘸酱、汉堡肉</x:v>
       </x:c>
       <x:c r="E11" t="inlineStr">
         <x:is>
@@ -1525,6 +1498,7 @@
           <x:t xml:space="preserve">Sprites/UI/Events/event_new_event</x:t>
         </x:is>
       </x:c>
+      <x:c r="J11"/>
       <x:c r="K11" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1540,10 +1514,8 @@
           <x:t xml:space="preserve">最后的晚餐</x:t>
         </x:is>
       </x:c>
-      <x:c r="D12" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">12位厨师围坐在长桌前。主厨刚举起酒杯，便宣布：“你们中有人把秘方卖给了对面餐厅。”众人立刻放下餐具，互相指认起来。</x:t>
-        </x:is>
+      <x:c r="D12" t="str">
+        <x:v>12位厨师围坐在长桌前。主厨刚举起酒杯，便宣布：“你们中有人把秘方卖给了对面餐厅。”众人立刻放下餐具，互相指认起来。</x:v>
       </x:c>
       <x:c r="E12" t="inlineStr">
         <x:is>
@@ -1556,6 +1528,7 @@
       <x:c r="H12" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J12"/>
       <x:c r="K12" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1571,10 +1544,8 @@
           <x:t xml:space="preserve">双R餐厅的夜晚</x:t>
         </x:is>
       </x:c>
-      <x:c r="D13" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">雨夜，你走进双R餐厅。黑咖啡刚煮好，樱桃派只剩最后一块；角落里的木头女士似乎有话要说。</x:t>
-        </x:is>
+      <x:c r="D13" t="str">
+        <x:v>雨夜，你走进双R餐厅。黑咖啡刚煮好，樱桃派只剩最后一块；角落里的木头女士似乎有话要说。</x:v>
       </x:c>
       <x:c r="E13" t="inlineStr">
         <x:is>
@@ -1587,38 +1558,40 @@
       <x:c r="H13" t="n">
         <x:v>1</x:v>
       </x:c>
+      <x:c r="J13"/>
       <x:c r="K13" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
-      <x:c r="A14"/>
-      <x:c r="B14" t="str">
-        <x:v>ev_chuka_ichiban_trial</x:v>
-      </x:c>
-      <x:c r="C14" t="str">
-        <x:v>最后一灶也会发光</x:v>
+      <x:c r="B14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ev_chuka_ichiban_trial</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">最后一灶也会发光</x:t>
+        </x:is>
       </x:c>
       <x:c r="D14" t="str">
         <x:v>阳泉酒家收档前又来了一桌客人。小当家把最后一眼灶火让给你：“用哪道料理招待他们？”</x:v>
       </x:c>
-      <x:c r="E14" t="str">
-        <x:v>Event|Reward</x:v>
-      </x:c>
-      <x:c r="F14"/>
+      <x:c r="E14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Event|Reward</x:t>
+        </x:is>
+      </x:c>
       <x:c r="G14" t="n">
         <x:v>1</x:v>
       </x:c>
       <x:c r="H14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="I14"/>
       <x:c r="J14"/>
       <x:c r="K14" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="L14"/>
-      <x:c r="M14"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1668,25 +1641,19 @@
           <x:t xml:space="preserve">parentId</x:t>
         </x:is>
       </x:c>
-      <x:c r="E1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">text</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">resultText</x:t>
-        </x:is>
+      <x:c r="E1" s="1" t="str">
+        <x:v>text</x:v>
+      </x:c>
+      <x:c r="F1" s="1" t="str">
+        <x:v>resultText</x:v>
       </x:c>
       <x:c r="G1" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">condition</x:t>
         </x:is>
       </x:c>
-      <x:c r="H1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">conditionText</x:t>
-        </x:is>
+      <x:c r="H1" s="1" t="str">
+        <x:v>conditionText</x:v>
       </x:c>
       <x:c r="I1" s="1" t="inlineStr">
         <x:is>
@@ -1713,10 +1680,8 @@
           <x:t xml:space="preserve">branchWeight</x:t>
         </x:is>
       </x:c>
-      <x:c r="N1" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">branchPageText</x:t>
-        </x:is>
+      <x:c r="N1" s="1" t="str">
+        <x:v>branchPageText</x:v>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -1740,25 +1705,19 @@
           <x:t xml:space="preserve">父选项ID→event_option.id</x:t>
         </x:is>
       </x:c>
-      <x:c r="E2" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">选项文本(按钮)</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F2" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">选中后的结果/子页正文</x:t>
-        </x:is>
+      <x:c r="E2" s="1" t="str">
+        <x:v>选项文本(按钮)</x:v>
+      </x:c>
+      <x:c r="F2" s="1" t="str">
+        <x:v>选中后的结果/子页正文</x:v>
       </x:c>
       <x:c r="G2" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">选项前置条件</x:t>
         </x:is>
       </x:c>
-      <x:c r="H2" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">选项前置条件显示文案</x:t>
-        </x:is>
+      <x:c r="H2" s="1" t="str">
+        <x:v>选项前置条件显示文案</x:v>
       </x:c>
       <x:c r="I2" s="1" t="inlineStr">
         <x:is>
@@ -1785,10 +1744,8 @@
           <x:t xml:space="preserve">同一父选项下随机子分支相对权重；同组全部为 0 时保持手动选择</x:t>
         </x:is>
       </x:c>
-      <x:c r="N2" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">随机命中该子选项后显示的页面正文（空=沿用父选项结果正文）</x:t>
-        </x:is>
+      <x:c r="N2" s="1" t="str">
+        <x:v>随机命中该子选项后显示的页面正文（空=沿用父选项结果正文）</x:v>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1812,25 +1769,19 @@
           <x:t xml:space="preserve">string</x:t>
         </x:is>
       </x:c>
-      <x:c r="E3" s="1" t="inlineStr">
+      <x:c r="E3" s="1" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="F3" s="1" t="str">
+        <x:v>string</x:v>
+      </x:c>
+      <x:c r="G3" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">string</x:t>
         </x:is>
       </x:c>
-      <x:c r="F3" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">string</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="G3" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">string</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H3" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">string</x:t>
-        </x:is>
+      <x:c r="H3" s="1" t="str">
+        <x:v>string</x:v>
       </x:c>
       <x:c r="I3" s="1" t="inlineStr">
         <x:is>
@@ -1857,10 +1808,8 @@
           <x:t xml:space="preserve">float</x:t>
         </x:is>
       </x:c>
-      <x:c r="N3" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">string</x:t>
-        </x:is>
+      <x:c r="N3" s="1" t="str">
+        <x:v>string</x:v>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1874,16 +1823,13 @@
           <x:t xml:space="preserve">ev_midnight_tasting</x:t>
         </x:is>
       </x:c>
-      <x:c r="E4" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">不切直接吃</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F4" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">新鲜的红香肠，肉香浓密</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E4" s="1" t="str">
+        <x:v>不切直接吃</x:v>
+      </x:c>
+      <x:c r="F4" s="1" t="str">
+        <x:v>新鲜的红香肠，肉香浓密</x:v>
+      </x:c>
+      <x:c r="H4"/>
       <x:c r="I4" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -1903,6 +1849,7 @@
       <x:c r="M4" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N4"/>
     </x:row>
     <x:row r="5">
       <x:c r="B5" s="1" t="inlineStr">
@@ -1915,16 +1862,13 @@
           <x:t xml:space="preserve">ev_midnight_tasting</x:t>
         </x:is>
       </x:c>
-      <x:c r="E5" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">切成章鱼的样子</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F5" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">红香肠被切两刀，在沸水的作用下弯曲起来</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E5" s="1" t="str">
+        <x:v>切成章鱼的样子</x:v>
+      </x:c>
+      <x:c r="F5" s="1" t="str">
+        <x:v>红香肠被切两刀，在沸水的作用下弯曲起来</x:v>
+      </x:c>
+      <x:c r="H5"/>
       <x:c r="I5" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -1944,6 +1888,7 @@
       <x:c r="M5" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N5"/>
     </x:row>
     <x:row r="6">
       <x:c r="B6" s="1" t="inlineStr">
@@ -1956,16 +1901,13 @@
           <x:t xml:space="preserve">ev_midnight_tasting</x:t>
         </x:is>
       </x:c>
-      <x:c r="E6" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">来碗泡面配着吃</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F6" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">厨师称赞，“不愧是老吃家”，奉上独门秘籍</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E6" s="1" t="str">
+        <x:v>来碗泡面配着吃</x:v>
+      </x:c>
+      <x:c r="F6" s="1" t="str">
+        <x:v>厨师称赞，“不愧是老吃家”，奉上独门秘籍</x:v>
+      </x:c>
+      <x:c r="H6"/>
       <x:c r="I6" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -1985,6 +1927,7 @@
       <x:c r="M6" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N6"/>
     </x:row>
     <x:row r="7">
       <x:c r="B7" s="1" t="inlineStr">
@@ -1997,16 +1940,13 @@
           <x:t xml:space="preserve">ev_ancestral_recipe_page</x:t>
         </x:is>
       </x:c>
-      <x:c r="E7" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">尝尝沙拉</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F7" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">你发现沙拉别有一番滋味，调料方式出乎意料</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E7" s="1" t="str">
+        <x:v>尝尝沙拉</x:v>
+      </x:c>
+      <x:c r="F7" s="1" t="str">
+        <x:v>你发现沙拉别有一番滋味，调料方式出乎意料</x:v>
+      </x:c>
+      <x:c r="H7"/>
       <x:c r="I7" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -2026,6 +1966,7 @@
       <x:c r="M7" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N7"/>
     </x:row>
     <x:row r="8">
       <x:c r="B8" s="1" t="inlineStr">
@@ -2038,16 +1979,13 @@
           <x:t xml:space="preserve">ev_ancestral_recipe_page</x:t>
         </x:is>
       </x:c>
-      <x:c r="E8" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">我不是来看你变魔术的</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F8" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">“我是来吃饭的，不是来看你变魔术的，要装神弄鬼你回法国”</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E8" s="1" t="str">
+        <x:v>我不是来看你变魔术的</x:v>
+      </x:c>
+      <x:c r="F8" s="1" t="str">
+        <x:v>“我是来吃饭的，不是来看你变魔术的，要装神弄鬼你回法国”</x:v>
+      </x:c>
+      <x:c r="H8"/>
       <x:c r="I8" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -2067,6 +2005,7 @@
       <x:c r="M8" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N8"/>
     </x:row>
     <x:row r="9">
       <x:c r="B9" s="1" t="inlineStr">
@@ -2079,16 +2018,13 @@
           <x:t xml:space="preserve">ev_ancestral_recipe_page</x:t>
         </x:is>
       </x:c>
-      <x:c r="E9" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">比试厨艺</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F9" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">你做了一道家常菜“葱爆牛肉”，味道惊人，餐厅名声大噪</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E9" s="1" t="str">
+        <x:v>比试厨艺</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="str">
+        <x:v>你做了一道家常菜“葱爆牛肉”，味道惊人，餐厅名声大噪</x:v>
+      </x:c>
+      <x:c r="H9"/>
       <x:c r="I9" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -2108,6 +2044,7 @@
       <x:c r="M9" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N9"/>
     </x:row>
     <x:row r="10">
       <x:c r="B10" s="1" t="inlineStr">
@@ -2120,16 +2057,13 @@
           <x:t xml:space="preserve">ev_table_carpenter</x:t>
         </x:is>
       </x:c>
-      <x:c r="E10" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">修改为石料</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F10" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">木匠从卡车上搬下来两个石料箱</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E10" s="1" t="str">
+        <x:v>修改为石料</x:v>
+      </x:c>
+      <x:c r="F10" s="1" t="str">
+        <x:v>木匠从卡车上搬下来两个石料箱</x:v>
+      </x:c>
+      <x:c r="H10"/>
       <x:c r="I10" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -2149,6 +2083,7 @@
       <x:c r="M10" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N10"/>
     </x:row>
     <x:row r="11">
       <x:c r="B11" s="1" t="inlineStr">
@@ -2161,16 +2096,13 @@
           <x:t xml:space="preserve">ev_table_carpenter</x:t>
         </x:is>
       </x:c>
-      <x:c r="E11" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">修改为木料</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F11" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">木匠从卡车上搬下来两个木料箱</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E11" s="1" t="str">
+        <x:v>修改为木料</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="str">
+        <x:v>木匠从卡车上搬下来两个木料箱</x:v>
+      </x:c>
+      <x:c r="H11"/>
       <x:c r="I11" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -2190,6 +2122,7 @@
       <x:c r="M11" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N11"/>
     </x:row>
     <x:row r="12">
       <x:c r="B12" s="1" t="inlineStr">
@@ -2202,16 +2135,13 @@
           <x:t xml:space="preserve">ev_table_carpenter</x:t>
         </x:is>
       </x:c>
-      <x:c r="E12" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">选择金属料</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F12" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">木匠从卡车上搬下来两个金属料箱</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E12" s="1" t="str">
+        <x:v>选择金属料</x:v>
+      </x:c>
+      <x:c r="F12" s="1" t="str">
+        <x:v>木匠从卡车上搬下来两个金属料箱</x:v>
+      </x:c>
+      <x:c r="H12"/>
       <x:c r="I12" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -2231,6 +2161,7 @@
       <x:c r="M12" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N12"/>
     </x:row>
     <x:row r="13">
       <x:c r="B13" s="1" t="inlineStr">
@@ -2243,25 +2174,19 @@
           <x:t xml:space="preserve">ev_kitchen_god_statue</x:t>
         </x:is>
       </x:c>
-      <x:c r="E13" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">申诉负面舆论</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F13" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">经平台核实，对方的言论不实，特此赠予餐厅一件装饰品，以表安慰</x:t>
-        </x:is>
+      <x:c r="E13" s="1" t="str">
+        <x:v>申诉负面舆论</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="str">
+        <x:v>经平台核实，对方的言论不实，特此赠予餐厅一件[term]装饰品[/term]，以表安慰</x:v>
       </x:c>
       <x:c r="G13" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">minGold:30</x:t>
         </x:is>
       </x:c>
-      <x:c r="H13" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">需要至少 30 金币</x:t>
-        </x:is>
+      <x:c r="H13" s="2" t="str">
+        <x:v>需要至少 [gold]30 金币[/gold]</x:v>
       </x:c>
       <x:c r="I13" s="1" t="inlineStr">
         <x:is>
@@ -2282,6 +2207,7 @@
       <x:c r="M13" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N13"/>
     </x:row>
     <x:row r="14">
       <x:c r="B14" s="1" t="inlineStr">
@@ -2294,25 +2220,19 @@
           <x:t xml:space="preserve">ev_kitchen_god_statue</x:t>
         </x:is>
       </x:c>
-      <x:c r="E14" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">激情互喷</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F14" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">争论吸引了大量关注，有支持也有贬低</x:t>
-        </x:is>
+      <x:c r="E14" s="1" t="str">
+        <x:v>激情互喷</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="str">
+        <x:v>争论吸引了大量关注，有支持也有贬低</x:v>
       </x:c>
       <x:c r="G14" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">hasRecipeDish</x:t>
         </x:is>
       </x:c>
-      <x:c r="H14" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">需要食谱中至少有 1 个食物</x:t>
-        </x:is>
+      <x:c r="H14" s="2" t="str">
+        <x:v>需要食谱中至少有 1 个食物</x:v>
       </x:c>
       <x:c r="I14" s="1" t="inlineStr">
         <x:is>
@@ -2333,6 +2253,7 @@
       <x:c r="M14" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N14"/>
     </x:row>
     <x:row r="15">
       <x:c r="B15" s="1" t="inlineStr">
@@ -2345,16 +2266,13 @@
           <x:t xml:space="preserve">ev_kitchen_god_statue</x:t>
         </x:is>
       </x:c>
-      <x:c r="E15" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">置之不理</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F15" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">消极的应对给餐厅带来了一些影响，不过很快平息</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E15" s="1" t="str">
+        <x:v>置之不理</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="str">
+        <x:v>消极的应对给餐厅带来了一些影响，不过很快平息</x:v>
+      </x:c>
+      <x:c r="H15"/>
       <x:c r="I15" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -2374,6 +2292,7 @@
       <x:c r="M15" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N15"/>
     </x:row>
     <x:row r="16">
       <x:c r="B16" s="1" t="inlineStr">
@@ -2386,11 +2305,11 @@
           <x:t xml:space="preserve">ev_interest</x:t>
         </x:is>
       </x:c>
-      <x:c r="E16" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">金币 +{gain}</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E16" s="1" t="str">
+        <x:v>[gold]金币 +{gain}[/gold]</x:v>
+      </x:c>
+      <x:c r="F16"/>
+      <x:c r="H16"/>
       <x:c r="I16" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">CollectInterest</x:t>
@@ -2410,6 +2329,7 @@
       <x:c r="M16" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N16"/>
     </x:row>
     <x:row r="17">
       <x:c r="B17" s="1" t="inlineStr">
@@ -2422,11 +2342,11 @@
           <x:t xml:space="preserve">ev_slot_machine</x:t>
         </x:is>
       </x:c>
-      <x:c r="E17" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">{slotCostText}（{slotStatus}）</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E17" s="1" t="str">
+        <x:v>{slotCostText}（{slotStatus}）</x:v>
+      </x:c>
+      <x:c r="F17"/>
+      <x:c r="H17"/>
       <x:c r="I17" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -2446,6 +2366,7 @@
       <x:c r="M17" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N17"/>
     </x:row>
     <x:row r="18">
       <x:c r="B18" s="1" t="inlineStr">
@@ -2458,11 +2379,11 @@
           <x:t xml:space="preserve">ev_slot_machine</x:t>
         </x:is>
       </x:c>
-      <x:c r="E18" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">离开</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E18" s="1" t="str">
+        <x:v>离开</x:v>
+      </x:c>
+      <x:c r="F18"/>
+      <x:c r="H18"/>
       <x:c r="I18" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -2482,6 +2403,7 @@
       <x:c r="M18" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N18"/>
     </x:row>
     <x:row r="19">
       <x:c r="B19" s="1" t="inlineStr">
@@ -2499,16 +2421,13 @@
           <x:t xml:space="preserve">opt_midnight_sample</x:t>
         </x:is>
       </x:c>
-      <x:c r="E19" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">对食物的理解加深了！后续更容易获得更好的食物</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F19" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">食物奖励隐藏分永久 +5。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E19" s="1" t="str">
+        <x:v>对食物的理解加深了！后续更容易获得更好的食物</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="str">
+        <x:v>食物奖励隐藏分永久 +5。</x:v>
+      </x:c>
+      <x:c r="H19"/>
       <x:c r="I19" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddHiddenScoreOffset</x:t>
@@ -2528,6 +2447,7 @@
       <x:c r="M19" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N19"/>
     </x:row>
     <x:row r="20">
       <x:c r="B20" s="1" t="inlineStr">
@@ -2545,16 +2465,13 @@
           <x:t xml:space="preserve">opt_midnight_menu</x:t>
         </x:is>
       </x:c>
-      <x:c r="E20" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">心情大好，下次营业获得的金币额外+60%</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F20" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">下一次营业基础金币 ×1.6。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E20" s="1" t="str">
+        <x:v>心情大好，下次营业获得的[gold]金币[/gold]额外[gold]+60%[/gold]</x:v>
+      </x:c>
+      <x:c r="F20" s="1" t="str">
+        <x:v>下一次营业基础[gold]金币[/gold] ×1.6。</x:v>
+      </x:c>
+      <x:c r="H20"/>
       <x:c r="I20" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddBusinessGoldPct</x:t>
@@ -2574,6 +2491,7 @@
       <x:c r="M20" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="1" t="inlineStr">
@@ -2591,16 +2509,13 @@
           <x:t xml:space="preserve">opt_midnight_leave</x:t>
         </x:is>
       </x:c>
-      <x:c r="E21" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">所有食物分数+2！这就是知识的力量</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F21" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">触发时食谱中已有的全部食物永久分数 +2。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E21" s="1" t="str">
+        <x:v>[context]所有[/context]食物[strong]分数[/strong][score]+2[/score]！这就是知识的力量</x:v>
+      </x:c>
+      <x:c r="F21" s="1" t="str">
+        <x:v>触发时食谱中已有的全部食物永久[strong]分数[/strong] [score]+2[/score]。</x:v>
+      </x:c>
+      <x:c r="H21"/>
       <x:c r="I21" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddAllRecipeScoreFlat</x:t>
@@ -2620,6 +2535,7 @@
       <x:c r="M21" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N21"/>
     </x:row>
     <x:row r="22">
       <x:c r="B22" s="1" t="inlineStr">
@@ -2637,16 +2553,13 @@
           <x:t xml:space="preserve">opt_recipe_page_sell</x:t>
         </x:is>
       </x:c>
-      <x:c r="E22" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">本周后续营业的金币奖励提升30%</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F22" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">本周后续营业基础金币 ×1.3。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E22" s="1" t="str">
+        <x:v>本周后续营业的[gold]金币[/gold]奖励提升[gold]30%[/gold]</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="str">
+        <x:v>本周后续营业基础[gold]金币[/gold] ×1.3。</x:v>
+      </x:c>
+      <x:c r="H22"/>
       <x:c r="I22" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddBusinessGoldPct</x:t>
@@ -2666,6 +2579,7 @@
       <x:c r="M22" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N22"/>
     </x:row>
     <x:row r="23">
       <x:c r="B23" s="1" t="inlineStr">
@@ -2683,16 +2597,13 @@
           <x:t xml:space="preserve">opt_recipe_page_body</x:t>
         </x:is>
       </x:c>
-      <x:c r="E23" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">获得两个调味相关的消耗品</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F23" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">从六种调味箱中放回随机获得 2 个。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E23" s="1" t="str">
+        <x:v>获得两个调味相关的[term]消耗品[/term]</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="str">
+        <x:v>从六种调味箱中放回随机获得 2 个。</x:v>
+      </x:c>
+      <x:c r="H23"/>
       <x:c r="I23" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GrantRandomActiveItems</x:t>
@@ -2712,6 +2623,7 @@
       <x:c r="M23" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N23"/>
     </x:row>
     <x:row r="24">
       <x:c r="B24" s="1" t="inlineStr">
@@ -2729,16 +2641,13 @@
           <x:t xml:space="preserve">opt_recipe_page_cover</x:t>
         </x:is>
       </x:c>
-      <x:c r="E24" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">星级评鉴美味值要求提升20%，金币奖励翻倍</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F24" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">后续星级评鉴目标 ×1.2，基础金币 ×2。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E24" s="1" t="str">
+        <x:v>[context]星级评鉴[/context]美味值要求提升20%，[gold]金币[/gold]奖励翻倍</x:v>
+      </x:c>
+      <x:c r="F24" s="1" t="str">
+        <x:v>后续[context]星级评鉴[/context]目标 ×1.2，基础[gold]金币[/gold] ×2。</x:v>
+      </x:c>
+      <x:c r="H24"/>
       <x:c r="I24" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddBossTargetScorePct</x:t>
@@ -2758,8 +2667,12 @@
       <x:c r="M24" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N24"/>
     </x:row>
     <x:row r="25">
+      <x:c r="E25"/>
+      <x:c r="F25"/>
+      <x:c r="H25"/>
       <x:c r="I25" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddBossBaseGoldPct</x:t>
@@ -2773,6 +2686,7 @@
           <x:t xml:space="preserve">-</x:t>
         </x:is>
       </x:c>
+      <x:c r="N25"/>
     </x:row>
     <x:row r="26">
       <x:c r="B26" s="1" t="inlineStr">
@@ -2790,16 +2704,13 @@
           <x:t xml:space="preserve">opt_carpenter_wood</x:t>
         </x:is>
       </x:c>
-      <x:c r="E26" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">获得2个石料类强化箱</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F26" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">从三种石料箱中放回随机获得 2 个。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E26" s="1" t="str">
+        <x:v>获得2个石料类强化箱</x:v>
+      </x:c>
+      <x:c r="F26" s="1" t="str">
+        <x:v>从三种石料箱中放回随机获得 2 个。</x:v>
+      </x:c>
+      <x:c r="H26"/>
       <x:c r="I26" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GrantRandomActiveItems</x:t>
@@ -2819,6 +2730,7 @@
       <x:c r="M26" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N26"/>
     </x:row>
     <x:row r="27">
       <x:c r="B27" s="1" t="inlineStr">
@@ -2836,16 +2748,13 @@
           <x:t xml:space="preserve">opt_carpenter_stone</x:t>
         </x:is>
       </x:c>
-      <x:c r="E27" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">获得2个木料类强化箱</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F27" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">从两种木料箱中放回随机获得 2 个。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E27" s="1" t="str">
+        <x:v>获得2个木料类强化箱</x:v>
+      </x:c>
+      <x:c r="F27" s="1" t="str">
+        <x:v>从两种木料箱中放回随机获得 2 个。</x:v>
+      </x:c>
+      <x:c r="H27"/>
       <x:c r="I27" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GrantRandomActiveItems</x:t>
@@ -2865,6 +2774,7 @@
       <x:c r="M27" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N27"/>
     </x:row>
     <x:row r="28">
       <x:c r="B28" s="1" t="inlineStr">
@@ -2882,16 +2792,13 @@
           <x:t xml:space="preserve">opt_carpenter_metal</x:t>
         </x:is>
       </x:c>
-      <x:c r="E28" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">获得2个金属料强化箱</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F28" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">从两种金属箱中放回随机获得 2 个。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E28" s="1" t="str">
+        <x:v>获得2个金属料强化箱</x:v>
+      </x:c>
+      <x:c r="F28" s="1" t="str">
+        <x:v>从两种金属箱中放回随机获得 2 个。</x:v>
+      </x:c>
+      <x:c r="H28"/>
       <x:c r="I28" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GrantRandomActiveItems</x:t>
@@ -2911,6 +2818,7 @@
       <x:c r="M28" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N28"/>
     </x:row>
     <x:row r="29">
       <x:c r="B29" s="1" t="inlineStr">
@@ -2928,16 +2836,13 @@
           <x:t xml:space="preserve">opt_statue_gold</x:t>
         </x:is>
       </x:c>
-      <x:c r="E29" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">获得1个装饰品</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F29" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">支付 30 金币，随机获得 1 个非诅咒装饰品。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E29" s="1" t="str">
+        <x:v>获得1个[term]装饰品[/term]</x:v>
+      </x:c>
+      <x:c r="F29" s="1" t="str">
+        <x:v>支付 [gold]30 金币[/gold]，随机获得 1 个非诅咒[term]装饰品[/term]。</x:v>
+      </x:c>
+      <x:c r="H29"/>
       <x:c r="I29" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GainGold</x:t>
@@ -2957,8 +2862,12 @@
       <x:c r="M29" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N29"/>
     </x:row>
     <x:row r="30">
+      <x:c r="E30"/>
+      <x:c r="F30"/>
+      <x:c r="H30"/>
       <x:c r="I30" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GrantRandomPassiveItems</x:t>
@@ -2972,6 +2881,7 @@
           <x:t xml:space="preserve">Positive</x:t>
         </x:is>
       </x:c>
+      <x:c r="N30"/>
     </x:row>
     <x:row r="31">
       <x:c r="B31" s="1" t="inlineStr">
@@ -2989,16 +2899,13 @@
           <x:t xml:space="preserve">opt_statue_dish</x:t>
         </x:is>
       </x:c>
-      <x:c r="E31" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">获得100金币和1个负面装饰品</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F31" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">获得 100 金币和 1 个诅咒装饰品。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E31" s="1" t="str">
+        <x:v>获得[gold]100金币[/gold]和1个负面[term]装饰品[/term]</x:v>
+      </x:c>
+      <x:c r="F31" s="1" t="str">
+        <x:v>获得 [gold]100 金币[/gold]和 1 个诅咒[term]装饰品[/term]。</x:v>
+      </x:c>
+      <x:c r="H31"/>
       <x:c r="I31" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GainGold</x:t>
@@ -3018,8 +2925,12 @@
       <x:c r="M31" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N31"/>
     </x:row>
     <x:row r="32">
+      <x:c r="E32"/>
+      <x:c r="F32"/>
+      <x:c r="H32"/>
       <x:c r="I32" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GrantRandomPassiveItems</x:t>
@@ -3033,6 +2944,7 @@
           <x:t xml:space="preserve">Negative</x:t>
         </x:is>
       </x:c>
+      <x:c r="N32"/>
     </x:row>
     <x:row r="33">
       <x:c r="B33" s="1" t="inlineStr">
@@ -3050,16 +2962,13 @@
           <x:t xml:space="preserve">opt_statue_steal</x:t>
         </x:is>
       </x:c>
-      <x:c r="E33" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">下次营业金币-40%</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F33" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">获得 100 金币和 1 个随机消耗品；下一次营业基础金币 ×0.6。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E33" s="1" t="str">
+        <x:v>下次营业[gold]金币-40%[/gold]</x:v>
+      </x:c>
+      <x:c r="F33" s="1" t="str">
+        <x:v>获得 [gold]100 金币[/gold]和 1 个随机[term]消耗品[/term]；下一次营业基础[gold]金币[/gold] ×0.6。</x:v>
+      </x:c>
+      <x:c r="H33"/>
       <x:c r="I33" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddBusinessGoldPct</x:t>
@@ -3079,6 +2988,7 @@
       <x:c r="M33" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N33"/>
     </x:row>
     <x:row r="34">
       <x:c r="B34" s="1" t="inlineStr">
@@ -3091,16 +3001,13 @@
           <x:t xml:space="preserve">ev_new_event</x:t>
         </x:is>
       </x:c>
-      <x:c r="E34" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">喝迎宾酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F34" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">慢慢品尝，味道别有一番风味</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E34" s="1" t="str">
+        <x:v>喝迎宾酒</x:v>
+      </x:c>
+      <x:c r="F34" s="1" t="str">
+        <x:v>慢慢品尝，味道别有一番风味</x:v>
+      </x:c>
+      <x:c r="H34"/>
       <x:c r="I34" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -3120,6 +3027,7 @@
       <x:c r="M34" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N34"/>
     </x:row>
     <x:row r="35">
       <x:c r="B35" s="1" t="inlineStr">
@@ -3137,16 +3045,13 @@
           <x:t xml:space="preserve">opt_new_event_choice</x:t>
         </x:is>
       </x:c>
-      <x:c r="E35" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">为随机两个食物添加风味</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F35" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">为随机 2 个不同食物添加随机风味，优先选择没有风味的食物。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E35" s="1" t="str">
+        <x:v>为随机两个食物添加风味</x:v>
+      </x:c>
+      <x:c r="F35" s="1" t="str">
+        <x:v>为随机 2 个不同食物添加随机风味，优先选择没有风味的食物。</x:v>
+      </x:c>
+      <x:c r="H35"/>
       <x:c r="I35" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddRandomRecipeFlavor</x:t>
@@ -3166,6 +3071,7 @@
       <x:c r="M35" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N35"/>
     </x:row>
     <x:row r="36">
       <x:c r="B36" s="1" t="inlineStr">
@@ -3178,16 +3084,13 @@
           <x:t xml:space="preserve">ev_new_event</x:t>
         </x:is>
       </x:c>
-      <x:c r="E36" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">吃蔬菜棒蘸酱</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F36" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">蔬菜棒很新鲜，酱咸香合适</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E36" s="1" t="str">
+        <x:v>吃蔬菜棒蘸酱</x:v>
+      </x:c>
+      <x:c r="F36" s="1" t="str">
+        <x:v>蔬菜棒很新鲜，酱咸香合适</x:v>
+      </x:c>
+      <x:c r="H36"/>
       <x:c r="I36" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -3207,6 +3110,7 @@
       <x:c r="M36" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N36"/>
     </x:row>
     <x:row r="37">
       <x:c r="B37" s="1" t="inlineStr">
@@ -3219,16 +3123,13 @@
           <x:t xml:space="preserve">ev_new_event</x:t>
         </x:is>
       </x:c>
-      <x:c r="E37" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">吃汉堡肉</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F37" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">感觉味道怪怪的，身体有些不舒服</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E37" s="1" t="str">
+        <x:v>吃汉堡肉</x:v>
+      </x:c>
+      <x:c r="F37" s="1" t="str">
+        <x:v>感觉味道怪怪的，身体有些不舒服</x:v>
+      </x:c>
+      <x:c r="H37"/>
       <x:c r="I37" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -3248,6 +3149,7 @@
       <x:c r="M37" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N37"/>
     </x:row>
     <x:row r="38">
       <x:c r="B38" s="1" t="inlineStr">
@@ -3265,16 +3167,13 @@
           <x:t xml:space="preserve">opt_new_event_choice_3</x:t>
         </x:is>
       </x:c>
-      <x:c r="E38" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">对食物的理解提升了！更容易获得更好的食物</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F38" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">食物奖励隐藏分永久 +5。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E38" s="1" t="str">
+        <x:v>对食物的理解提升了！更容易获得更好的食物</x:v>
+      </x:c>
+      <x:c r="F38" s="1" t="str">
+        <x:v>食物奖励隐藏分永久 +5。</x:v>
+      </x:c>
+      <x:c r="H38"/>
       <x:c r="I38" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddHiddenScoreOffset</x:t>
@@ -3294,6 +3193,7 @@
       <x:c r="M38" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N38"/>
     </x:row>
     <x:row r="39">
       <x:c r="B39" s="1" t="inlineStr">
@@ -3311,16 +3211,13 @@
           <x:t xml:space="preserve">opt_new_event_choice_4</x:t>
         </x:is>
       </x:c>
-      <x:c r="E39" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">休息两天，店内活动适当调整</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F39" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">身体不舒服就应该休息啦，稍后调整下店里活动的安排就好</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E39" s="1" t="str">
+        <x:v>休息两天，店内活动适当调整</x:v>
+      </x:c>
+      <x:c r="F39" s="1" t="str">
+        <x:v>身体不舒服就应该休息啦，稍后调整下店里活动的安排就好</x:v>
+      </x:c>
+      <x:c r="H39"/>
       <x:c r="I39" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -3340,6 +3237,7 @@
       <x:c r="M39" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N39"/>
     </x:row>
     <x:row r="40">
       <x:c r="B40" s="1" t="inlineStr">
@@ -3357,16 +3255,13 @@
           <x:t xml:space="preserve">opt_new_event_choice_4</x:t>
         </x:is>
       </x:c>
-      <x:c r="E40" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">坚持工作</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F40" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">顾客听说了店长的事迹，纷纷投来感动的目光，一个小孩子捧着一个装饰品给你</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E40" s="1" t="str">
+        <x:v>坚持工作</x:v>
+      </x:c>
+      <x:c r="F40" s="1" t="str">
+        <x:v>顾客听说了店长的事迹，纷纷投来感动的目光，一个小孩子捧着一个[term]装饰品[/term]给你</x:v>
+      </x:c>
+      <x:c r="H40"/>
       <x:c r="I40" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -3386,6 +3281,7 @@
       <x:c r="M40" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N40"/>
     </x:row>
     <x:row r="41">
       <x:c r="B41" s="1" t="inlineStr">
@@ -3403,16 +3299,13 @@
           <x:t xml:space="preserve">opt_new_event_choice_6</x:t>
         </x:is>
       </x:c>
-      <x:c r="E41" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">获得两个调整单类的消耗品</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F41" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">从全部调整单中放回随机获得 2 个。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E41" s="1" t="str">
+        <x:v>获得两个调整单类的[term]消耗品[/term]</x:v>
+      </x:c>
+      <x:c r="F41" s="1" t="str">
+        <x:v>从全部调整单中放回随机获得 2 个。</x:v>
+      </x:c>
+      <x:c r="H41"/>
       <x:c r="I41" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GrantRandomActiveItems</x:t>
@@ -3432,6 +3325,7 @@
       <x:c r="M41" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N41"/>
     </x:row>
     <x:row r="42">
       <x:c r="B42" s="1" t="inlineStr">
@@ -3449,16 +3343,13 @@
           <x:t xml:space="preserve">opt_new_event_choice_7</x:t>
         </x:is>
       </x:c>
-      <x:c r="E42" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">获得一个装饰品</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F42" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">随机获得 1 个非诅咒装饰品。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E42" s="1" t="str">
+        <x:v>获得一个[term]装饰品[/term]</x:v>
+      </x:c>
+      <x:c r="F42" s="1" t="str">
+        <x:v>随机获得 1 个非诅咒[term]装饰品[/term]。</x:v>
+      </x:c>
+      <x:c r="H42"/>
       <x:c r="I42" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GrantRandomPassiveItems</x:t>
@@ -3478,6 +3369,7 @@
       <x:c r="M42" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N42"/>
     </x:row>
     <x:row r="43">
       <x:c r="B43" s="1" t="inlineStr">
@@ -3490,16 +3382,13 @@
           <x:t xml:space="preserve">ev_crossroad_sign</x:t>
         </x:is>
       </x:c>
-      <x:c r="E43" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">第一关：品尝白蘑菇</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F43" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">先从白色蘑菇开始。每次安全尝完都可以见好就收，也可以继续挑战下一种蘑菇。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E43" s="1" t="str">
+        <x:v>第一关：品尝白蘑菇</x:v>
+      </x:c>
+      <x:c r="F43" s="1" t="str">
+        <x:v>先从白色蘑菇开始。每次安全尝完都可以见好就收，也可以继续挑战下一种蘑菇。</x:v>
+      </x:c>
+      <x:c r="H43"/>
       <x:c r="I43" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -3519,6 +3408,7 @@
       <x:c r="M43" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N43"/>
     </x:row>
     <x:row r="44">
       <x:c r="B44" s="1" t="inlineStr">
@@ -3531,16 +3421,13 @@
           <x:t xml:space="preserve">ev_crossroad_sign</x:t>
         </x:is>
       </x:c>
-      <x:c r="E44" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">不参加了</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F44" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">明智的选择，还是一朝被蛇咬，十年怕井绳呢</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E44" s="1" t="str">
+        <x:v>不参加了</x:v>
+      </x:c>
+      <x:c r="F44" s="1" t="str">
+        <x:v>明智的选择，还是一朝被蛇咬，十年怕井绳呢</x:v>
+      </x:c>
+      <x:c r="H44"/>
       <x:c r="I44" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -3560,6 +3447,7 @@
       <x:c r="M44" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N44"/>
     </x:row>
     <x:row r="45">
       <x:c r="B45" s="1" t="inlineStr">
@@ -3577,16 +3465,13 @@
           <x:t xml:space="preserve">opt_sign_secondhand</x:t>
         </x:is>
       </x:c>
-      <x:c r="E45" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">参与奖：金币+50</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F45" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">获得 50 金币。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E45" s="1" t="str">
+        <x:v>参与奖：[gold]金币+50[/gold]</x:v>
+      </x:c>
+      <x:c r="F45" s="1" t="str">
+        <x:v>获得 [gold]50 金币[/gold]。</x:v>
+      </x:c>
+      <x:c r="H45"/>
       <x:c r="I45" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GainGold</x:t>
@@ -3606,6 +3491,7 @@
       <x:c r="M45" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N45"/>
     </x:row>
     <x:row r="46">
       <x:c r="B46" s="1" t="inlineStr">
@@ -3623,16 +3509,13 @@
           <x:t xml:space="preserve">opt_sign_food_street</x:t>
         </x:is>
       </x:c>
-      <x:c r="E46" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">去抢救，金币-20</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F46" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">你被紧急送往医院抢救。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E46" s="1" t="str">
+        <x:v>去抢救，[gold]金币-20[/gold]</x:v>
+      </x:c>
+      <x:c r="F46" s="1" t="str">
+        <x:v>你被紧急送往医院抢救。</x:v>
+      </x:c>
+      <x:c r="H46"/>
       <x:c r="I46" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">LoseEscalatingGold</x:t>
@@ -3652,10 +3535,8 @@
       <x:c r="M46" s="2" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="N46" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">白色蘑菇刚入口，舌尖便开始发麻，眼前的餐厅转了起来。</x:t>
-        </x:is>
+      <x:c r="N46" s="2" t="str">
+        <x:v>白色蘑菇刚入口，舌尖便开始发麻，眼前的餐厅转了起来。</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -3674,16 +3555,13 @@
           <x:t xml:space="preserve">opt_sign_food_street</x:t>
         </x:is>
       </x:c>
-      <x:c r="E47" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">白色蘑菇很安全</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F47" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">白色蘑菇鲜甜爽脆。要带着这份好运离开，还是继续品尝红色蘑菇？</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E47" s="1" t="str">
+        <x:v>白色蘑菇很安全</x:v>
+      </x:c>
+      <x:c r="F47" s="1" t="str">
+        <x:v>白色蘑菇鲜甜爽脆。要带着这份好运离开，还是继续品尝红色蘑菇？</x:v>
+      </x:c>
+      <x:c r="H47"/>
       <x:c r="I47" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -3703,10 +3581,8 @@
       <x:c r="M47" s="2" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="N47" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">白色蘑菇清甜鲜嫩，吃完后身体毫无异样。</x:t>
-        </x:is>
+      <x:c r="N47" s="2" t="str">
+        <x:v>白色蘑菇清甜鲜嫩，吃完后身体毫无异样。</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -3725,16 +3601,13 @@
           <x:t xml:space="preserve">opt_mushroom_white_safe</x:t>
         </x:is>
       </x:c>
-      <x:c r="E48" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">见好就收，领取 70 金币</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F48" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">你把剩下的白色蘑菇卖给了识货的客人，获得 70 金币。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E48" s="1" t="str">
+        <x:v>见好就收，领取 [gold]70 金币[/gold]</x:v>
+      </x:c>
+      <x:c r="F48" s="1" t="str">
+        <x:v>你把剩下的白色蘑菇卖给了识货的客人，获得 [gold]70 金币[/gold]。</x:v>
+      </x:c>
+      <x:c r="H48"/>
       <x:c r="I48" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GainGold</x:t>
@@ -3754,6 +3627,7 @@
       <x:c r="M48" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N48"/>
     </x:row>
     <x:row r="49">
       <x:c r="B49" s="1" t="inlineStr">
@@ -3771,16 +3645,13 @@
           <x:t xml:space="preserve">opt_mushroom_white_safe</x:t>
         </x:is>
       </x:c>
-      <x:c r="E49" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">第二关：品尝红蘑菇</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F49" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">你夹起了颜色鲜艳的红色蘑菇。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E49" s="1" t="str">
+        <x:v>第二关：品尝红蘑菇</x:v>
+      </x:c>
+      <x:c r="F49" s="1" t="str">
+        <x:v>你夹起了颜色鲜艳的红色蘑菇。</x:v>
+      </x:c>
+      <x:c r="H49"/>
       <x:c r="I49" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -3800,6 +3671,7 @@
       <x:c r="M49" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N49"/>
     </x:row>
     <x:row r="50">
       <x:c r="B50" s="1" t="inlineStr">
@@ -3817,16 +3689,13 @@
           <x:t xml:space="preserve">opt_mushroom_try_red</x:t>
         </x:is>
       </x:c>
-      <x:c r="E50" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">去抢救，金币-40</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F50" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">毒性来势汹汹，你再次被送往医院抢救。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E50" s="1" t="str">
+        <x:v>去抢救，[gold]金币-40[/gold]</x:v>
+      </x:c>
+      <x:c r="F50" s="1" t="str">
+        <x:v>毒性来势汹汹，你再次被送往医院抢救。</x:v>
+      </x:c>
+      <x:c r="H50"/>
       <x:c r="I50" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">LoseEscalatingGold</x:t>
@@ -3846,10 +3715,8 @@
       <x:c r="M50" s="2" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="N50" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">红色蘑菇辛辣得反常，没过多久，你的视线便开始模糊。</x:t>
-        </x:is>
+      <x:c r="N50" s="2" t="str">
+        <x:v>红色蘑菇辛辣得反常，没过多久，你的视线便开始模糊。</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -3868,16 +3735,13 @@
           <x:t xml:space="preserve">opt_mushroom_try_red</x:t>
         </x:is>
       </x:c>
-      <x:c r="E51" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">红色蘑菇也很安全</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F51" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">红色蘑菇带着微微果香。现在收手已经收获颇丰，或者再尝最后的绿色蘑菇。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E51" s="1" t="str">
+        <x:v>红色蘑菇也很安全</x:v>
+      </x:c>
+      <x:c r="F51" s="1" t="str">
+        <x:v>红色蘑菇带着微微果香。现在收手已经收获颇丰，或者再尝最后的绿色蘑菇。</x:v>
+      </x:c>
+      <x:c r="H51"/>
       <x:c r="I51" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -3897,10 +3761,8 @@
       <x:c r="M51" s="2" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="N51" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">红色蘑菇入口微辣，却没有任何毒性，你又安全过了一关。</x:t>
-        </x:is>
+      <x:c r="N51" s="2" t="str">
+        <x:v>红色蘑菇入口微辣，却没有任何毒性，你又安全过了一关。</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -3919,16 +3781,13 @@
           <x:t xml:space="preserve">opt_mushroom_red_safe</x:t>
         </x:is>
       </x:c>
-      <x:c r="E52" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">稳妥收手，领取 120 金币</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F52" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">你把剩余蘑菇高价转让，获得 120 金币。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E52" s="1" t="str">
+        <x:v>稳妥收手，领取 [gold]120 金币[/gold]</x:v>
+      </x:c>
+      <x:c r="F52" s="1" t="str">
+        <x:v>你把剩余蘑菇高价转让，获得 [gold]120 金币[/gold]。</x:v>
+      </x:c>
+      <x:c r="H52"/>
       <x:c r="I52" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GainGold</x:t>
@@ -3948,6 +3807,7 @@
       <x:c r="M52" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N52"/>
     </x:row>
     <x:row r="53">
       <x:c r="B53" s="1" t="inlineStr">
@@ -3965,16 +3825,13 @@
           <x:t xml:space="preserve">opt_mushroom_red_safe</x:t>
         </x:is>
       </x:c>
-      <x:c r="E53" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">第三关：品尝绿蘑菇</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F53" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">最后一朵绿色蘑菇散发着危险又迷人的清香。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E53" s="1" t="str">
+        <x:v>第三关：品尝绿蘑菇</x:v>
+      </x:c>
+      <x:c r="F53" s="1" t="str">
+        <x:v>最后一朵绿色蘑菇散发着危险又迷人的清香。</x:v>
+      </x:c>
+      <x:c r="H53"/>
       <x:c r="I53" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -3994,6 +3851,7 @@
       <x:c r="M53" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N53"/>
     </x:row>
     <x:row r="54">
       <x:c r="B54" s="1" t="inlineStr">
@@ -4011,16 +3869,13 @@
           <x:t xml:space="preserve">opt_mushroom_try_green</x:t>
         </x:is>
       </x:c>
-      <x:c r="E54" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">去icu抢救，金币-60</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F54" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">你倒在餐桌旁，被火速送往医院抢救。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E54" s="1" t="str">
+        <x:v>去icu抢救，[gold]金币-60[/gold]</x:v>
+      </x:c>
+      <x:c r="F54" s="1" t="str">
+        <x:v>你倒在餐桌旁，被火速送往医院抢救。</x:v>
+      </x:c>
+      <x:c r="H54"/>
       <x:c r="I54" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">LoseEscalatingGold</x:t>
@@ -4040,10 +3895,8 @@
       <x:c r="M54" s="2" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="N54" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">绿色蘑菇鲜得惊人——紧接着，房间里的所有东西都变成了绿色。</x:t>
-        </x:is>
+      <x:c r="N54" s="2" t="str">
+        <x:v>绿色蘑菇鲜得惊人——紧接着，房间里的所有东西都变成了绿色。</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -4062,16 +3915,13 @@
           <x:t xml:space="preserve">opt_mushroom_try_green</x:t>
         </x:is>
       </x:c>
-      <x:c r="E55" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">大获成功！获得传奇装饰品</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F55" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">你完整记住了三种蘑菇的风味，并获得 1 个传奇装饰品。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E55" s="1" t="str">
+        <x:v>大获成功！获得传奇[term]装饰品[/term]</x:v>
+      </x:c>
+      <x:c r="F55" s="1" t="str">
+        <x:v>你完整记住了三种蘑菇的风味，并获得 1 个传奇[term]装饰品[/term]。</x:v>
+      </x:c>
+      <x:c r="H55"/>
       <x:c r="I55" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GainLegendaryItem</x:t>
@@ -4091,10 +3941,8 @@
       <x:c r="M55" s="2" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="N55" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">绿色蘑菇化成一股清香。你连过三关，主厨惊讶地捧出了珍藏礼物。</x:t>
-        </x:is>
+      <x:c r="N55" s="2" t="str">
+        <x:v>绿色蘑菇化成一股清香。你连过三关，主厨惊讶地捧出了珍藏礼物。</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -4108,16 +3956,13 @@
           <x:t xml:space="preserve">ev_last_supper</x:t>
         </x:is>
       </x:c>
-      <x:c r="E56" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">举杯饮酒</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F56" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">你举杯平息了争执。众厨师感谢你缓和气氛，约好下次到你的餐厅聚餐。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E56" s="1" t="str">
+        <x:v>举杯饮酒</x:v>
+      </x:c>
+      <x:c r="F56" s="1" t="str">
+        <x:v>你举杯平息了争执。众厨师感谢你缓和气氛，约好下次到你的餐厅聚餐。</x:v>
+      </x:c>
+      <x:c r="H56"/>
       <x:c r="I56" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -4137,6 +3982,7 @@
       <x:c r="M56" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N56"/>
     </x:row>
     <x:row r="57">
       <x:c r="B57" s="1" t="inlineStr">
@@ -4154,16 +4000,13 @@
           <x:t xml:space="preserve">opt_last_supper_toast</x:t>
         </x:is>
       </x:c>
-      <x:c r="E57" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">下次营业金币+60%</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F57" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">众厨师如约来访。下一次营业获得的基础金币提高60%。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E57" s="1" t="str">
+        <x:v>下次营业[gold]金币+60%[/gold]</x:v>
+      </x:c>
+      <x:c r="F57" s="1" t="str">
+        <x:v>众厨师如约来访。下一次营业获得的基础[gold]金币[/gold]提高[gold]60%[/gold]。</x:v>
+      </x:c>
+      <x:c r="H57"/>
       <x:c r="I57" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddBusinessGoldPct</x:t>
@@ -4183,6 +4026,7 @@
       <x:c r="M57" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N57"/>
     </x:row>
     <x:row r="58">
       <x:c r="B58" s="1" t="inlineStr">
@@ -4195,16 +4039,13 @@
           <x:t xml:space="preserve">ev_last_supper</x:t>
         </x:is>
       </x:c>
-      <x:c r="E58" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">指认别人</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F58" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">你指出那位袖口沾着对面餐厅印泥的厨师。他只好交出收到的定金。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E58" s="1" t="str">
+        <x:v>指认别人</x:v>
+      </x:c>
+      <x:c r="F58" s="1" t="str">
+        <x:v>你指出那位袖口沾着对面餐厅印泥的厨师。他只好交出收到的定金。</x:v>
+      </x:c>
+      <x:c r="H58"/>
       <x:c r="I58" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -4224,6 +4065,7 @@
       <x:c r="M58" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N58"/>
     </x:row>
     <x:row r="59">
       <x:c r="B59" s="1" t="inlineStr">
@@ -4241,16 +4083,13 @@
           <x:t xml:space="preserve">opt_last_supper_accuse</x:t>
         </x:is>
       </x:c>
-      <x:c r="E59" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">收下定金</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F59" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">获得100金币。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E59" s="1" t="str">
+        <x:v>收下定金</x:v>
+      </x:c>
+      <x:c r="F59" s="1" t="str">
+        <x:v>获得[gold]100金币[/gold]。</x:v>
+      </x:c>
+      <x:c r="H59"/>
       <x:c r="I59" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GainGold</x:t>
@@ -4270,6 +4109,7 @@
       <x:c r="M59" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N59"/>
     </x:row>
     <x:row r="60">
       <x:c r="B60" s="1" t="inlineStr">
@@ -4282,16 +4122,13 @@
           <x:t xml:space="preserve">ev_last_supper</x:t>
         </x:is>
       </x:c>
-      <x:c r="E60" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">分食面包</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F60" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">你把面包分给众人。十二位厨师各自用拿手菜回礼，你从中带走了两道。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E60" s="1" t="str">
+        <x:v>分食面包</x:v>
+      </x:c>
+      <x:c r="F60" s="1" t="str">
+        <x:v>你把面包分给众人。十二位厨师各自用拿手菜回礼，你从中带走了两道。</x:v>
+      </x:c>
+      <x:c r="H60"/>
       <x:c r="I60" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -4311,6 +4148,7 @@
       <x:c r="M60" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N60"/>
     </x:row>
     <x:row r="61">
       <x:c r="B61" s="1" t="inlineStr">
@@ -4328,16 +4166,13 @@
           <x:t xml:space="preserve">opt_last_supper_share</x:t>
         </x:is>
       </x:c>
-      <x:c r="E61" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">收下两道回礼</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F61" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">从众人的回礼中获得2个随机风味食物。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E61" s="1" t="str">
+        <x:v>收下两道回礼</x:v>
+      </x:c>
+      <x:c r="F61" s="1" t="str">
+        <x:v>从众人的回礼中获得2个随机风味食物。</x:v>
+      </x:c>
+      <x:c r="H61"/>
       <x:c r="I61" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GainRandomFlavoredDishes</x:t>
@@ -4357,6 +4192,7 @@
       <x:c r="M61" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N61"/>
     </x:row>
     <x:row r="62">
       <x:c r="B62" s="1" t="inlineStr">
@@ -4369,16 +4205,13 @@
           <x:t xml:space="preserve">ev_twin_peaks_diner</x:t>
         </x:is>
       </x:c>
-      <x:c r="E62" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">喝黑咖啡</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F62" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">咖啡苦得恰到好处，你一下清醒过来，连夜整理了下一次营业安排。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E62" s="1" t="str">
+        <x:v>喝黑咖啡</x:v>
+      </x:c>
+      <x:c r="F62" s="1" t="str">
+        <x:v>咖啡苦得恰到好处，你一下清醒过来，连夜整理了下一次营业安排。</x:v>
+      </x:c>
+      <x:c r="H62"/>
       <x:c r="I62" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -4398,6 +4231,7 @@
       <x:c r="M62" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N62"/>
     </x:row>
     <x:row r="63">
       <x:c r="B63" s="1" t="inlineStr">
@@ -4415,24 +4249,25 @@
           <x:t xml:space="preserve">opt_twin_peaks_coffee</x:t>
         </x:is>
       </x:c>
-      <x:c r="E63" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">下两次营业金币+60%</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F63" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">下两次营业基础金币×1.6。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I63" s="1" t="str">
-        <x:v>AddBusinessGoldPct</x:v>
+      <x:c r="E63" s="1" t="str">
+        <x:v>下两次营业[gold]金币+60%[/gold]</x:v>
+      </x:c>
+      <x:c r="F63" s="1" t="str">
+        <x:v>下两次营业基础[gold]金币[/gold]×1.6。</x:v>
+      </x:c>
+      <x:c r="H63"/>
+      <x:c r="I63" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">AddBusinessGoldPct</x:t>
+        </x:is>
       </x:c>
       <x:c r="J63" s="1" t="n">
         <x:v>0.6</x:v>
       </x:c>
-      <x:c r="K63" s="1" t="str">
-        <x:v>Next:2</x:v>
+      <x:c r="K63" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">Next:2</x:t>
+        </x:is>
       </x:c>
       <x:c r="L63" s="1" t="n">
         <x:v>1</x:v>
@@ -4440,6 +4275,7 @@
       <x:c r="M63" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N63"/>
     </x:row>
     <x:row r="64">
       <x:c r="B64" s="1" t="inlineStr">
@@ -4452,16 +4288,13 @@
           <x:t xml:space="preserve">ev_twin_peaks_diner</x:t>
         </x:is>
       </x:c>
-      <x:c r="E64" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">点樱桃派</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F64" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">樱桃派美味可口，一天的疲惫一扫而空</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E64" s="1" t="str">
+        <x:v>点樱桃派</x:v>
+      </x:c>
+      <x:c r="F64" s="1" t="str">
+        <x:v>樱桃派美味可口，一天的疲惫一扫而空</x:v>
+      </x:c>
+      <x:c r="H64"/>
       <x:c r="I64" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -4481,6 +4314,7 @@
       <x:c r="M64" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N64"/>
     </x:row>
     <x:row r="65">
       <x:c r="B65" s="1" t="inlineStr">
@@ -4501,19 +4335,22 @@
       <x:c r="E65" s="1" t="str">
         <x:v>恢复1颗红心</x:v>
       </x:c>
-      <x:c r="F65" t="str">
+      <x:c r="F65" s="1" t="str">
         <x:v>恢复1颗红心，不超过红心上限。</x:v>
       </x:c>
-      <x:c r="G65"/>
       <x:c r="H65"/>
-      <x:c r="I65" s="1" t="str">
-        <x:v>RestoreHearts</x:v>
+      <x:c r="I65" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RestoreHearts</x:t>
+        </x:is>
       </x:c>
       <x:c r="J65" s="1" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="K65" s="1" t="str">
-        <x:v>-</x:v>
+      <x:c r="K65" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">-</x:t>
+        </x:is>
       </x:c>
       <x:c r="L65" s="1" t="n">
         <x:v>1</x:v>
@@ -4521,6 +4358,7 @@
       <x:c r="M65" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N65"/>
     </x:row>
     <x:row r="66">
       <x:c r="B66" s="1" t="inlineStr">
@@ -4533,16 +4371,13 @@
           <x:t xml:space="preserve">ev_twin_peaks_diner</x:t>
         </x:is>
       </x:c>
-      <x:c r="E66" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">听听木头怎么说</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F66" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">木头女士转述了一段古怪配方。你回去试了一夜，食谱里原有的菜竟都变得更好吃了。</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E66" s="1" t="str">
+        <x:v>听听木头怎么说</x:v>
+      </x:c>
+      <x:c r="F66" s="1" t="str">
+        <x:v>木头女士转述了一段古怪配方。你回去试了一夜，食谱里原有的菜竟都变得更好吃了。</x:v>
+      </x:c>
+      <x:c r="H66"/>
       <x:c r="I66" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -4562,6 +4397,7 @@
       <x:c r="M66" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N66"/>
     </x:row>
     <x:row r="67">
       <x:c r="B67" s="1" t="inlineStr">
@@ -4579,16 +4415,13 @@
           <x:t xml:space="preserve">opt_twin_peaks_log</x:t>
         </x:is>
       </x:c>
-      <x:c r="E67" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">所有食物分数永久+10</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="F67" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">触发时食谱中已有的全部食物永久分数+10</x:t>
-        </x:is>
-      </x:c>
+      <x:c r="E67" s="1" t="str">
+        <x:v>[context]所有[/context]食物[strong]分数[/strong]永久[score]+10[/score]</x:v>
+      </x:c>
+      <x:c r="F67" s="1" t="str">
+        <x:v>触发时食谱中已有的全部食物永久[strong]分数[/strong][score]+10[/score]</x:v>
+      </x:c>
+      <x:c r="H67"/>
       <x:c r="I67" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddAllRecipeScoreFlat</x:t>
@@ -4608,213 +4441,249 @@
       <x:c r="M67" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
+      <x:c r="N67"/>
     </x:row>
     <x:row r="68">
-      <x:c r="A68"/>
-      <x:c r="B68" t="str">
-        <x:v>opt_chuka_ichiban_fried_rice</x:v>
-      </x:c>
-      <x:c r="C68" t="str">
-        <x:v>ev_chuka_ichiban_trial</x:v>
-      </x:c>
-      <x:c r="D68"/>
-      <x:c r="E68" t="str">
-        <x:v>颠一锅黄金炒饭</x:v>
-      </x:c>
-      <x:c r="F68" t="str">
+      <x:c r="B68" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_chuka_ichiban_fried_rice</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C68" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ev_chuka_ichiban_trial</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E68" s="1" t="str">
+        <x:v>黄金炒饭</x:v>
+      </x:c>
+      <x:c r="F68" s="1" t="str">
         <x:v>蛋液裹住每一粒米，揭盖时金光一闪。旅人把碗吃得干干净净，还在桌上留下赏钱。</x:v>
       </x:c>
-      <x:c r="G68"/>
       <x:c r="H68"/>
-      <x:c r="I68" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="J68" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K68" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="L68" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M68" t="n">
+      <x:c r="I68" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J68" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K68" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">-</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L68" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M68" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N68"/>
     </x:row>
     <x:row r="69">
-      <x:c r="A69"/>
-      <x:c r="B69" t="str">
-        <x:v>opt_chuka_ichiban_fried_rice_reward</x:v>
-      </x:c>
-      <x:c r="C69" t="str">
-        <x:v>ev_chuka_ichiban_trial</x:v>
-      </x:c>
-      <x:c r="D69" t="str">
-        <x:v>opt_chuka_ichiban_fried_rice</x:v>
-      </x:c>
-      <x:c r="E69" t="str">
-        <x:v>收下80金币赏钱</x:v>
-      </x:c>
-      <x:c r="F69" t="str">
-        <x:v>旅人因黄金炒饭心满意足，留下80金币。</x:v>
-      </x:c>
-      <x:c r="G69"/>
+      <x:c r="B69" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_chuka_ichiban_fried_rice_reward</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C69" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ev_chuka_ichiban_trial</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D69" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_chuka_ichiban_fried_rice</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E69" s="1" t="str">
+        <x:v>收下[gold]80金币[/gold]赏钱</x:v>
+      </x:c>
+      <x:c r="F69" s="1" t="str">
+        <x:v>旅人因黄金炒饭心满意足，留下[gold]80金币[/gold]。</x:v>
+      </x:c>
       <x:c r="H69"/>
-      <x:c r="I69" t="str">
-        <x:v>GainGold</x:v>
-      </x:c>
-      <x:c r="J69" t="n">
+      <x:c r="I69" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">GainGold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J69" s="1" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="K69" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="L69" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M69" t="n">
+      <x:c r="K69" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">-</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L69" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M69" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N69"/>
     </x:row>
     <x:row r="70">
-      <x:c r="A70"/>
-      <x:c r="B70" t="str">
-        <x:v>opt_chuka_ichiban_mapo_tofu</x:v>
-      </x:c>
-      <x:c r="C70" t="str">
-        <x:v>ev_chuka_ichiban_trial</x:v>
-      </x:c>
-      <x:c r="D70"/>
-      <x:c r="E70" t="str">
-        <x:v>补齐麻婆豆腐的第六味</x:v>
-      </x:c>
-      <x:c r="F70" t="str">
+      <x:c r="B70" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_chuka_ichiban_mapo_tofu</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C70" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ev_chuka_ichiban_trial</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E70" s="1" t="str">
+        <x:v>麻婆豆腐</x:v>
+      </x:c>
+      <x:c r="F70" s="1" t="str">
         <x:v>你把大豆炒得酥香，让麻、辣、香、色、烫之外又添一层爽脆。小当家笑着点了点头。</x:v>
       </x:c>
-      <x:c r="G70"/>
       <x:c r="H70"/>
-      <x:c r="I70" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="J70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K70" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="L70" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M70" t="n">
+      <x:c r="I70" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J70" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K70" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">-</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L70" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M70" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N70"/>
     </x:row>
     <x:row r="71">
-      <x:c r="A71"/>
-      <x:c r="B71" t="str">
-        <x:v>opt_chuka_ichiban_mapo_tofu_reward</x:v>
-      </x:c>
-      <x:c r="C71" t="str">
-        <x:v>ev_chuka_ichiban_trial</x:v>
-      </x:c>
-      <x:c r="D71" t="str">
-        <x:v>opt_chuka_ichiban_mapo_tofu</x:v>
-      </x:c>
-      <x:c r="E71" t="str">
-        <x:v>给1个食物添加随机风味</x:v>
-      </x:c>
-      <x:c r="F71" t="str">
-        <x:v>从“酥”的灵感中举一反三，为食谱中1个食物添加随机风味。</x:v>
-      </x:c>
-      <x:c r="G71"/>
+      <x:c r="B71" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_chuka_ichiban_mapo_tofu_reward</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C71" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ev_chuka_ichiban_trial</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D71" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_chuka_ichiban_mapo_tofu</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E71" s="1" t="str">
+        <x:v>获得2个风味强化箱</x:v>
+      </x:c>
+      <x:c r="F71" s="1" t="str">
+        <x:v>你从“酥”的灵感中举一反三，从六种风味强化箱中随机获得2个，可能重复。</x:v>
+      </x:c>
       <x:c r="H71"/>
-      <x:c r="I71" t="str">
-        <x:v>AddRandomRecipeFlavor</x:v>
-      </x:c>
-      <x:c r="J71" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K71" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="L71" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M71" t="n">
+      <x:c r="I71" s="1" t="str">
+        <x:v>GrantRandomActiveItems</x:v>
+      </x:c>
+      <x:c r="J71" s="1" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="K71" s="1" t="str">
+        <x:v>Ids:item_active_season_sweet,item_active_season_bitter,item_active_season_umami,item_active_season_numb,item_active_season_sour,item_active_season_salty|Replace</x:v>
+      </x:c>
+      <x:c r="L71" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M71" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N71"/>
     </x:row>
     <x:row r="72">
-      <x:c r="A72"/>
-      <x:c r="B72" t="str">
-        <x:v>opt_chuka_ichiban_dumpling</x:v>
-      </x:c>
-      <x:c r="C72" t="str">
-        <x:v>ev_chuka_ichiban_trial</x:v>
-      </x:c>
-      <x:c r="D72"/>
-      <x:c r="E72" t="str">
-        <x:v>蒸一笼大宇宙烧卖</x:v>
-      </x:c>
-      <x:c r="F72" t="str">
+      <x:c r="B72" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_chuka_ichiban_dumpling</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C72" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ev_chuka_ichiban_trial</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E72" s="1" t="str">
+        <x:v>大宇宙烧卖</x:v>
+      </x:c>
+      <x:c r="F72" s="1" t="str">
         <x:v>一只烧卖占满了蒸笼，切开正好够全店分。众人围桌大笑，收档前的疲惫一扫而空。</x:v>
       </x:c>
-      <x:c r="G72"/>
       <x:c r="H72"/>
-      <x:c r="I72" t="str">
-        <x:v>None</x:v>
-      </x:c>
-      <x:c r="J72" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K72" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="L72" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M72" t="n">
+      <x:c r="I72" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J72" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K72" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">-</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L72" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M72" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N72"/>
     </x:row>
     <x:row r="73">
-      <x:c r="A73"/>
-      <x:c r="B73" t="str">
-        <x:v>opt_chuka_ichiban_dumpling_reward</x:v>
-      </x:c>
-      <x:c r="C73" t="str">
-        <x:v>ev_chuka_ichiban_trial</x:v>
-      </x:c>
-      <x:c r="D73" t="str">
-        <x:v>opt_chuka_ichiban_dumpling</x:v>
-      </x:c>
-      <x:c r="E73" t="str">
+      <x:c r="B73" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_chuka_ichiban_dumpling_reward</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C73" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ev_chuka_ichiban_trial</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D73" s="2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_chuka_ichiban_dumpling</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E73" s="1" t="str">
         <x:v>恢复1颗红心</x:v>
       </x:c>
-      <x:c r="F73" t="str">
+      <x:c r="F73" s="1" t="str">
         <x:v>大家分享烧卖后重新打起精神。恢复1颗红心，不超过红心上限。</x:v>
       </x:c>
-      <x:c r="G73"/>
       <x:c r="H73"/>
-      <x:c r="I73" t="str">
-        <x:v>RestoreHearts</x:v>
-      </x:c>
-      <x:c r="J73" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K73" t="str">
-        <x:v>-</x:v>
-      </x:c>
-      <x:c r="L73" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M73" t="n">
+      <x:c r="I73" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">RestoreHearts</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J73" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K73" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">-</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L73" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M73" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="N73"/>

--- a/GourmetProject/GameConfig/Datas/event.xlsx
+++ b/GourmetProject/GameConfig/Datas/event.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event" sheetId="1" r:id="Ra26460acd8d2445a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event_option" sheetId="2" r:id="R212b18f305094f95"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event" sheetId="1" r:id="R8a547c5be26c4e0d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="event_option" sheetId="2" r:id="R7845934732ef4d03"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1031,8 +1031,10 @@
           <x:t xml:space="preserve">name</x:t>
         </x:is>
       </x:c>
-      <x:c r="D1" t="str">
-        <x:v>desc</x:v>
+      <x:c r="D1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">desc</x:t>
+        </x:is>
       </x:c>
       <x:c r="E1" t="inlineStr">
         <x:is>
@@ -1059,8 +1061,10 @@
           <x:t xml:space="preserve">bgSprite</x:t>
         </x:is>
       </x:c>
-      <x:c r="J1" t="str">
-        <x:v>resultText</x:v>
+      <x:c r="J1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">resultText</x:t>
+        </x:is>
       </x:c>
       <x:c r="K1" t="inlineStr">
         <x:is>
@@ -1094,8 +1098,10 @@
           <x:t xml:space="preserve">事件名称</x:t>
         </x:is>
       </x:c>
-      <x:c r="D2" t="str">
-        <x:v>事件描述(初始/根页正文)</x:v>
+      <x:c r="D2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">事件描述(初始/根页正文)</x:t>
+        </x:is>
       </x:c>
       <x:c r="E2" t="inlineStr">
         <x:is>
@@ -1122,8 +1128,10 @@
           <x:t xml:space="preserve">事件插画 Sprite（Resources 路径，空=不显示）</x:t>
         </x:is>
       </x:c>
-      <x:c r="J2" t="str">
-        <x:v>终止型事件结果文本模板</x:v>
+      <x:c r="J2" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">终止型事件结果文本模板</x:t>
+        </x:is>
       </x:c>
       <x:c r="K2" t="inlineStr">
         <x:is>
@@ -1157,8 +1165,10 @@
           <x:t xml:space="preserve">string</x:t>
         </x:is>
       </x:c>
-      <x:c r="D3" t="str">
-        <x:v>string</x:v>
+      <x:c r="D3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">string</x:t>
+        </x:is>
       </x:c>
       <x:c r="E3" t="inlineStr">
         <x:is>
@@ -1185,8 +1195,10 @@
           <x:t xml:space="preserve">string</x:t>
         </x:is>
       </x:c>
-      <x:c r="J3" t="str">
-        <x:v>string</x:v>
+      <x:c r="J3" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">string</x:t>
+        </x:is>
       </x:c>
       <x:c r="K3" t="inlineStr">
         <x:is>
@@ -1215,8 +1227,10 @@
           <x:t xml:space="preserve">午夜食堂</x:t>
         </x:is>
       </x:c>
-      <x:c r="D4" t="str">
-        <x:v>深夜时分，一家食堂悄然开启，厨师端出一道红香肠，说到，“要切成章鱼的样子吗”</x:v>
+      <x:c r="D4" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">深夜时分，一家食堂悄然开启，厨师端出一道红香肠，说到，“要切成章鱼的样子吗”</x:t>
+        </x:is>
       </x:c>
       <x:c r="E4" t="inlineStr">
         <x:is>
@@ -1234,7 +1248,6 @@
           <x:t xml:space="preserve">Sprites/UI/Events/event_midnight_tasting</x:t>
         </x:is>
       </x:c>
-      <x:c r="J4"/>
       <x:c r="K4" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1250,8 +1263,10 @@
           <x:t xml:space="preserve">决战食神</x:t>
         </x:is>
       </x:c>
-      <x:c r="D5" t="str">
-        <x:v>你去对面新开的西餐厅，点了一份沙拉，店员将水浇到沙拉上，说到“没见过吧，这是生长沙拉，里面所有元素都是可食用的”</x:v>
+      <x:c r="D5" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">你去对面新开的西餐厅，点了一份沙拉，店员将水浇到沙拉上，说到“没见过吧，这是生长沙拉，里面所有元素都是可食用的”</x:t>
+        </x:is>
       </x:c>
       <x:c r="E5" t="inlineStr">
         <x:is>
@@ -1269,7 +1284,6 @@
           <x:t xml:space="preserve">Sprites/UI/Events/event_ancestral_recipe_page</x:t>
         </x:is>
       </x:c>
-      <x:c r="J5"/>
       <x:c r="K5" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1285,8 +1299,10 @@
           <x:t xml:space="preserve">木匠吉佩托</x:t>
         </x:is>
       </x:c>
-      <x:c r="D6" t="str">
-        <x:v>一位技艺精湛的木匠造访，询问你是否需要强化一下餐桌</x:v>
+      <x:c r="D6" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">一位技艺精湛的木匠造访，询问你是否需要强化一下餐桌</x:t>
+        </x:is>
       </x:c>
       <x:c r="E6" t="inlineStr">
         <x:is>
@@ -1304,7 +1320,6 @@
           <x:t xml:space="preserve">Sprites/UI/Events/event_table_carpenter</x:t>
         </x:is>
       </x:c>
-      <x:c r="J6"/>
       <x:c r="K6" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1320,8 +1335,10 @@
           <x:t xml:space="preserve">举报风波</x:t>
         </x:is>
       </x:c>
-      <x:c r="D7" t="str">
-        <x:v>隔壁的餐厅，在网上发表污蔑的言论，希望以此获得竞争优势</x:v>
+      <x:c r="D7" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">隔壁的餐厅，在网上发表污蔑的言论，希望以此获得竞争优势</x:t>
+        </x:is>
       </x:c>
       <x:c r="E7" t="inlineStr">
         <x:is>
@@ -1339,7 +1356,6 @@
           <x:t xml:space="preserve">Sprites/UI/Events/event_kitchen_god_statue</x:t>
         </x:is>
       </x:c>
-      <x:c r="J7"/>
       <x:c r="K7" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1355,8 +1371,10 @@
           <x:t xml:space="preserve">蘑菇挑战赛</x:t>
         </x:is>
       </x:c>
-      <x:c r="D8" t="str">
-        <x:v>主厨端出来一份蘑菇煲，其中各种鲜香的鲜艳蘑菇，让你既忍不住吞咽口水，又担心安全。主厨说道，“吃下这些蘑菇，可以获得我的终极大奖”</x:v>
+      <x:c r="D8" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">主厨端出来一份蘑菇煲，其中各种鲜香的鲜艳蘑菇，让你既忍不住吞咽口水，又担心安全。主厨说道，“吃下这些蘑菇，可以获得我的终极大奖”</x:t>
+        </x:is>
       </x:c>
       <x:c r="E8" t="inlineStr">
         <x:is>
@@ -1379,7 +1397,6 @@
           <x:t xml:space="preserve">Sprites/UI/Events/event_crossroad_sign</x:t>
         </x:is>
       </x:c>
-      <x:c r="J8"/>
       <x:c r="K8" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1395,8 +1412,10 @@
           <x:t xml:space="preserve">收取利息</x:t>
         </x:is>
       </x:c>
-      <x:c r="D9" t="str">
-        <x:v>每满 [gold]{threshold} 金币[/gold]获得 [gold]{goldPer}金币[/gold]，最高 [gold]{maxGain}金币[/gold]</x:v>
+      <x:c r="D9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">每满 [gold]{threshold} 金币[/gold]获得 [gold]{goldPer}金币[/gold]，最高 [gold]{maxGain}金币[/gold]</x:t>
+        </x:is>
       </x:c>
       <x:c r="E9" t="inlineStr">
         <x:is>
@@ -1414,8 +1433,10 @@
           <x:t xml:space="preserve">Sprites/UI/Events/event_interest</x:t>
         </x:is>
       </x:c>
-      <x:c r="J9" t="str">
-        <x:v>[gold]金币 +{gain}[/gold]</x:v>
+      <x:c r="J9" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[gold]金币 +{gain}[/gold]</x:t>
+        </x:is>
       </x:c>
       <x:c r="K9" t="n">
         <x:v>0</x:v>
@@ -1432,8 +1453,10 @@
           <x:t xml:space="preserve">抽奖机</x:t>
         </x:is>
       </x:c>
-      <x:c r="D10" t="str">
-        <x:v>一个华丽的机器，投入[gold]金币[/gold]有概率获得任何奖励</x:v>
+      <x:c r="D10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">一个华丽的机器，投入[gold]金币[/gold]有概率获得任何奖励</x:t>
+        </x:is>
       </x:c>
       <x:c r="E10" t="inlineStr">
         <x:is>
@@ -1451,8 +1474,10 @@
           <x:t xml:space="preserve">Sprites/UI/Events/event_slot_machine</x:t>
         </x:is>
       </x:c>
-      <x:c r="J10" t="str">
-        <x:v>这次什么也没有。</x:v>
+      <x:c r="J10" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">这次什么也没有。</x:t>
+        </x:is>
       </x:c>
       <x:c r="K10" t="n">
         <x:v>0.4</x:v>
@@ -1479,8 +1504,10 @@
           <x:t xml:space="preserve">会员制餐厅</x:t>
         </x:is>
       </x:c>
-      <x:c r="D11" t="str">
-        <x:v>你与另一位朋友德川相约同去一处会员制餐厅就餐。服务员上了三道菜，分别是迎宾酒、蔬菜棒蘸酱、汉堡肉</x:v>
+      <x:c r="D11" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">你与另一位朋友德川相约同去一处会员制餐厅就餐。服务员上了三道菜，分别是迎宾酒、蔬菜棒蘸酱、汉堡肉</x:t>
+        </x:is>
       </x:c>
       <x:c r="E11" t="inlineStr">
         <x:is>
@@ -1498,7 +1525,6 @@
           <x:t xml:space="preserve">Sprites/UI/Events/event_new_event</x:t>
         </x:is>
       </x:c>
-      <x:c r="J11"/>
       <x:c r="K11" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1514,8 +1540,10 @@
           <x:t xml:space="preserve">最后的晚餐</x:t>
         </x:is>
       </x:c>
-      <x:c r="D12" t="str">
-        <x:v>12位厨师围坐在长桌前。主厨刚举起酒杯，便宣布：“你们中有人把秘方卖给了对面餐厅。”众人立刻放下餐具，互相指认起来。</x:v>
+      <x:c r="D12" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">12位厨师围坐在长桌前。主厨刚举起酒杯，便宣布：“你们中有人把秘方卖给了对面餐厅。”众人立刻放下餐具，互相指认起来。</x:t>
+        </x:is>
       </x:c>
       <x:c r="E12" t="inlineStr">
         <x:is>
@@ -1528,7 +1556,6 @@
       <x:c r="H12" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J12"/>
       <x:c r="K12" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1544,8 +1571,10 @@
           <x:t xml:space="preserve">双R餐厅的夜晚</x:t>
         </x:is>
       </x:c>
-      <x:c r="D13" t="str">
-        <x:v>雨夜，你走进双R餐厅。黑咖啡刚煮好，樱桃派只剩最后一块；角落里的木头女士似乎有话要说。</x:v>
+      <x:c r="D13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">雨夜，你走进双R餐厅。黑咖啡刚煮好，樱桃派只剩最后一块；角落里的木头女士似乎有话要说。</x:t>
+        </x:is>
       </x:c>
       <x:c r="E13" t="inlineStr">
         <x:is>
@@ -1558,7 +1587,6 @@
       <x:c r="H13" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J13"/>
       <x:c r="K13" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1574,8 +1602,10 @@
           <x:t xml:space="preserve">最后一灶也会发光</x:t>
         </x:is>
       </x:c>
-      <x:c r="D14" t="str">
-        <x:v>阳泉酒家收档前又来了一桌客人。小当家把最后一眼灶火让给你：“用哪道料理招待他们？”</x:v>
+      <x:c r="D14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">阳泉酒家收档前又来了一桌客人。小当家把最后一眼灶火让给你：“用哪道料理招待他们？”</x:t>
+        </x:is>
       </x:c>
       <x:c r="E14" t="inlineStr">
         <x:is>
@@ -1588,7 +1618,6 @@
       <x:c r="H14" t="n">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="J14"/>
       <x:c r="K14" t="n">
         <x:v>0</x:v>
       </x:c>
@@ -1641,19 +1670,25 @@
           <x:t xml:space="preserve">parentId</x:t>
         </x:is>
       </x:c>
-      <x:c r="E1" s="1" t="str">
-        <x:v>text</x:v>
-      </x:c>
-      <x:c r="F1" s="1" t="str">
-        <x:v>resultText</x:v>
+      <x:c r="E1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">text</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">resultText</x:t>
+        </x:is>
       </x:c>
       <x:c r="G1" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">condition</x:t>
         </x:is>
       </x:c>
-      <x:c r="H1" s="1" t="str">
-        <x:v>conditionText</x:v>
+      <x:c r="H1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">conditionText</x:t>
+        </x:is>
       </x:c>
       <x:c r="I1" s="1" t="inlineStr">
         <x:is>
@@ -1680,8 +1715,10 @@
           <x:t xml:space="preserve">branchWeight</x:t>
         </x:is>
       </x:c>
-      <x:c r="N1" s="1" t="str">
-        <x:v>branchPageText</x:v>
+      <x:c r="N1" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">branchPageText</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="2">
@@ -1705,19 +1742,25 @@
           <x:t xml:space="preserve">父选项ID→event_option.id</x:t>
         </x:is>
       </x:c>
-      <x:c r="E2" s="1" t="str">
-        <x:v>选项文本(按钮)</x:v>
-      </x:c>
-      <x:c r="F2" s="1" t="str">
-        <x:v>选中后的结果/子页正文</x:v>
+      <x:c r="E2" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">选项文本(按钮)</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F2" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">选中后的结果/子页正文</x:t>
+        </x:is>
       </x:c>
       <x:c r="G2" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">选项前置条件</x:t>
         </x:is>
       </x:c>
-      <x:c r="H2" s="1" t="str">
-        <x:v>选项前置条件显示文案</x:v>
+      <x:c r="H2" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">选项前置条件显示文案</x:t>
+        </x:is>
       </x:c>
       <x:c r="I2" s="1" t="inlineStr">
         <x:is>
@@ -1744,8 +1787,10 @@
           <x:t xml:space="preserve">同一父选项下随机子分支相对权重；同组全部为 0 时保持手动选择</x:t>
         </x:is>
       </x:c>
-      <x:c r="N2" s="1" t="str">
-        <x:v>随机命中该子选项后显示的页面正文（空=沿用父选项结果正文）</x:v>
+      <x:c r="N2" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">随机命中该子选项后显示的页面正文（空=沿用父选项结果正文）</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="3">
@@ -1769,19 +1814,25 @@
           <x:t xml:space="preserve">string</x:t>
         </x:is>
       </x:c>
-      <x:c r="E3" s="1" t="str">
-        <x:v>string</x:v>
-      </x:c>
-      <x:c r="F3" s="1" t="str">
-        <x:v>string</x:v>
+      <x:c r="E3" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">string</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F3" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">string</x:t>
+        </x:is>
       </x:c>
       <x:c r="G3" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">string</x:t>
         </x:is>
       </x:c>
-      <x:c r="H3" s="1" t="str">
-        <x:v>string</x:v>
+      <x:c r="H3" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">string</x:t>
+        </x:is>
       </x:c>
       <x:c r="I3" s="1" t="inlineStr">
         <x:is>
@@ -1808,8 +1859,10 @@
           <x:t xml:space="preserve">float</x:t>
         </x:is>
       </x:c>
-      <x:c r="N3" s="1" t="str">
-        <x:v>string</x:v>
+      <x:c r="N3" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">string</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="4">
@@ -1823,13 +1876,16 @@
           <x:t xml:space="preserve">ev_midnight_tasting</x:t>
         </x:is>
       </x:c>
-      <x:c r="E4" s="1" t="str">
-        <x:v>不切直接吃</x:v>
-      </x:c>
-      <x:c r="F4" s="1" t="str">
-        <x:v>新鲜的红香肠，肉香浓密</x:v>
-      </x:c>
-      <x:c r="H4"/>
+      <x:c r="E4" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">不切直接吃</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F4" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">新鲜的红香肠，肉香浓密</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I4" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -1849,7 +1905,6 @@
       <x:c r="M4" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N4"/>
     </x:row>
     <x:row r="5">
       <x:c r="B5" s="1" t="inlineStr">
@@ -1862,13 +1917,16 @@
           <x:t xml:space="preserve">ev_midnight_tasting</x:t>
         </x:is>
       </x:c>
-      <x:c r="E5" s="1" t="str">
-        <x:v>切成章鱼的样子</x:v>
-      </x:c>
-      <x:c r="F5" s="1" t="str">
-        <x:v>红香肠被切两刀，在沸水的作用下弯曲起来</x:v>
-      </x:c>
-      <x:c r="H5"/>
+      <x:c r="E5" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">切成章鱼的样子</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F5" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">红香肠被切两刀，在沸水的作用下弯曲起来</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I5" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -1888,7 +1946,6 @@
       <x:c r="M5" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N5"/>
     </x:row>
     <x:row r="6">
       <x:c r="B6" s="1" t="inlineStr">
@@ -1901,13 +1958,16 @@
           <x:t xml:space="preserve">ev_midnight_tasting</x:t>
         </x:is>
       </x:c>
-      <x:c r="E6" s="1" t="str">
-        <x:v>来碗泡面配着吃</x:v>
-      </x:c>
-      <x:c r="F6" s="1" t="str">
-        <x:v>厨师称赞，“不愧是老吃家”，奉上独门秘籍</x:v>
-      </x:c>
-      <x:c r="H6"/>
+      <x:c r="E6" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">来碗泡面配着吃</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F6" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">厨师称赞，“不愧是老吃家”，奉上独门秘籍</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I6" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -1927,7 +1987,6 @@
       <x:c r="M6" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N6"/>
     </x:row>
     <x:row r="7">
       <x:c r="B7" s="1" t="inlineStr">
@@ -1940,13 +1999,16 @@
           <x:t xml:space="preserve">ev_ancestral_recipe_page</x:t>
         </x:is>
       </x:c>
-      <x:c r="E7" s="1" t="str">
-        <x:v>尝尝沙拉</x:v>
-      </x:c>
-      <x:c r="F7" s="1" t="str">
-        <x:v>你发现沙拉别有一番滋味，调料方式出乎意料</x:v>
-      </x:c>
-      <x:c r="H7"/>
+      <x:c r="E7" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">尝尝沙拉</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F7" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">你发现沙拉别有一番滋味，调料方式出乎意料</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I7" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -1966,7 +2028,6 @@
       <x:c r="M7" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N7"/>
     </x:row>
     <x:row r="8">
       <x:c r="B8" s="1" t="inlineStr">
@@ -1979,13 +2040,16 @@
           <x:t xml:space="preserve">ev_ancestral_recipe_page</x:t>
         </x:is>
       </x:c>
-      <x:c r="E8" s="1" t="str">
-        <x:v>我不是来看你变魔术的</x:v>
-      </x:c>
-      <x:c r="F8" s="1" t="str">
-        <x:v>“我是来吃饭的，不是来看你变魔术的，要装神弄鬼你回法国”</x:v>
-      </x:c>
-      <x:c r="H8"/>
+      <x:c r="E8" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">我不是来看你变魔术的</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F8" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">“我是来吃饭的，不是来看你变魔术的，要装神弄鬼你回法国”</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I8" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -2005,7 +2069,6 @@
       <x:c r="M8" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N8"/>
     </x:row>
     <x:row r="9">
       <x:c r="B9" s="1" t="inlineStr">
@@ -2018,13 +2081,16 @@
           <x:t xml:space="preserve">ev_ancestral_recipe_page</x:t>
         </x:is>
       </x:c>
-      <x:c r="E9" s="1" t="str">
-        <x:v>比试厨艺</x:v>
-      </x:c>
-      <x:c r="F9" s="1" t="str">
-        <x:v>你做了一道家常菜“葱爆牛肉”，味道惊人，餐厅名声大噪</x:v>
-      </x:c>
-      <x:c r="H9"/>
+      <x:c r="E9" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">比试厨艺</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F9" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">你做了一道家常菜“葱爆牛肉”，味道惊人，餐厅名声大噪</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I9" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -2044,7 +2110,6 @@
       <x:c r="M9" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N9"/>
     </x:row>
     <x:row r="10">
       <x:c r="B10" s="1" t="inlineStr">
@@ -2057,13 +2122,16 @@
           <x:t xml:space="preserve">ev_table_carpenter</x:t>
         </x:is>
       </x:c>
-      <x:c r="E10" s="1" t="str">
-        <x:v>修改为石料</x:v>
-      </x:c>
-      <x:c r="F10" s="1" t="str">
-        <x:v>木匠从卡车上搬下来两个石料箱</x:v>
-      </x:c>
-      <x:c r="H10"/>
+      <x:c r="E10" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">修改为石料</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F10" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">木匠从卡车上搬下来两个石料箱</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I10" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -2083,7 +2151,6 @@
       <x:c r="M10" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N10"/>
     </x:row>
     <x:row r="11">
       <x:c r="B11" s="1" t="inlineStr">
@@ -2096,13 +2163,16 @@
           <x:t xml:space="preserve">ev_table_carpenter</x:t>
         </x:is>
       </x:c>
-      <x:c r="E11" s="1" t="str">
-        <x:v>修改为木料</x:v>
-      </x:c>
-      <x:c r="F11" s="1" t="str">
-        <x:v>木匠从卡车上搬下来两个木料箱</x:v>
-      </x:c>
-      <x:c r="H11"/>
+      <x:c r="E11" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">修改为木料</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F11" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">木匠从卡车上搬下来两个木料箱</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I11" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -2122,7 +2192,6 @@
       <x:c r="M11" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N11"/>
     </x:row>
     <x:row r="12">
       <x:c r="B12" s="1" t="inlineStr">
@@ -2135,13 +2204,16 @@
           <x:t xml:space="preserve">ev_table_carpenter</x:t>
         </x:is>
       </x:c>
-      <x:c r="E12" s="1" t="str">
-        <x:v>选择金属料</x:v>
-      </x:c>
-      <x:c r="F12" s="1" t="str">
-        <x:v>木匠从卡车上搬下来两个金属料箱</x:v>
-      </x:c>
-      <x:c r="H12"/>
+      <x:c r="E12" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">选择金属料</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F12" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">木匠从卡车上搬下来两个金属料箱</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I12" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -2161,7 +2233,6 @@
       <x:c r="M12" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N12"/>
     </x:row>
     <x:row r="13">
       <x:c r="B13" s="1" t="inlineStr">
@@ -2174,19 +2245,25 @@
           <x:t xml:space="preserve">ev_kitchen_god_statue</x:t>
         </x:is>
       </x:c>
-      <x:c r="E13" s="1" t="str">
-        <x:v>申诉负面舆论</x:v>
-      </x:c>
-      <x:c r="F13" s="1" t="str">
-        <x:v>经平台核实，对方的言论不实，特此赠予餐厅一件[term]装饰品[/term]，以表安慰</x:v>
+      <x:c r="E13" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">申诉负面舆论</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F13" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">经平台核实，对方的言论不实，特此赠予餐厅一件[term]装饰品[/term]，以表安慰</x:t>
+        </x:is>
       </x:c>
       <x:c r="G13" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">minGold:30</x:t>
         </x:is>
       </x:c>
-      <x:c r="H13" s="2" t="str">
-        <x:v>需要至少 [gold]30 金币[/gold]</x:v>
+      <x:c r="H13" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">需要至少 [gold]30 金币[/gold]</x:t>
+        </x:is>
       </x:c>
       <x:c r="I13" s="1" t="inlineStr">
         <x:is>
@@ -2207,7 +2284,6 @@
       <x:c r="M13" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N13"/>
     </x:row>
     <x:row r="14">
       <x:c r="B14" s="1" t="inlineStr">
@@ -2220,19 +2296,25 @@
           <x:t xml:space="preserve">ev_kitchen_god_statue</x:t>
         </x:is>
       </x:c>
-      <x:c r="E14" s="1" t="str">
-        <x:v>激情互喷</x:v>
-      </x:c>
-      <x:c r="F14" s="1" t="str">
-        <x:v>争论吸引了大量关注，有支持也有贬低</x:v>
+      <x:c r="E14" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">激情互喷</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F14" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">争论吸引了大量关注，有支持也有贬低</x:t>
+        </x:is>
       </x:c>
       <x:c r="G14" s="2" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">hasRecipeDish</x:t>
         </x:is>
       </x:c>
-      <x:c r="H14" s="2" t="str">
-        <x:v>需要食谱中至少有 1 个食物</x:v>
+      <x:c r="H14" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">需要食谱中至少有 1 个食物</x:t>
+        </x:is>
       </x:c>
       <x:c r="I14" s="1" t="inlineStr">
         <x:is>
@@ -2253,7 +2335,6 @@
       <x:c r="M14" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N14"/>
     </x:row>
     <x:row r="15">
       <x:c r="B15" s="1" t="inlineStr">
@@ -2266,13 +2347,16 @@
           <x:t xml:space="preserve">ev_kitchen_god_statue</x:t>
         </x:is>
       </x:c>
-      <x:c r="E15" s="1" t="str">
-        <x:v>置之不理</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="str">
-        <x:v>消极的应对给餐厅带来了一些影响，不过很快平息</x:v>
-      </x:c>
-      <x:c r="H15"/>
+      <x:c r="E15" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">置之不理</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F15" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">消极的应对给餐厅带来了一些影响，不过很快平息</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I15" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -2292,7 +2376,6 @@
       <x:c r="M15" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N15"/>
     </x:row>
     <x:row r="16">
       <x:c r="B16" s="1" t="inlineStr">
@@ -2305,11 +2388,11 @@
           <x:t xml:space="preserve">ev_interest</x:t>
         </x:is>
       </x:c>
-      <x:c r="E16" s="1" t="str">
-        <x:v>[gold]金币 +{gain}[/gold]</x:v>
-      </x:c>
-      <x:c r="F16"/>
-      <x:c r="H16"/>
+      <x:c r="E16" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[gold]金币 +{gain}[/gold]</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I16" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">CollectInterest</x:t>
@@ -2329,7 +2412,6 @@
       <x:c r="M16" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N16"/>
     </x:row>
     <x:row r="17">
       <x:c r="B17" s="1" t="inlineStr">
@@ -2342,11 +2424,11 @@
           <x:t xml:space="preserve">ev_slot_machine</x:t>
         </x:is>
       </x:c>
-      <x:c r="E17" s="1" t="str">
-        <x:v>{slotCostText}（{slotStatus}）</x:v>
-      </x:c>
-      <x:c r="F17"/>
-      <x:c r="H17"/>
+      <x:c r="E17" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">{slotCostText}（{slotStatus}）</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I17" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -2366,7 +2448,6 @@
       <x:c r="M17" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N17"/>
     </x:row>
     <x:row r="18">
       <x:c r="B18" s="1" t="inlineStr">
@@ -2379,11 +2460,11 @@
           <x:t xml:space="preserve">ev_slot_machine</x:t>
         </x:is>
       </x:c>
-      <x:c r="E18" s="1" t="str">
-        <x:v>离开</x:v>
-      </x:c>
-      <x:c r="F18"/>
-      <x:c r="H18"/>
+      <x:c r="E18" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">离开</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I18" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -2403,7 +2484,6 @@
       <x:c r="M18" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N18"/>
     </x:row>
     <x:row r="19">
       <x:c r="B19" s="1" t="inlineStr">
@@ -2421,13 +2501,16 @@
           <x:t xml:space="preserve">opt_midnight_sample</x:t>
         </x:is>
       </x:c>
-      <x:c r="E19" s="1" t="str">
-        <x:v>对食物的理解加深了！后续更容易获得更好的食物</x:v>
-      </x:c>
-      <x:c r="F19" s="1" t="str">
-        <x:v>食物奖励隐藏分永久 +5。</x:v>
-      </x:c>
-      <x:c r="H19"/>
+      <x:c r="E19" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">对食物的理解加深了！后续更容易获得更好的食物</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F19" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">食物奖励隐藏分永久 +5。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I19" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddHiddenScoreOffset</x:t>
@@ -2447,7 +2530,6 @@
       <x:c r="M19" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N19"/>
     </x:row>
     <x:row r="20">
       <x:c r="B20" s="1" t="inlineStr">
@@ -2465,13 +2547,16 @@
           <x:t xml:space="preserve">opt_midnight_menu</x:t>
         </x:is>
       </x:c>
-      <x:c r="E20" s="1" t="str">
-        <x:v>心情大好，下次营业获得的[gold]金币[/gold]额外[gold]+60%[/gold]</x:v>
-      </x:c>
-      <x:c r="F20" s="1" t="str">
-        <x:v>下一次营业基础[gold]金币[/gold] ×1.6。</x:v>
-      </x:c>
-      <x:c r="H20"/>
+      <x:c r="E20" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">心情大好，下次营业获得的[gold]金币[/gold]额外[gold]+60%[/gold]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F20" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">下一次营业基础[gold]金币[/gold] ×1.6。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I20" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddBusinessGoldPct</x:t>
@@ -2491,7 +2576,6 @@
       <x:c r="M20" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N20"/>
     </x:row>
     <x:row r="21">
       <x:c r="B21" s="1" t="inlineStr">
@@ -2509,13 +2593,16 @@
           <x:t xml:space="preserve">opt_midnight_leave</x:t>
         </x:is>
       </x:c>
-      <x:c r="E21" s="1" t="str">
-        <x:v>[context]所有[/context]食物[strong]分数[/strong][score]+2[/score]！这就是知识的力量</x:v>
-      </x:c>
-      <x:c r="F21" s="1" t="str">
-        <x:v>触发时食谱中已有的全部食物永久[strong]分数[/strong] [score]+2[/score]。</x:v>
-      </x:c>
-      <x:c r="H21"/>
+      <x:c r="E21" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[context]所有[/context]食物[strong]分数[/strong][score]+2[/score]！这就是知识的力量</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F21" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">触发时食谱中已有的全部食物永久[strong]分数[/strong] [score]+2[/score]。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I21" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddAllRecipeScoreFlat</x:t>
@@ -2535,7 +2622,6 @@
       <x:c r="M21" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N21"/>
     </x:row>
     <x:row r="22">
       <x:c r="B22" s="1" t="inlineStr">
@@ -2553,13 +2639,16 @@
           <x:t xml:space="preserve">opt_recipe_page_sell</x:t>
         </x:is>
       </x:c>
-      <x:c r="E22" s="1" t="str">
-        <x:v>本周后续营业的[gold]金币[/gold]奖励提升[gold]30%[/gold]</x:v>
-      </x:c>
-      <x:c r="F22" s="1" t="str">
-        <x:v>本周后续营业基础[gold]金币[/gold] ×1.3。</x:v>
-      </x:c>
-      <x:c r="H22"/>
+      <x:c r="E22" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本周后续营业的[gold]金币[/gold]奖励提升[gold]30%[/gold]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F22" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">本周后续营业基础[gold]金币[/gold] ×1.3。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I22" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddBusinessGoldPct</x:t>
@@ -2579,7 +2668,6 @@
       <x:c r="M22" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N22"/>
     </x:row>
     <x:row r="23">
       <x:c r="B23" s="1" t="inlineStr">
@@ -2597,13 +2685,16 @@
           <x:t xml:space="preserve">opt_recipe_page_body</x:t>
         </x:is>
       </x:c>
-      <x:c r="E23" s="1" t="str">
-        <x:v>获得两个调味相关的[term]消耗品[/term]</x:v>
-      </x:c>
-      <x:c r="F23" s="1" t="str">
-        <x:v>从六种调味箱中放回随机获得 2 个。</x:v>
-      </x:c>
-      <x:c r="H23"/>
+      <x:c r="E23" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">获得两个调味相关的[term]消耗品[/term]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F23" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">从六种调味箱中放回随机获得 2 个。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I23" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GrantRandomActiveItems</x:t>
@@ -2623,7 +2714,6 @@
       <x:c r="M23" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N23"/>
     </x:row>
     <x:row r="24">
       <x:c r="B24" s="1" t="inlineStr">
@@ -2641,13 +2731,16 @@
           <x:t xml:space="preserve">opt_recipe_page_cover</x:t>
         </x:is>
       </x:c>
-      <x:c r="E24" s="1" t="str">
-        <x:v>[context]星级评鉴[/context]美味值要求提升20%，[gold]金币[/gold]奖励翻倍</x:v>
-      </x:c>
-      <x:c r="F24" s="1" t="str">
-        <x:v>后续[context]星级评鉴[/context]目标 ×1.2，基础[gold]金币[/gold] ×2。</x:v>
-      </x:c>
-      <x:c r="H24"/>
+      <x:c r="E24" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">[context]星级评鉴[/context]美味值要求提升20%，[gold]金币[/gold]奖励翻倍</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F24" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">后续[context]星级评鉴[/context]目标 ×1.2，基础[gold]金币[/gold] ×2。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I24" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddBossTargetScorePct</x:t>
@@ -2667,12 +2760,8 @@
       <x:c r="M24" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N24"/>
     </x:row>
     <x:row r="25">
-      <x:c r="E25"/>
-      <x:c r="F25"/>
-      <x:c r="H25"/>
       <x:c r="I25" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddBossBaseGoldPct</x:t>
@@ -2686,7 +2775,6 @@
           <x:t xml:space="preserve">-</x:t>
         </x:is>
       </x:c>
-      <x:c r="N25"/>
     </x:row>
     <x:row r="26">
       <x:c r="B26" s="1" t="inlineStr">
@@ -2704,13 +2792,16 @@
           <x:t xml:space="preserve">opt_carpenter_wood</x:t>
         </x:is>
       </x:c>
-      <x:c r="E26" s="1" t="str">
-        <x:v>获得2个石料类强化箱</x:v>
-      </x:c>
-      <x:c r="F26" s="1" t="str">
-        <x:v>从三种石料箱中放回随机获得 2 个。</x:v>
-      </x:c>
-      <x:c r="H26"/>
+      <x:c r="E26" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">获得2个石料类强化箱</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F26" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">从三种石料箱中放回随机获得 2 个。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I26" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GrantRandomActiveItems</x:t>
@@ -2730,7 +2821,6 @@
       <x:c r="M26" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N26"/>
     </x:row>
     <x:row r="27">
       <x:c r="B27" s="1" t="inlineStr">
@@ -2748,13 +2838,16 @@
           <x:t xml:space="preserve">opt_carpenter_stone</x:t>
         </x:is>
       </x:c>
-      <x:c r="E27" s="1" t="str">
-        <x:v>获得2个木料类强化箱</x:v>
-      </x:c>
-      <x:c r="F27" s="1" t="str">
-        <x:v>从两种木料箱中放回随机获得 2 个。</x:v>
-      </x:c>
-      <x:c r="H27"/>
+      <x:c r="E27" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">获得2个木料类强化箱</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F27" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">从两种木料箱中放回随机获得 2 个。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I27" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GrantRandomActiveItems</x:t>
@@ -2774,7 +2867,6 @@
       <x:c r="M27" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N27"/>
     </x:row>
     <x:row r="28">
       <x:c r="B28" s="1" t="inlineStr">
@@ -2792,13 +2884,16 @@
           <x:t xml:space="preserve">opt_carpenter_metal</x:t>
         </x:is>
       </x:c>
-      <x:c r="E28" s="1" t="str">
-        <x:v>获得2个金属料强化箱</x:v>
-      </x:c>
-      <x:c r="F28" s="1" t="str">
-        <x:v>从两种金属箱中放回随机获得 2 个。</x:v>
-      </x:c>
-      <x:c r="H28"/>
+      <x:c r="E28" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">获得2个金属料强化箱</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F28" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">从两种金属箱中放回随机获得 2 个。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I28" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GrantRandomActiveItems</x:t>
@@ -2818,7 +2913,6 @@
       <x:c r="M28" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N28"/>
     </x:row>
     <x:row r="29">
       <x:c r="B29" s="1" t="inlineStr">
@@ -2836,13 +2930,16 @@
           <x:t xml:space="preserve">opt_statue_gold</x:t>
         </x:is>
       </x:c>
-      <x:c r="E29" s="1" t="str">
-        <x:v>获得1个[term]装饰品[/term]</x:v>
-      </x:c>
-      <x:c r="F29" s="1" t="str">
-        <x:v>支付 [gold]30 金币[/gold]，随机获得 1 个非诅咒[term]装饰品[/term]。</x:v>
-      </x:c>
-      <x:c r="H29"/>
+      <x:c r="E29" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">获得1个[term]装饰品[/term]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F29" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">支付 [gold]30 金币[/gold]，随机获得 1 个非诅咒[term]装饰品[/term]。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I29" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GainGold</x:t>
@@ -2862,12 +2959,8 @@
       <x:c r="M29" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N29"/>
     </x:row>
     <x:row r="30">
-      <x:c r="E30"/>
-      <x:c r="F30"/>
-      <x:c r="H30"/>
       <x:c r="I30" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GrantRandomPassiveItems</x:t>
@@ -2881,7 +2974,6 @@
           <x:t xml:space="preserve">Positive</x:t>
         </x:is>
       </x:c>
-      <x:c r="N30"/>
     </x:row>
     <x:row r="31">
       <x:c r="B31" s="1" t="inlineStr">
@@ -2899,13 +2991,16 @@
           <x:t xml:space="preserve">opt_statue_dish</x:t>
         </x:is>
       </x:c>
-      <x:c r="E31" s="1" t="str">
-        <x:v>获得[gold]100金币[/gold]和1个负面[term]装饰品[/term]</x:v>
-      </x:c>
-      <x:c r="F31" s="1" t="str">
-        <x:v>获得 [gold]100 金币[/gold]和 1 个诅咒[term]装饰品[/term]。</x:v>
-      </x:c>
-      <x:c r="H31"/>
+      <x:c r="E31" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">获得[gold]100金币[/gold]和1个负面[term]装饰品[/term]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F31" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">获得 [gold]100 金币[/gold]和 1 个诅咒[term]装饰品[/term]。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I31" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GainGold</x:t>
@@ -2925,12 +3020,8 @@
       <x:c r="M31" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N31"/>
     </x:row>
     <x:row r="32">
-      <x:c r="E32"/>
-      <x:c r="F32"/>
-      <x:c r="H32"/>
       <x:c r="I32" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GrantRandomPassiveItems</x:t>
@@ -2944,7 +3035,6 @@
           <x:t xml:space="preserve">Negative</x:t>
         </x:is>
       </x:c>
-      <x:c r="N32"/>
     </x:row>
     <x:row r="33">
       <x:c r="B33" s="1" t="inlineStr">
@@ -2962,13 +3052,16 @@
           <x:t xml:space="preserve">opt_statue_steal</x:t>
         </x:is>
       </x:c>
-      <x:c r="E33" s="1" t="str">
-        <x:v>下次营业[gold]金币-40%[/gold]</x:v>
-      </x:c>
-      <x:c r="F33" s="1" t="str">
-        <x:v>获得 [gold]100 金币[/gold]和 1 个随机[term]消耗品[/term]；下一次营业基础[gold]金币[/gold] ×0.6。</x:v>
-      </x:c>
-      <x:c r="H33"/>
+      <x:c r="E33" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">下次营业[gold]金币-40%[/gold]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F33" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">获得 [gold]100 金币[/gold]和 1 个随机[term]消耗品[/term]；下一次营业基础[gold]金币[/gold] ×0.6。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I33" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddBusinessGoldPct</x:t>
@@ -2988,7 +3081,6 @@
       <x:c r="M33" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N33"/>
     </x:row>
     <x:row r="34">
       <x:c r="B34" s="1" t="inlineStr">
@@ -3001,13 +3093,16 @@
           <x:t xml:space="preserve">ev_new_event</x:t>
         </x:is>
       </x:c>
-      <x:c r="E34" s="1" t="str">
-        <x:v>喝迎宾酒</x:v>
-      </x:c>
-      <x:c r="F34" s="1" t="str">
-        <x:v>慢慢品尝，味道别有一番风味</x:v>
-      </x:c>
-      <x:c r="H34"/>
+      <x:c r="E34" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">喝迎宾酒</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F34" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">慢慢品尝，味道别有一番风味</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I34" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -3027,7 +3122,6 @@
       <x:c r="M34" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N34"/>
     </x:row>
     <x:row r="35">
       <x:c r="B35" s="1" t="inlineStr">
@@ -3045,13 +3139,16 @@
           <x:t xml:space="preserve">opt_new_event_choice</x:t>
         </x:is>
       </x:c>
-      <x:c r="E35" s="1" t="str">
-        <x:v>为随机两个食物添加风味</x:v>
-      </x:c>
-      <x:c r="F35" s="1" t="str">
-        <x:v>为随机 2 个不同食物添加随机风味，优先选择没有风味的食物。</x:v>
-      </x:c>
-      <x:c r="H35"/>
+      <x:c r="E35" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">为随机两个食物添加风味</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F35" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">为随机 2 个不同食物添加随机风味，优先选择没有风味的食物。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I35" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddRandomRecipeFlavor</x:t>
@@ -3071,7 +3168,6 @@
       <x:c r="M35" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N35"/>
     </x:row>
     <x:row r="36">
       <x:c r="B36" s="1" t="inlineStr">
@@ -3084,13 +3180,16 @@
           <x:t xml:space="preserve">ev_new_event</x:t>
         </x:is>
       </x:c>
-      <x:c r="E36" s="1" t="str">
-        <x:v>吃蔬菜棒蘸酱</x:v>
-      </x:c>
-      <x:c r="F36" s="1" t="str">
-        <x:v>蔬菜棒很新鲜，酱咸香合适</x:v>
-      </x:c>
-      <x:c r="H36"/>
+      <x:c r="E36" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">吃蔬菜棒蘸酱</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F36" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">蔬菜棒很新鲜，酱咸香合适</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I36" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -3110,7 +3209,6 @@
       <x:c r="M36" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N36"/>
     </x:row>
     <x:row r="37">
       <x:c r="B37" s="1" t="inlineStr">
@@ -3123,13 +3221,16 @@
           <x:t xml:space="preserve">ev_new_event</x:t>
         </x:is>
       </x:c>
-      <x:c r="E37" s="1" t="str">
-        <x:v>吃汉堡肉</x:v>
-      </x:c>
-      <x:c r="F37" s="1" t="str">
-        <x:v>感觉味道怪怪的，身体有些不舒服</x:v>
-      </x:c>
-      <x:c r="H37"/>
+      <x:c r="E37" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">吃汉堡肉</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F37" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">感觉味道怪怪的，身体有些不舒服</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I37" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -3149,7 +3250,6 @@
       <x:c r="M37" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N37"/>
     </x:row>
     <x:row r="38">
       <x:c r="B38" s="1" t="inlineStr">
@@ -3167,13 +3267,16 @@
           <x:t xml:space="preserve">opt_new_event_choice_3</x:t>
         </x:is>
       </x:c>
-      <x:c r="E38" s="1" t="str">
-        <x:v>对食物的理解提升了！更容易获得更好的食物</x:v>
-      </x:c>
-      <x:c r="F38" s="1" t="str">
-        <x:v>食物奖励隐藏分永久 +5。</x:v>
-      </x:c>
-      <x:c r="H38"/>
+      <x:c r="E38" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">对食物的理解提升了！更容易获得更好的食物</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F38" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">食物奖励隐藏分永久 +5。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I38" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddHiddenScoreOffset</x:t>
@@ -3193,7 +3296,6 @@
       <x:c r="M38" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N38"/>
     </x:row>
     <x:row r="39">
       <x:c r="B39" s="1" t="inlineStr">
@@ -3211,13 +3313,16 @@
           <x:t xml:space="preserve">opt_new_event_choice_4</x:t>
         </x:is>
       </x:c>
-      <x:c r="E39" s="1" t="str">
-        <x:v>休息两天，店内活动适当调整</x:v>
-      </x:c>
-      <x:c r="F39" s="1" t="str">
-        <x:v>身体不舒服就应该休息啦，稍后调整下店里活动的安排就好</x:v>
-      </x:c>
-      <x:c r="H39"/>
+      <x:c r="E39" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">休息两天，店内活动适当调整</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F39" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">身体不舒服就应该休息啦，稍后调整下店里活动的安排就好</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I39" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -3237,7 +3342,6 @@
       <x:c r="M39" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N39"/>
     </x:row>
     <x:row r="40">
       <x:c r="B40" s="1" t="inlineStr">
@@ -3255,13 +3359,16 @@
           <x:t xml:space="preserve">opt_new_event_choice_4</x:t>
         </x:is>
       </x:c>
-      <x:c r="E40" s="1" t="str">
-        <x:v>坚持工作</x:v>
-      </x:c>
-      <x:c r="F40" s="1" t="str">
-        <x:v>顾客听说了店长的事迹，纷纷投来感动的目光，一个小孩子捧着一个[term]装饰品[/term]给你</x:v>
-      </x:c>
-      <x:c r="H40"/>
+      <x:c r="E40" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">坚持工作</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F40" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">顾客听说了店长的事迹，纷纷投来感动的目光，一个小孩子捧着一个[term]装饰品[/term]给你</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I40" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -3281,7 +3388,6 @@
       <x:c r="M40" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N40"/>
     </x:row>
     <x:row r="41">
       <x:c r="B41" s="1" t="inlineStr">
@@ -3299,13 +3405,16 @@
           <x:t xml:space="preserve">opt_new_event_choice_6</x:t>
         </x:is>
       </x:c>
-      <x:c r="E41" s="1" t="str">
-        <x:v>获得两个调整单类的[term]消耗品[/term]</x:v>
-      </x:c>
-      <x:c r="F41" s="1" t="str">
-        <x:v>从全部调整单中放回随机获得 2 个。</x:v>
-      </x:c>
-      <x:c r="H41"/>
+      <x:c r="E41" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">获得两个调整单类的[term]消耗品[/term]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F41" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">从全部调整单中放回随机获得 2 个。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I41" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GrantRandomActiveItems</x:t>
@@ -3325,7 +3434,6 @@
       <x:c r="M41" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N41"/>
     </x:row>
     <x:row r="42">
       <x:c r="B42" s="1" t="inlineStr">
@@ -3343,13 +3451,16 @@
           <x:t xml:space="preserve">opt_new_event_choice_7</x:t>
         </x:is>
       </x:c>
-      <x:c r="E42" s="1" t="str">
-        <x:v>获得一个[term]装饰品[/term]</x:v>
-      </x:c>
-      <x:c r="F42" s="1" t="str">
-        <x:v>随机获得 1 个非诅咒[term]装饰品[/term]。</x:v>
-      </x:c>
-      <x:c r="H42"/>
+      <x:c r="E42" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">获得一个[term]装饰品[/term]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F42" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">随机获得 1 个非诅咒[term]装饰品[/term]。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I42" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GrantRandomPassiveItems</x:t>
@@ -3369,7 +3480,6 @@
       <x:c r="M42" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N42"/>
     </x:row>
     <x:row r="43">
       <x:c r="B43" s="1" t="inlineStr">
@@ -3382,13 +3492,16 @@
           <x:t xml:space="preserve">ev_crossroad_sign</x:t>
         </x:is>
       </x:c>
-      <x:c r="E43" s="1" t="str">
-        <x:v>第一关：品尝白蘑菇</x:v>
-      </x:c>
-      <x:c r="F43" s="1" t="str">
-        <x:v>先从白色蘑菇开始。每次安全尝完都可以见好就收，也可以继续挑战下一种蘑菇。</x:v>
-      </x:c>
-      <x:c r="H43"/>
+      <x:c r="E43" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">第一关：品尝白蘑菇</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F43" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">先从白色蘑菇开始。每次安全尝完都可以见好就收，也可以继续挑战下一种蘑菇。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I43" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -3408,7 +3521,6 @@
       <x:c r="M43" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N43"/>
     </x:row>
     <x:row r="44">
       <x:c r="B44" s="1" t="inlineStr">
@@ -3421,13 +3533,16 @@
           <x:t xml:space="preserve">ev_crossroad_sign</x:t>
         </x:is>
       </x:c>
-      <x:c r="E44" s="1" t="str">
-        <x:v>不参加了</x:v>
-      </x:c>
-      <x:c r="F44" s="1" t="str">
-        <x:v>明智的选择，还是一朝被蛇咬，十年怕井绳呢</x:v>
-      </x:c>
-      <x:c r="H44"/>
+      <x:c r="E44" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">不参加了</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F44" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">明智的选择，还是一朝被蛇咬，十年怕井绳呢</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I44" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -3447,7 +3562,6 @@
       <x:c r="M44" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N44"/>
     </x:row>
     <x:row r="45">
       <x:c r="B45" s="1" t="inlineStr">
@@ -3465,13 +3579,16 @@
           <x:t xml:space="preserve">opt_sign_secondhand</x:t>
         </x:is>
       </x:c>
-      <x:c r="E45" s="1" t="str">
-        <x:v>参与奖：[gold]金币+50[/gold]</x:v>
-      </x:c>
-      <x:c r="F45" s="1" t="str">
-        <x:v>获得 [gold]50 金币[/gold]。</x:v>
-      </x:c>
-      <x:c r="H45"/>
+      <x:c r="E45" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">参与奖：[gold]金币+50[/gold]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F45" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">获得 [gold]50 金币[/gold]。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I45" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GainGold</x:t>
@@ -3491,7 +3608,6 @@
       <x:c r="M45" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N45"/>
     </x:row>
     <x:row r="46">
       <x:c r="B46" s="1" t="inlineStr">
@@ -3509,13 +3625,16 @@
           <x:t xml:space="preserve">opt_sign_food_street</x:t>
         </x:is>
       </x:c>
-      <x:c r="E46" s="1" t="str">
-        <x:v>去抢救，[gold]金币-20[/gold]</x:v>
-      </x:c>
-      <x:c r="F46" s="1" t="str">
-        <x:v>你被紧急送往医院抢救。</x:v>
-      </x:c>
-      <x:c r="H46"/>
+      <x:c r="E46" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">去抢救，[gold]金币-20[/gold]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F46" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">你被紧急送往医院抢救。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I46" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">LoseEscalatingGold</x:t>
@@ -3535,8 +3654,10 @@
       <x:c r="M46" s="2" t="n">
         <x:v>20</x:v>
       </x:c>
-      <x:c r="N46" s="2" t="str">
-        <x:v>白色蘑菇刚入口，舌尖便开始发麻，眼前的餐厅转了起来。</x:v>
+      <x:c r="N46" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">白色蘑菇刚入口，舌尖便开始发麻，眼前的餐厅转了起来。</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -3555,13 +3676,16 @@
           <x:t xml:space="preserve">opt_sign_food_street</x:t>
         </x:is>
       </x:c>
-      <x:c r="E47" s="1" t="str">
-        <x:v>白色蘑菇很安全</x:v>
-      </x:c>
-      <x:c r="F47" s="1" t="str">
-        <x:v>白色蘑菇鲜甜爽脆。要带着这份好运离开，还是继续品尝红色蘑菇？</x:v>
-      </x:c>
-      <x:c r="H47"/>
+      <x:c r="E47" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">白色蘑菇很安全</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F47" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">白色蘑菇鲜甜爽脆。要带着这份好运离开，还是继续品尝红色蘑菇？</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I47" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -3581,8 +3705,10 @@
       <x:c r="M47" s="2" t="n">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="N47" s="2" t="str">
-        <x:v>白色蘑菇清甜鲜嫩，吃完后身体毫无异样。</x:v>
+      <x:c r="N47" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">白色蘑菇清甜鲜嫩，吃完后身体毫无异样。</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -3601,13 +3727,16 @@
           <x:t xml:space="preserve">opt_mushroom_white_safe</x:t>
         </x:is>
       </x:c>
-      <x:c r="E48" s="1" t="str">
-        <x:v>见好就收，领取 [gold]70 金币[/gold]</x:v>
-      </x:c>
-      <x:c r="F48" s="1" t="str">
-        <x:v>你把剩下的白色蘑菇卖给了识货的客人，获得 [gold]70 金币[/gold]。</x:v>
-      </x:c>
-      <x:c r="H48"/>
+      <x:c r="E48" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">见好就收，领取 [gold]70 金币[/gold]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F48" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">你把剩下的白色蘑菇卖给了识货的客人，获得 [gold]70 金币[/gold]。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I48" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GainGold</x:t>
@@ -3627,7 +3756,6 @@
       <x:c r="M48" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N48"/>
     </x:row>
     <x:row r="49">
       <x:c r="B49" s="1" t="inlineStr">
@@ -3645,13 +3773,16 @@
           <x:t xml:space="preserve">opt_mushroom_white_safe</x:t>
         </x:is>
       </x:c>
-      <x:c r="E49" s="1" t="str">
-        <x:v>第二关：品尝红蘑菇</x:v>
-      </x:c>
-      <x:c r="F49" s="1" t="str">
-        <x:v>你夹起了颜色鲜艳的红色蘑菇。</x:v>
-      </x:c>
-      <x:c r="H49"/>
+      <x:c r="E49" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">第二关：品尝红蘑菇</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F49" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">你夹起了颜色鲜艳的红色蘑菇。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I49" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -3671,7 +3802,6 @@
       <x:c r="M49" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N49"/>
     </x:row>
     <x:row r="50">
       <x:c r="B50" s="1" t="inlineStr">
@@ -3689,13 +3819,16 @@
           <x:t xml:space="preserve">opt_mushroom_try_red</x:t>
         </x:is>
       </x:c>
-      <x:c r="E50" s="1" t="str">
-        <x:v>去抢救，[gold]金币-40[/gold]</x:v>
-      </x:c>
-      <x:c r="F50" s="1" t="str">
-        <x:v>毒性来势汹汹，你再次被送往医院抢救。</x:v>
-      </x:c>
-      <x:c r="H50"/>
+      <x:c r="E50" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">去抢救，[gold]金币-40[/gold]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F50" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">毒性来势汹汹，你再次被送往医院抢救。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I50" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">LoseEscalatingGold</x:t>
@@ -3715,8 +3848,10 @@
       <x:c r="M50" s="2" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="N50" s="2" t="str">
-        <x:v>红色蘑菇辛辣得反常，没过多久，你的视线便开始模糊。</x:v>
+      <x:c r="N50" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">红色蘑菇辛辣得反常，没过多久，你的视线便开始模糊。</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -3735,13 +3870,16 @@
           <x:t xml:space="preserve">opt_mushroom_try_red</x:t>
         </x:is>
       </x:c>
-      <x:c r="E51" s="1" t="str">
-        <x:v>红色蘑菇也很安全</x:v>
-      </x:c>
-      <x:c r="F51" s="1" t="str">
-        <x:v>红色蘑菇带着微微果香。现在收手已经收获颇丰，或者再尝最后的绿色蘑菇。</x:v>
-      </x:c>
-      <x:c r="H51"/>
+      <x:c r="E51" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">红色蘑菇也很安全</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F51" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">红色蘑菇带着微微果香。现在收手已经收获颇丰，或者再尝最后的绿色蘑菇。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I51" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -3761,8 +3899,10 @@
       <x:c r="M51" s="2" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="N51" s="2" t="str">
-        <x:v>红色蘑菇入口微辣，却没有任何毒性，你又安全过了一关。</x:v>
+      <x:c r="N51" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">红色蘑菇入口微辣，却没有任何毒性，你又安全过了一关。</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -3781,13 +3921,16 @@
           <x:t xml:space="preserve">opt_mushroom_red_safe</x:t>
         </x:is>
       </x:c>
-      <x:c r="E52" s="1" t="str">
-        <x:v>稳妥收手，领取 [gold]120 金币[/gold]</x:v>
-      </x:c>
-      <x:c r="F52" s="1" t="str">
-        <x:v>你把剩余蘑菇高价转让，获得 [gold]120 金币[/gold]。</x:v>
-      </x:c>
-      <x:c r="H52"/>
+      <x:c r="E52" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">稳妥收手，领取 [gold]120 金币[/gold]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F52" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">你把剩余蘑菇高价转让，获得 [gold]120 金币[/gold]。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I52" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GainGold</x:t>
@@ -3807,7 +3950,6 @@
       <x:c r="M52" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N52"/>
     </x:row>
     <x:row r="53">
       <x:c r="B53" s="1" t="inlineStr">
@@ -3825,13 +3967,16 @@
           <x:t xml:space="preserve">opt_mushroom_red_safe</x:t>
         </x:is>
       </x:c>
-      <x:c r="E53" s="1" t="str">
-        <x:v>第三关：品尝绿蘑菇</x:v>
-      </x:c>
-      <x:c r="F53" s="1" t="str">
-        <x:v>最后一朵绿色蘑菇散发着危险又迷人的清香。</x:v>
-      </x:c>
-      <x:c r="H53"/>
+      <x:c r="E53" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">第三关：品尝绿蘑菇</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F53" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">最后一朵绿色蘑菇散发着危险又迷人的清香。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I53" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -3851,7 +3996,6 @@
       <x:c r="M53" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N53"/>
     </x:row>
     <x:row r="54">
       <x:c r="B54" s="1" t="inlineStr">
@@ -3869,13 +4013,16 @@
           <x:t xml:space="preserve">opt_mushroom_try_green</x:t>
         </x:is>
       </x:c>
-      <x:c r="E54" s="1" t="str">
-        <x:v>去icu抢救，[gold]金币-60[/gold]</x:v>
-      </x:c>
-      <x:c r="F54" s="1" t="str">
-        <x:v>你倒在餐桌旁，被火速送往医院抢救。</x:v>
-      </x:c>
-      <x:c r="H54"/>
+      <x:c r="E54" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">去icu抢救，[gold]金币-60[/gold]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F54" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">你倒在餐桌旁，被火速送往医院抢救。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I54" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">LoseEscalatingGold</x:t>
@@ -3895,8 +4042,10 @@
       <x:c r="M54" s="2" t="n">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="N54" s="2" t="str">
-        <x:v>绿色蘑菇鲜得惊人——紧接着，房间里的所有东西都变成了绿色。</x:v>
+      <x:c r="N54" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">绿色蘑菇鲜得惊人——紧接着，房间里的所有东西都变成了绿色。</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -3915,13 +4064,16 @@
           <x:t xml:space="preserve">opt_mushroom_try_green</x:t>
         </x:is>
       </x:c>
-      <x:c r="E55" s="1" t="str">
-        <x:v>大获成功！获得传奇[term]装饰品[/term]</x:v>
-      </x:c>
-      <x:c r="F55" s="1" t="str">
-        <x:v>你完整记住了三种蘑菇的风味，并获得 1 个传奇[term]装饰品[/term]。</x:v>
-      </x:c>
-      <x:c r="H55"/>
+      <x:c r="E55" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">大获成功！获得传奇[term]装饰品[/term]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F55" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">你完整记住了三种蘑菇的风味，并获得 1 个传奇[term]装饰品[/term]。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I55" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GainLegendaryItem</x:t>
@@ -3941,8 +4093,10 @@
       <x:c r="M55" s="2" t="n">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="N55" s="2" t="str">
-        <x:v>绿色蘑菇化成一股清香。你连过三关，主厨惊讶地捧出了珍藏礼物。</x:v>
+      <x:c r="N55" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">绿色蘑菇化成一股清香。你连过三关，主厨惊讶地捧出了珍藏礼物。</x:t>
+        </x:is>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -3956,13 +4110,16 @@
           <x:t xml:space="preserve">ev_last_supper</x:t>
         </x:is>
       </x:c>
-      <x:c r="E56" s="1" t="str">
-        <x:v>举杯饮酒</x:v>
-      </x:c>
-      <x:c r="F56" s="1" t="str">
-        <x:v>你举杯平息了争执。众厨师感谢你缓和气氛，约好下次到你的餐厅聚餐。</x:v>
-      </x:c>
-      <x:c r="H56"/>
+      <x:c r="E56" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">举杯饮酒</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F56" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">你举杯平息了争执。众厨师感谢你缓和气氛，约好下次到你的餐厅聚餐。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I56" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -3982,7 +4139,6 @@
       <x:c r="M56" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N56"/>
     </x:row>
     <x:row r="57">
       <x:c r="B57" s="1" t="inlineStr">
@@ -4000,13 +4156,16 @@
           <x:t xml:space="preserve">opt_last_supper_toast</x:t>
         </x:is>
       </x:c>
-      <x:c r="E57" s="1" t="str">
-        <x:v>下次营业[gold]金币+60%[/gold]</x:v>
-      </x:c>
-      <x:c r="F57" s="1" t="str">
-        <x:v>众厨师如约来访。下一次营业获得的基础[gold]金币[/gold]提高[gold]60%[/gold]。</x:v>
-      </x:c>
-      <x:c r="H57"/>
+      <x:c r="E57" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">下次营业[gold]金币+60%[/gold]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F57" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">众厨师如约来访。下一次营业获得的基础[gold]金币[/gold]提高[gold]60%[/gold]。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I57" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">AddBusinessGoldPct</x:t>
@@ -4026,7 +4185,6 @@
       <x:c r="M57" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N57"/>
     </x:row>
     <x:row r="58">
       <x:c r="B58" s="1" t="inlineStr">
@@ -4039,13 +4197,16 @@
           <x:t xml:space="preserve">ev_last_supper</x:t>
         </x:is>
       </x:c>
-      <x:c r="E58" s="1" t="str">
-        <x:v>指认别人</x:v>
-      </x:c>
-      <x:c r="F58" s="1" t="str">
-        <x:v>你指出那位袖口沾着对面餐厅印泥的厨师。他只好交出收到的定金。</x:v>
-      </x:c>
-      <x:c r="H58"/>
+      <x:c r="E58" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">指认别人</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F58" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">你指出那位袖口沾着对面餐厅印泥的厨师。他只好交出收到的定金。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I58" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -4065,7 +4226,6 @@
       <x:c r="M58" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N58"/>
     </x:row>
     <x:row r="59">
       <x:c r="B59" s="1" t="inlineStr">
@@ -4083,13 +4243,16 @@
           <x:t xml:space="preserve">opt_last_supper_accuse</x:t>
         </x:is>
       </x:c>
-      <x:c r="E59" s="1" t="str">
-        <x:v>收下定金</x:v>
-      </x:c>
-      <x:c r="F59" s="1" t="str">
-        <x:v>获得[gold]100金币[/gold]。</x:v>
-      </x:c>
-      <x:c r="H59"/>
+      <x:c r="E59" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">金币+100</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F59" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">获得[gold]100金币[/gold]。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I59" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">GainGold</x:t>
@@ -4109,7 +4272,6 @@
       <x:c r="M59" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N59"/>
     </x:row>
     <x:row r="60">
       <x:c r="B60" s="1" t="inlineStr">
@@ -4122,13 +4284,16 @@
           <x:t xml:space="preserve">ev_last_supper</x:t>
         </x:is>
       </x:c>
-      <x:c r="E60" s="1" t="str">
-        <x:v>分食面包</x:v>
-      </x:c>
-      <x:c r="F60" s="1" t="str">
-        <x:v>你把面包分给众人。十二位厨师各自用拿手菜回礼，你从中带走了两道。</x:v>
-      </x:c>
-      <x:c r="H60"/>
+      <x:c r="E60" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">分食面包</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F60" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">你把面包分给众人。十二位厨师各自用拿手菜回礼，你从中带走了两道。</x:t>
+        </x:is>
+      </x:c>
       <x:c r="I60" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">None</x:t>
@@ -4148,7 +4313,6 @@
       <x:c r="M60" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N60"/>
     </x:row>
     <x:row r="61">
       <x:c r="B61" s="1" t="inlineStr">
@@ -4166,25 +4330,24 @@
           <x:t xml:space="preserve">opt_last_supper_share</x:t>
         </x:is>
       </x:c>
-      <x:c r="E61" s="1" t="str">
-        <x:v>收下两道回礼</x:v>
+      <x:c r="E61" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">获得两个食物3选1</x:t>
+        </x:is>
       </x:c>
       <x:c r="F61" s="1" t="str">
-        <x:v>从众人的回礼中获得2个随机风味食物。</x:v>
-      </x:c>
+        <x:v>十二位厨师依次端上拿手菜。你从两组三道回礼中各选一道，加入食谱。</x:v>
+      </x:c>
+      <x:c r="G61"/>
       <x:c r="H61"/>
-      <x:c r="I61" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">GainRandomFlavoredDishes</x:t>
-        </x:is>
+      <x:c r="I61" s="1" t="str">
+        <x:v>EnqueueDishChoice</x:v>
       </x:c>
       <x:c r="J61" s="1" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K61" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">flavored_dish_2|众人的回礼</x:t>
-        </x:is>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K61" s="1" t="str">
+        <x:v>dish_choice_3|第一道回礼</x:v>
       </x:c>
       <x:c r="L61" s="1" t="n">
         <x:v>1</x:v>
@@ -4192,85 +4355,69 @@
       <x:c r="M61" s="2" t="n">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="N61"/>
     </x:row>
     <x:row r="62">
-      <x:c r="B62" s="1" t="inlineStr">
+      <x:c r="A62"/>
+      <x:c r="B62" s="1"/>
+      <x:c r="C62" s="1"/>
+      <x:c r="D62"/>
+      <x:c r="E62" s="1"/>
+      <x:c r="F62" s="1"/>
+      <x:c r="G62"/>
+      <x:c r="H62"/>
+      <x:c r="I62" s="1" t="str">
+        <x:v>EnqueueDishChoice</x:v>
+      </x:c>
+      <x:c r="J62" s="1" t="n">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="K62" s="1" t="str">
+        <x:v>dish_choice_3|第二道回礼</x:v>
+      </x:c>
+      <x:c r="L62" s="1"/>
+      <x:c r="M62" s="2"/>
+      <x:c r="N62"/>
+    </x:row>
+    <x:row r="63">
+      <x:c r="A63"/>
+      <x:c r="B63" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">opt_twin_peaks_coffee</x:t>
         </x:is>
       </x:c>
-      <x:c r="C62" s="1" t="inlineStr">
+      <x:c r="C63" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ev_twin_peaks_diner</x:t>
         </x:is>
       </x:c>
-      <x:c r="E62" s="1" t="str">
-        <x:v>喝黑咖啡</x:v>
-      </x:c>
-      <x:c r="F62" s="1" t="str">
-        <x:v>咖啡苦得恰到好处，你一下清醒过来，连夜整理了下一次营业安排。</x:v>
-      </x:c>
-      <x:c r="H62"/>
-      <x:c r="I62" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">None</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J62" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K62" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">-</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L62" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M62" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N62"/>
-    </x:row>
-    <x:row r="63">
-      <x:c r="B63" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">opt_twin_peaks_coffee_reward</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C63" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ev_twin_peaks_diner</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="D63" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">opt_twin_peaks_coffee</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E63" s="1" t="str">
-        <x:v>下两次营业[gold]金币+60%[/gold]</x:v>
-      </x:c>
-      <x:c r="F63" s="1" t="str">
-        <x:v>下两次营业基础[gold]金币[/gold]×1.6。</x:v>
-      </x:c>
+      <x:c r="D63" s="2"/>
+      <x:c r="E63" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">喝黑咖啡</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F63" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">咖啡苦得恰到好处，你一下清醒过来，连夜整理了下一次营业安排。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G63"/>
       <x:c r="H63"/>
       <x:c r="I63" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AddBusinessGoldPct</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J63" s="1" t="n">
-        <x:v>0.6</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K63" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">Next:2</x:t>
+          <x:t xml:space="preserve">-</x:t>
         </x:is>
       </x:c>
       <x:c r="L63" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M63" s="2" t="n">
         <x:v>0</x:v>
@@ -4278,9 +4425,10 @@
       <x:c r="N63"/>
     </x:row>
     <x:row r="64">
+      <x:c r="A64"/>
       <x:c r="B64" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">opt_twin_peaks_pie</x:t>
+          <x:t xml:space="preserve">opt_twin_peaks_coffee_reward</x:t>
         </x:is>
       </x:c>
       <x:c r="C64" s="1" t="inlineStr">
@@ -4288,28 +4436,38 @@
           <x:t xml:space="preserve">ev_twin_peaks_diner</x:t>
         </x:is>
       </x:c>
-      <x:c r="E64" s="1" t="str">
-        <x:v>点樱桃派</x:v>
-      </x:c>
-      <x:c r="F64" s="1" t="str">
-        <x:v>樱桃派美味可口，一天的疲惫一扫而空</x:v>
-      </x:c>
+      <x:c r="D64" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_twin_peaks_coffee</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E64" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">下两次营业[gold]金币+60%[/gold]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F64" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">下两次营业基础[gold]金币[/gold]×1.6。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G64"/>
       <x:c r="H64"/>
       <x:c r="I64" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">AddBusinessGoldPct</x:t>
         </x:is>
       </x:c>
       <x:c r="J64" s="1" t="n">
-        <x:v>0</x:v>
+        <x:v>0.6</x:v>
       </x:c>
       <x:c r="K64" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">-</x:t>
+          <x:t xml:space="preserve">Next:2</x:t>
         </x:is>
       </x:c>
       <x:c r="L64" s="1" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M64" s="2" t="n">
         <x:v>0</x:v>
@@ -4317,9 +4475,10 @@
       <x:c r="N64"/>
     </x:row>
     <x:row r="65">
+      <x:c r="A65"/>
       <x:c r="B65" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">opt_twin_peaks_pie_reward</x:t>
+          <x:t xml:space="preserve">opt_twin_peaks_pie</x:t>
         </x:is>
       </x:c>
       <x:c r="C65" s="1" t="inlineStr">
@@ -4327,25 +4486,26 @@
           <x:t xml:space="preserve">ev_twin_peaks_diner</x:t>
         </x:is>
       </x:c>
-      <x:c r="D65" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">opt_twin_peaks_pie</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E65" s="1" t="str">
-        <x:v>恢复1颗红心</x:v>
-      </x:c>
-      <x:c r="F65" s="1" t="str">
-        <x:v>恢复1颗红心，不超过红心上限。</x:v>
-      </x:c>
+      <x:c r="D65" s="2"/>
+      <x:c r="E65" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">点樱桃派</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F65" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">樱桃派美味可口，一天的疲惫一扫而空</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G65"/>
       <x:c r="H65"/>
       <x:c r="I65" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">RestoreHearts</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J65" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K65" s="1" t="inlineStr">
         <x:is>
@@ -4353,7 +4513,7 @@
         </x:is>
       </x:c>
       <x:c r="L65" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M65" s="2" t="n">
         <x:v>0</x:v>
@@ -4361,9 +4521,10 @@
       <x:c r="N65"/>
     </x:row>
     <x:row r="66">
+      <x:c r="A66"/>
       <x:c r="B66" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">opt_twin_peaks_log</x:t>
+          <x:t xml:space="preserve">opt_twin_peaks_pie_reward</x:t>
         </x:is>
       </x:c>
       <x:c r="C66" s="1" t="inlineStr">
@@ -4371,20 +4532,30 @@
           <x:t xml:space="preserve">ev_twin_peaks_diner</x:t>
         </x:is>
       </x:c>
-      <x:c r="E66" s="1" t="str">
-        <x:v>听听木头怎么说</x:v>
-      </x:c>
-      <x:c r="F66" s="1" t="str">
-        <x:v>木头女士转述了一段古怪配方。你回去试了一夜，食谱里原有的菜竟都变得更好吃了。</x:v>
-      </x:c>
+      <x:c r="D66" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_twin_peaks_pie</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E66" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">恢复1颗红心</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F66" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">恢复1颗红心，不超过红心上限。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G66"/>
       <x:c r="H66"/>
       <x:c r="I66" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">RestoreHearts</x:t>
         </x:is>
       </x:c>
       <x:c r="J66" s="1" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="K66" s="1" t="inlineStr">
         <x:is>
@@ -4392,7 +4563,7 @@
         </x:is>
       </x:c>
       <x:c r="L66" s="1" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M66" s="2" t="n">
         <x:v>0</x:v>
@@ -4400,9 +4571,10 @@
       <x:c r="N66"/>
     </x:row>
     <x:row r="67">
+      <x:c r="A67"/>
       <x:c r="B67" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">opt_twin_peaks_log_reward</x:t>
+          <x:t xml:space="preserve">opt_twin_peaks_log</x:t>
         </x:is>
       </x:c>
       <x:c r="C67" s="1" t="inlineStr">
@@ -4410,25 +4582,26 @@
           <x:t xml:space="preserve">ev_twin_peaks_diner</x:t>
         </x:is>
       </x:c>
-      <x:c r="D67" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">opt_twin_peaks_log</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E67" s="1" t="str">
-        <x:v>[context]所有[/context]食物[strong]分数[/strong]永久[score]+10[/score]</x:v>
-      </x:c>
-      <x:c r="F67" s="1" t="str">
-        <x:v>触发时食谱中已有的全部食物永久[strong]分数[/strong][score]+10[/score]</x:v>
-      </x:c>
+      <x:c r="D67" s="2"/>
+      <x:c r="E67" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">听听木头怎么说</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F67" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">木头女士转述了一段古怪配方。你回去试了一夜，食谱里原有的菜竟都变得更好吃了。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G67"/>
       <x:c r="H67"/>
       <x:c r="I67" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">AddAllRecipeScoreFlat</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J67" s="1" t="n">
-        <x:v>10</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K67" s="1" t="inlineStr">
         <x:is>
@@ -4436,7 +4609,7 @@
         </x:is>
       </x:c>
       <x:c r="L67" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M67" s="2" t="n">
         <x:v>0</x:v>
@@ -4444,30 +4617,39 @@
       <x:c r="N67"/>
     </x:row>
     <x:row r="68">
+      <x:c r="A68"/>
       <x:c r="B68" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">opt_chuka_ichiban_fried_rice</x:t>
+          <x:t xml:space="preserve">opt_twin_peaks_log_reward</x:t>
         </x:is>
       </x:c>
       <x:c r="C68" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">ev_chuka_ichiban_trial</x:t>
+          <x:t xml:space="preserve">ev_twin_peaks_diner</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D68" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_twin_peaks_log</x:t>
         </x:is>
       </x:c>
       <x:c r="E68" s="1" t="str">
-        <x:v>黄金炒饭</x:v>
-      </x:c>
-      <x:c r="F68" s="1" t="str">
-        <x:v>蛋液裹住每一粒米，揭盖时金光一闪。旅人把碗吃得干干净净，还在桌上留下赏钱。</x:v>
-      </x:c>
+        <x:v>[context]所有[/context]食物[strong]分数[/strong]永久[score]+15[/score]</x:v>
+      </x:c>
+      <x:c r="F68" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">触发时食谱中已有的全部食物永久[strong]分数[/strong][score]+15[/score]</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G68"/>
       <x:c r="H68"/>
       <x:c r="I68" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">AddAllRecipeScoreFlat</x:t>
         </x:is>
       </x:c>
       <x:c r="J68" s="1" t="n">
-        <x:v>0</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="K68" s="1" t="inlineStr">
         <x:is>
@@ -4475,7 +4657,7 @@
         </x:is>
       </x:c>
       <x:c r="L68" s="1" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M68" s="2" t="n">
         <x:v>0</x:v>
@@ -4483,9 +4665,10 @@
       <x:c r="N68"/>
     </x:row>
     <x:row r="69">
+      <x:c r="A69"/>
       <x:c r="B69" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">opt_chuka_ichiban_fried_rice_reward</x:t>
+          <x:t xml:space="preserve">opt_chuka_ichiban_fried_rice</x:t>
         </x:is>
       </x:c>
       <x:c r="C69" s="1" t="inlineStr">
@@ -4493,25 +4676,26 @@
           <x:t xml:space="preserve">ev_chuka_ichiban_trial</x:t>
         </x:is>
       </x:c>
-      <x:c r="D69" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">opt_chuka_ichiban_fried_rice</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E69" s="1" t="str">
-        <x:v>收下[gold]80金币[/gold]赏钱</x:v>
-      </x:c>
-      <x:c r="F69" s="1" t="str">
-        <x:v>旅人因黄金炒饭心满意足，留下[gold]80金币[/gold]。</x:v>
-      </x:c>
+      <x:c r="D69" s="2"/>
+      <x:c r="E69" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">黄金炒饭</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F69" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">蛋液裹住每一粒米，揭盖时金光一闪。旅人把碗吃得干干净净，还在桌上留下赏钱。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G69"/>
       <x:c r="H69"/>
       <x:c r="I69" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">GainGold</x:t>
+          <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
       <x:c r="J69" s="1" t="n">
-        <x:v>80</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="K69" s="1" t="inlineStr">
         <x:is>
@@ -4519,7 +4703,7 @@
         </x:is>
       </x:c>
       <x:c r="L69" s="1" t="n">
-        <x:v>1</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="M69" s="2" t="n">
         <x:v>0</x:v>
@@ -4527,9 +4711,10 @@
       <x:c r="N69"/>
     </x:row>
     <x:row r="70">
+      <x:c r="A70"/>
       <x:c r="B70" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">opt_chuka_ichiban_mapo_tofu</x:t>
+          <x:t xml:space="preserve">opt_chuka_ichiban_fried_rice_reward</x:t>
         </x:is>
       </x:c>
       <x:c r="C70" s="1" t="inlineStr">
@@ -4537,107 +4722,134 @@
           <x:t xml:space="preserve">ev_chuka_ichiban_trial</x:t>
         </x:is>
       </x:c>
-      <x:c r="E70" s="1" t="str">
-        <x:v>麻婆豆腐</x:v>
-      </x:c>
-      <x:c r="F70" s="1" t="str">
-        <x:v>你把大豆炒得酥香，让麻、辣、香、色、烫之外又添一层爽脆。小当家笑着点了点头。</x:v>
-      </x:c>
+      <x:c r="D70" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_chuka_ichiban_fried_rice</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E70" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">收下[gold]80金币[/gold]赏钱</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F70" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">旅人因黄金炒饭心满意足，留下[gold]80金币[/gold]。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G70"/>
       <x:c r="H70"/>
       <x:c r="I70" s="1" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">GainGold</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J70" s="1" t="n">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="K70" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">-</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L70" s="1" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M70" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N70"/>
+    </x:row>
+    <x:row r="71">
+      <x:c r="A71"/>
+      <x:c r="B71" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_chuka_ichiban_mapo_tofu</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C71" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ev_chuka_ichiban_trial</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D71" s="2"/>
+      <x:c r="E71" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">麻婆豆腐</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F71" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">你把大豆炒得酥香，让麻、辣、香、色、烫之外又添一层爽脆。小当家笑着点了点头。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G71"/>
+      <x:c r="H71"/>
+      <x:c r="I71" s="1" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">None</x:t>
         </x:is>
       </x:c>
-      <x:c r="J70" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K70" s="1" t="inlineStr">
+      <x:c r="J71" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K71" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">-</x:t>
         </x:is>
       </x:c>
-      <x:c r="L70" s="1" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="M70" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N70"/>
-    </x:row>
-    <x:row r="71">
-      <x:c r="B71" s="1" t="inlineStr">
+      <x:c r="L71" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M71" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N71"/>
+    </x:row>
+    <x:row r="72">
+      <x:c r="A72"/>
+      <x:c r="B72" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">opt_chuka_ichiban_mapo_tofu_reward</x:t>
         </x:is>
       </x:c>
-      <x:c r="C71" s="1" t="inlineStr">
+      <x:c r="C72" s="1" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">ev_chuka_ichiban_trial</x:t>
         </x:is>
       </x:c>
-      <x:c r="D71" s="2" t="inlineStr">
+      <x:c r="D72" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">opt_chuka_ichiban_mapo_tofu</x:t>
         </x:is>
       </x:c>
-      <x:c r="E71" s="1" t="str">
-        <x:v>获得2个风味强化箱</x:v>
-      </x:c>
-      <x:c r="F71" s="1" t="str">
-        <x:v>你从“酥”的灵感中举一反三，从六种风味强化箱中随机获得2个，可能重复。</x:v>
-      </x:c>
-      <x:c r="H71"/>
-      <x:c r="I71" s="1" t="str">
-        <x:v>GrantRandomActiveItems</x:v>
-      </x:c>
-      <x:c r="J71" s="1" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="K71" s="1" t="str">
-        <x:v>Ids:item_active_season_sweet,item_active_season_bitter,item_active_season_umami,item_active_season_numb,item_active_season_sour,item_active_season_salty|Replace</x:v>
-      </x:c>
-      <x:c r="L71" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M71" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N71"/>
-    </x:row>
-    <x:row r="72">
-      <x:c r="B72" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">opt_chuka_ichiban_dumpling</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="C72" s="1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">ev_chuka_ichiban_trial</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E72" s="1" t="str">
-        <x:v>大宇宙烧卖</x:v>
-      </x:c>
-      <x:c r="F72" s="1" t="str">
-        <x:v>一只烧卖占满了蒸笼，切开正好够全店分。众人围桌大笑，收档前的疲惫一扫而空。</x:v>
-      </x:c>
+      <x:c r="E72" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">获得2个风味强化箱</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F72" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">你从“酥”的灵感中举一反三，从六种风味强化箱中随机获得2个，可能重复。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G72"/>
       <x:c r="H72"/>
       <x:c r="I72" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">None</x:t>
+          <x:t xml:space="preserve">GrantRandomActiveItems</x:t>
         </x:is>
       </x:c>
       <x:c r="J72" s="1" t="n">
-        <x:v>0</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="K72" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">-</x:t>
+          <x:t xml:space="preserve">Ids:item_active_season_sweet,item_active_season_bitter,item_active_season_umami,item_active_season_numb,item_active_season_sour,item_active_season_salty|Replace</x:t>
         </x:is>
       </x:c>
       <x:c r="L72" s="1" t="n">
-        <x:v>0</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="M72" s="2" t="n">
         <x:v>0</x:v>
@@ -4645,9 +4857,10 @@
       <x:c r="N72"/>
     </x:row>
     <x:row r="73">
+      <x:c r="A73"/>
       <x:c r="B73" s="1" t="inlineStr">
         <x:is>
-          <x:t xml:space="preserve">opt_chuka_ichiban_dumpling_reward</x:t>
+          <x:t xml:space="preserve">opt_chuka_ichiban_dumpling</x:t>
         </x:is>
       </x:c>
       <x:c r="C73" s="1" t="inlineStr">
@@ -4655,38 +4868,89 @@
           <x:t xml:space="preserve">ev_chuka_ichiban_trial</x:t>
         </x:is>
       </x:c>
-      <x:c r="D73" s="2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">opt_chuka_ichiban_dumpling</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="E73" s="1" t="str">
-        <x:v>恢复1颗红心</x:v>
-      </x:c>
-      <x:c r="F73" s="1" t="str">
-        <x:v>大家分享烧卖后重新打起精神。恢复1颗红心，不超过红心上限。</x:v>
-      </x:c>
+      <x:c r="D73" s="2"/>
+      <x:c r="E73" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">大宇宙烧卖</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F73" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">一只烧卖占满了蒸笼，切开正好够全店分。众人围桌大笑，收档前的疲惫一扫而空。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G73"/>
       <x:c r="H73"/>
       <x:c r="I73" s="1" t="inlineStr">
         <x:is>
+          <x:t xml:space="preserve">None</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="J73" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K73" s="1" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">-</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="L73" s="1" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="M73" s="2" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N73"/>
+    </x:row>
+    <x:row r="74">
+      <x:c r="A74"/>
+      <x:c r="B74" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_chuka_ichiban_dumpling_reward</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="C74" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">ev_chuka_ichiban_trial</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="D74" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">opt_chuka_ichiban_dumpling</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="E74" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">恢复1颗红心</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="F74" t="inlineStr">
+        <x:is>
+          <x:t xml:space="preserve">大家分享烧卖后重新打起精神。恢复1颗红心，不超过红心上限。</x:t>
+        </x:is>
+      </x:c>
+      <x:c r="G74"/>
+      <x:c r="H74"/>
+      <x:c r="I74" t="inlineStr">
+        <x:is>
           <x:t xml:space="preserve">RestoreHearts</x:t>
         </x:is>
       </x:c>
-      <x:c r="J73" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="K73" s="1" t="inlineStr">
+      <x:c r="J74" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="K74" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">-</x:t>
         </x:is>
       </x:c>
-      <x:c r="L73" s="1" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="M73" s="2" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N73"/>
+      <x:c r="L74" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="M74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="N74"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/GourmetProject/GameConfig/Datas/event.xlsx
+++ b/GourmetProject/GameConfig/Datas/event.xlsx
@@ -2461,7 +2461,7 @@
         <v>67</v>
       </c>
       <c r="K10">
-        <v>0.4</v>
+        <v>0.45</v>
       </c>
       <c r="L10" t="s">
         <v>68</v>
